--- a/data-cleaning/verified/导入_全部批次.xlsx
+++ b/data-cleaning/verified/导入_全部批次.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F004-W001</t>
+          <t>1G-GGRQ-GQ-L002-F004-W</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F005-W002</t>
+          <t>1G-GGRQ-GQ-L002-F005-W</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F006-W003</t>
+          <t>1G-GGRQ-GQ-L002-F006-W</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F007-W004</t>
+          <t>1G-GGRQ-GQ-L002-F007-W</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F008-W005</t>
+          <t>1G-GGRQ-GQ-L002-F008-W</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F009-W006</t>
+          <t>1G-GGRQ-GQ-L002-F009-W</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F010-W007</t>
+          <t>1G-GGRQ-GQ-L002-F010-W</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F014-W008</t>
+          <t>1G-GGRQ-GQ-L002-F014-W</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F015-W009</t>
+          <t>1G-GGRQ-GQ-L002-F015-W</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F016-W010</t>
+          <t>1G-GGRQ-GQ-L002-F016-W</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F017-W011</t>
+          <t>1G-GGRQ-GQ-L002-F017-W</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F018-W012</t>
+          <t>1G-GGRQ-GQ-L002-F018-W</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F019-W013</t>
+          <t>1G-GGRQ-GQ-L002-F019-W</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F020-W014</t>
+          <t>1G-GGRQ-GQ-L002-F020-W</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F021-W015</t>
+          <t>1G-GGRQ-GQ-L002-F021-W</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F022-W016</t>
+          <t>1G-GGRQ-GQ-L002-F022-W</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F004-W017</t>
+          <t>1G-GGRQ-GQ-L031-F004-W</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F005-W018</t>
+          <t>1G-GGRQ-GQ-L031-F005-W</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F006-W019</t>
+          <t>1G-GGRQ-GQ-L031-F006-W</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F007-W020</t>
+          <t>1G-GGRQ-GQ-L031-F007-W</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F008-W021</t>
+          <t>1G-GGRQ-GQ-L031-F008-W</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F009-W022</t>
+          <t>1G-GGRQ-GQ-L031-F009-W</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F010-W023</t>
+          <t>1G-GGRQ-GQ-L031-F010-W</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F014-W024</t>
+          <t>1G-GGRQ-GQ-L031-F014-W</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F015-W025</t>
+          <t>1G-GGRQ-GQ-L031-F015-W</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F016-W026</t>
+          <t>1G-GGRQ-GQ-L031-F016-W</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F017-W027</t>
+          <t>1G-GGRQ-GQ-L031-F017-W</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F018-W028</t>
+          <t>1G-GGRQ-GQ-L031-F018-W</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F019-W029</t>
+          <t>1G-GGRQ-GQ-L031-F019-W</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F020-W030</t>
+          <t>1G-GGRQ-GQ-L031-F020-W</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F021-W031</t>
+          <t>1G-GGRQ-GQ-L031-F021-W</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F022-W032</t>
+          <t>1G-GGRQ-GQ-L031-F022-W</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F001-W033</t>
+          <t>1G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F001-W034</t>
+          <t>1G-GGRQ-GQ-L002-F001-W</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F001-W035</t>
+          <t>1G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F001-W036</t>
+          <t>1G-GGRQ-GQ-L004-F001-W</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F001-W037</t>
+          <t>1G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F001-W038</t>
+          <t>1G-GGRQ-GQ-L006-F001-W</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F001-W039</t>
+          <t>1G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F001-W040</t>
+          <t>1G-GGRQ-GQ-L008-F001-W</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F001-W041</t>
+          <t>1G-GGRQ-GQ-L009-F001-W</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F001-W042</t>
+          <t>1G-GGRQ-GQ-L010-F001-W</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F001-W043</t>
+          <t>1G-GGRQ-GQ-L011-F001-W</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F001-W044</t>
+          <t>1G-GGRQ-GQ-L012-F001-W</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F001-W045</t>
+          <t>1G-GGRQ-GQ-L013-F001-W</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F001-W046</t>
+          <t>1G-GGRQ-GQ-L014-F001-W</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F001-W047</t>
+          <t>1G-GGRQ-GQ-L015-F001-W</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F001-W048</t>
+          <t>1G-GGRQ-GQ-L016-F001-W</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F001-W049</t>
+          <t>1G-GGRQ-GQ-L017-F001-W</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F001-W050</t>
+          <t>1G-GGRQ-GQ-L018-F001-W</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F001-W051</t>
+          <t>1G-GGRQ-GQ-L019-F001-W</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F001-W052</t>
+          <t>1G-GGRQ-GQ-L020-F001-W</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F001-W053</t>
+          <t>1G-GGRQ-GQ-L021-F001-W</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F001-W054</t>
+          <t>1G-GGRQ-GQ-L022-F001-W</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F001-W055</t>
+          <t>1G-GGRQ-GQ-L023-F001-W</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F001-W056</t>
+          <t>1G-GGRQ-GQ-L024-F001-W</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F001-W057</t>
+          <t>1G-GGRQ-GQ-L025-F001-W</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F001-W058</t>
+          <t>1G-GGRQ-GQ-L026-F001-W</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F001-W059</t>
+          <t>1G-GGRQ-GQ-L028-F001-W</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F001-W060</t>
+          <t>1G-GGRQ-GQ-L029-F001-W</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F001-W061</t>
+          <t>1G-GGRQ-GQ-L030-F001-W</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F001-W062</t>
+          <t>1G-GGRQ-GQ-L031-F001-W</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F001-W063</t>
+          <t>1G-GGRQ-GQ-L032-F001-W</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W064</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W065</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F002-W066</t>
+          <t>1G-GGRQ-GQ-L002-F002-W</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F003-W067</t>
+          <t>1G-GGRQ-GQ-L002-F003-W</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W068</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W069</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F002-W070</t>
+          <t>1G-GGRQ-GQ-L004-F002-W</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F003-W071</t>
+          <t>1G-GGRQ-GQ-L004-F003-W</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W072</t>
+          <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W073</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F002-W074</t>
+          <t>1G-GGRQ-GQ-L006-F002-W</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F003-W075</t>
+          <t>1G-GGRQ-GQ-L006-F003-W</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W076</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W077</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F002-W078</t>
+          <t>1G-GGRQ-GQ-L008-F002-W</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F003-W079</t>
+          <t>1G-GGRQ-GQ-L008-F003-W</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F002-W080</t>
+          <t>1G-GGRQ-GQ-L009-F002-W</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F003-W081</t>
+          <t>1G-GGRQ-GQ-L009-F003-W</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F002-W082</t>
+          <t>1G-GGRQ-GQ-L010-F002-W</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F003-W083</t>
+          <t>1G-GGRQ-GQ-L010-F003-W</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F002-W084</t>
+          <t>1G-GGRQ-GQ-L011-F002-W</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F003-W085</t>
+          <t>1G-GGRQ-GQ-L011-F003-W</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F002-W086</t>
+          <t>1G-GGRQ-GQ-L012-F002-W</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F003-W087</t>
+          <t>1G-GGRQ-GQ-L012-F003-W</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F002-W088</t>
+          <t>1G-GGRQ-GQ-L013-F002-W</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F003-W089</t>
+          <t>1G-GGRQ-GQ-L013-F003-W</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F002-W090</t>
+          <t>1G-GGRQ-GQ-L014-F002-W</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F003-W091</t>
+          <t>1G-GGRQ-GQ-L014-F003-W</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F002-W092</t>
+          <t>1G-GGRQ-GQ-L015-F002-W</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F003-W093</t>
+          <t>1G-GGRQ-GQ-L015-F003-W</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F002-W094</t>
+          <t>1G-GGRQ-GQ-L016-F002-W</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F003-W095</t>
+          <t>1G-GGRQ-GQ-L016-F003-W</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F002-W096</t>
+          <t>1G-GGRQ-GQ-L017-F002-W</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F003-W097</t>
+          <t>1G-GGRQ-GQ-L017-F003-W</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F002-W098</t>
+          <t>1G-GGRQ-GQ-L018-F002-W</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F003-W099</t>
+          <t>1G-GGRQ-GQ-L018-F003-W</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F002-W100</t>
+          <t>1G-GGRQ-GQ-L019-F002-W</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F003-W101</t>
+          <t>1G-GGRQ-GQ-L019-F003-W</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F002-W102</t>
+          <t>1G-GGRQ-GQ-L020-F002-W</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F003-W103</t>
+          <t>1G-GGRQ-GQ-L020-F003-W</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F002-W104</t>
+          <t>1G-GGRQ-GQ-L021-F002-W</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F003-W105</t>
+          <t>1G-GGRQ-GQ-L021-F003-W</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F002-W106</t>
+          <t>1G-GGRQ-GQ-L022-F002-W</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F003-W107</t>
+          <t>1G-GGRQ-GQ-L022-F003-W</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F002-W108</t>
+          <t>1G-GGRQ-GQ-L023-F002-W</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F003-W109</t>
+          <t>1G-GGRQ-GQ-L023-F003-W</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F002-W110</t>
+          <t>1G-GGRQ-GQ-L024-F002-W</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F003-W111</t>
+          <t>1G-GGRQ-GQ-L024-F003-W</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F002-W112</t>
+          <t>1G-GGRQ-GQ-L025-F002-W</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F003-W113</t>
+          <t>1G-GGRQ-GQ-L025-F003-W</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F002-W114</t>
+          <t>1G-GGRQ-GQ-L026-F002-W</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F003-W115</t>
+          <t>1G-GGRQ-GQ-L026-F003-W</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F002-W116</t>
+          <t>1G-GGRQ-GQ-L027-F002-W</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F003-W117</t>
+          <t>1G-GGRQ-GQ-L027-F003-W</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F002-W118</t>
+          <t>1G-GGRQ-GQ-L028-F002-W</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F003-W119</t>
+          <t>1G-GGRQ-GQ-L028-F003-W</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F002-W120</t>
+          <t>1G-GGRQ-GQ-L029-F002-W</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F003-W121</t>
+          <t>1G-GGRQ-GQ-L029-F003-W</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F002-W122</t>
+          <t>1G-GGRQ-GQ-L030-F002-W</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F003-W123</t>
+          <t>1G-GGRQ-GQ-L030-F003-W</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F002-W124</t>
+          <t>1G-GGRQ-GQ-L031-F002-W</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F003-W125</t>
+          <t>1G-GGRQ-GQ-L031-F003-W</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F002-W126</t>
+          <t>1G-GGRQ-GQ-L032-F002-W</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F003-W127</t>
+          <t>1G-GGRQ-GQ-L032-F003-W</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W128</t>
+          <t>1G-GGRQ-GQ-L001-B001-W</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W129</t>
+          <t>1G-GGRQ-GQ-L002-B001-W</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W130</t>
+          <t>1G-GGRQ-GQ-L003-B001-W</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W131</t>
+          <t>1G-GGRQ-GQ-L004-B001-W</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W132</t>
+          <t>1G-GGRQ-GQ-L005-B001-W</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W133</t>
+          <t>1G-GGRQ-GQ-L006-B001-W</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W134</t>
+          <t>1G-GGRQ-GQ-L007-B001-W</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W135</t>
+          <t>1G-GGRQ-GQ-L008-B001-W</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W136</t>
+          <t>1G-GGRQ-GQ-L009-B001-W</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W137</t>
+          <t>1G-GGRQ-GQ-L010-B001-W</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W138</t>
+          <t>1G-GGRQ-GQ-L011-B001-W</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W139</t>
+          <t>1G-GGRQ-GQ-L012-B001-W</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W140</t>
+          <t>1G-GGRQ-GQ-L013-B001-W</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W141</t>
+          <t>1G-GGRQ-GQ-L014-B001-W</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W142</t>
+          <t>1G-GGRQ-GQ-L015-B001-W</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W143</t>
+          <t>1G-GGRQ-GQ-L016-B001-W</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W144</t>
+          <t>1G-GGRQ-GQ-L017-B001-W</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W145</t>
+          <t>1G-GGRQ-GQ-L018-B001-W</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W146</t>
+          <t>1G-GGRQ-GQ-L019-B001-W</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W147</t>
+          <t>1G-GGRQ-GQ-L020-B001-W</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W148</t>
+          <t>1G-GGRQ-GQ-L021-B001-W</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W149</t>
+          <t>1G-GGRQ-GQ-L022-B001-W</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W150</t>
+          <t>1G-GGRQ-GQ-L023-B001-W</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W151</t>
+          <t>1G-GGRQ-GQ-L024-B001-W</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W152</t>
+          <t>1G-GGRQ-GQ-L025-B001-W</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W153</t>
+          <t>1G-GGRQ-GQ-L026-B001-W</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W154</t>
+          <t>1G-GGRQ-GQ-L027-B001-W</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W155</t>
+          <t>1G-GGRQ-GQ-L028-B001-W</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W156</t>
+          <t>1G-GGRQ-GQ-L029-B001-W</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W157</t>
+          <t>1G-GGRQ-GQ-L030-B001-W</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W158</t>
+          <t>1G-GGRQ-GQ-L031-B001-W</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W159</t>
+          <t>1G-GGRQ-GQ-L032-B001-W</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F001-W001</t>
+          <t>1G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr"/>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W002</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W003</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr"/>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F004-W004</t>
+          <t>1G-GGRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F005-W005</t>
+          <t>1G-GGRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F006-W006</t>
+          <t>1G-GGRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F007-W007</t>
+          <t>1G-GGRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr"/>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F008-W008</t>
+          <t>1G-GGRQ-GQ-L001-F008-W</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F009-W009</t>
+          <t>1G-GGRQ-GQ-L001-F009-W</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr"/>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F010-W010</t>
+          <t>1G-GGRQ-GQ-L001-F010-W</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F011-W011</t>
+          <t>1G-GGRQ-GQ-L001-F011-W</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr"/>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F012-W012</t>
+          <t>1G-GGRQ-GQ-L001-F012-W</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F001-W013</t>
+          <t>1G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr"/>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W014</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W015</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F004-W016</t>
+          <t>1G-GGRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -15968,7 +15968,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F005-W017</t>
+          <t>1G-GGRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr"/>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F006-W018</t>
+          <t>1G-GGRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F007-W019</t>
+          <t>1G-GGRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr"/>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F008-W020</t>
+          <t>1G-GGRQ-GQ-L003-F008-W</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F009-W021</t>
+          <t>1G-GGRQ-GQ-L003-F009-W</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr"/>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F010-W022</t>
+          <t>1G-GGRQ-GQ-L003-F010-W</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F011-W023</t>
+          <t>1G-GGRQ-GQ-L003-F011-W</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F012-W024</t>
+          <t>1G-GGRQ-GQ-L003-F012-W</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F001-W025</t>
+          <t>1G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr"/>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W026</t>
+          <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -16808,7 +16808,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W027</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr"/>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F004-W028</t>
+          <t>1G-GGRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F005-W029</t>
+          <t>1G-GGRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr"/>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F006-W030</t>
+          <t>1G-GGRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -17144,7 +17144,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F007-W031</t>
+          <t>1G-GGRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F008-W032</t>
+          <t>1G-GGRQ-GQ-L005-F008-W</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F009-W033</t>
+          <t>1G-GGRQ-GQ-L005-F009-W</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr"/>
@@ -17396,7 +17396,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F010-W034</t>
+          <t>1G-GGRQ-GQ-L005-F010-W</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F011-W035</t>
+          <t>1G-GGRQ-GQ-L005-F011-W</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr"/>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F012-W036</t>
+          <t>1G-GGRQ-GQ-L005-F012-W</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F001-W037</t>
+          <t>1G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr"/>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W038</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W039</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr"/>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F004-W040</t>
+          <t>1G-GGRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr"/>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F005-W041</t>
+          <t>1G-GGRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr"/>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F006-W042</t>
+          <t>1G-GGRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr"/>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F007-W043</t>
+          <t>1G-GGRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr"/>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F008-W044</t>
+          <t>1G-GGRQ-GQ-L007-F008-W</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F009-W045</t>
+          <t>1G-GGRQ-GQ-L007-F009-W</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F010-W046</t>
+          <t>1G-GGRQ-GQ-L007-F010-W</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F011-W047</t>
+          <t>1G-GGRQ-GQ-L007-F011-W</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr"/>
@@ -18572,7 +18572,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F012-W048</t>
+          <t>1G-GGRQ-GQ-L007-F012-W</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr"/>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F001-W049</t>
+          <t>1G-GGRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr"/>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F002-W050</t>
+          <t>1G-GGRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr"/>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F003-W051</t>
+          <t>1G-GGRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr"/>
@@ -18908,7 +18908,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F004-W052</t>
+          <t>1G-GGRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F005-W053</t>
+          <t>1G-GGRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr"/>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F006-W054</t>
+          <t>1G-GGRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr"/>
@@ -19160,7 +19160,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F007-W055</t>
+          <t>1G-GGRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr"/>
@@ -19244,7 +19244,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F008-W056</t>
+          <t>1G-GGRQ-GQ-R001-F008-W</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr"/>
@@ -19328,7 +19328,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F009-W057</t>
+          <t>1G-GGRQ-GQ-R001-F009-W</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr"/>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F010-W058</t>
+          <t>1G-GGRQ-GQ-R001-F010-W</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr"/>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F011-W059</t>
+          <t>1G-GGRQ-GQ-R001-F011-W</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr"/>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R001-F012-W060</t>
+          <t>1G-GGRQ-GQ-R001-F012-W</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F001-W061</t>
+          <t>1G-GGRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr"/>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F002-W062</t>
+          <t>1G-GGRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F003-W063</t>
+          <t>1G-GGRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr"/>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F004-W064</t>
+          <t>1G-GGRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F005-W065</t>
+          <t>1G-GGRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr"/>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F006-W066</t>
+          <t>1G-GGRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
@@ -20168,7 +20168,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F007-W067</t>
+          <t>1G-GGRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr"/>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F008-W068</t>
+          <t>1G-GGRQ-GQ-R003-F008-W</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F009-W069</t>
+          <t>1G-GGRQ-GQ-R003-F009-W</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr"/>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F010-W070</t>
+          <t>1G-GGRQ-GQ-R003-F010-W</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F011-W071</t>
+          <t>1G-GGRQ-GQ-R003-F011-W</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr"/>
@@ -20588,7 +20588,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R003-F012-W072</t>
+          <t>1G-GGRQ-GQ-R003-F012-W</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F001-W073</t>
+          <t>1G-GGRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr"/>
@@ -20756,7 +20756,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F002-W074</t>
+          <t>1G-GGRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr"/>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F003-W075</t>
+          <t>1G-GGRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F004-W076</t>
+          <t>1G-GGRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr"/>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F005-W077</t>
+          <t>1G-GGRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr"/>
@@ -21092,7 +21092,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F006-W078</t>
+          <t>1G-GGRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr"/>
@@ -21176,7 +21176,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F007-W079</t>
+          <t>1G-GGRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F008-W080</t>
+          <t>1G-GGRQ-GQ-R005-F008-W</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr"/>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F009-W081</t>
+          <t>1G-GGRQ-GQ-R005-F009-W</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr"/>
@@ -21428,7 +21428,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F010-W082</t>
+          <t>1G-GGRQ-GQ-R005-F010-W</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr"/>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F011-W083</t>
+          <t>1G-GGRQ-GQ-R005-F011-W</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr"/>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R005-F012-W084</t>
+          <t>1G-GGRQ-GQ-R005-F012-W</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr"/>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F001-W085</t>
+          <t>1G-GGRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr"/>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F002-W086</t>
+          <t>1G-GGRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F003-W087</t>
+          <t>1G-GGRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr"/>
@@ -21932,7 +21932,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F004-W088</t>
+          <t>1G-GGRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F005-W089</t>
+          <t>1G-GGRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr"/>
@@ -22100,7 +22100,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F006-W090</t>
+          <t>1G-GGRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F007-W091</t>
+          <t>1G-GGRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr"/>
@@ -22268,7 +22268,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F008-W092</t>
+          <t>1G-GGRQ-GQ-R007-F008-W</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr"/>
@@ -22352,7 +22352,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F009-W093</t>
+          <t>1G-GGRQ-GQ-R007-F009-W</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F010-W094</t>
+          <t>1G-GGRQ-GQ-R007-F010-W</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr"/>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F011-W095</t>
+          <t>1G-GGRQ-GQ-R007-F011-W</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr"/>
@@ -22604,7 +22604,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-R007-F012-W096</t>
+          <t>1G-GGRQ-GQ-R007-F012-W</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr"/>
@@ -22688,7 +22688,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F001-W097</t>
+          <t>1G-GZRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F002-W098</t>
+          <t>1G-GZRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F003-W099</t>
+          <t>1G-GZRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F004-W100</t>
+          <t>1G-GZRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F005-W101</t>
+          <t>1G-GZRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F006-W102</t>
+          <t>1G-GZRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L001-F007-W103</t>
+          <t>1G-GZRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -23304,7 +23304,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F001-W104</t>
+          <t>1G-GZRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F002-W105</t>
+          <t>1G-GZRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F003-W106</t>
+          <t>1G-GZRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -23568,7 +23568,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F004-W107</t>
+          <t>1G-GZRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -23656,7 +23656,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F005-W108</t>
+          <t>1G-GZRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F006-W109</t>
+          <t>1G-GZRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L003-F007-W110</t>
+          <t>1G-GZRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F001-W111</t>
+          <t>1G-GZRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -24008,7 +24008,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F002-W112</t>
+          <t>1G-GZRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F003-W113</t>
+          <t>1G-GZRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -24184,7 +24184,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F004-W114</t>
+          <t>1G-GZRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -24272,7 +24272,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F005-W115</t>
+          <t>1G-GZRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F006-W116</t>
+          <t>1G-GZRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L005-F007-W117</t>
+          <t>1G-GZRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F001-W118</t>
+          <t>1G-GZRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F002-W119</t>
+          <t>1G-GZRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F003-W120</t>
+          <t>1G-GZRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -24800,7 +24800,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F004-W121</t>
+          <t>1G-GZRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F005-W122</t>
+          <t>1G-GZRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F006-W123</t>
+          <t>1G-GZRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -25064,7 +25064,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-L007-F007-W124</t>
+          <t>1G-GZRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F001-W125</t>
+          <t>1G-GZRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -25240,7 +25240,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F002-W126</t>
+          <t>1G-GZRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F003-W127</t>
+          <t>1G-GZRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F004-W128</t>
+          <t>1G-GZRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -25504,7 +25504,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F005-W129</t>
+          <t>1G-GZRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F006-W130</t>
+          <t>1G-GZRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R001-F007-W131</t>
+          <t>1G-GZRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
@@ -25768,7 +25768,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F001-W132</t>
+          <t>1G-GZRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F002-W133</t>
+          <t>1G-GZRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
@@ -25944,7 +25944,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F003-W134</t>
+          <t>1G-GZRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F004-W135</t>
+          <t>1G-GZRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F005-W136</t>
+          <t>1G-GZRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F006-W137</t>
+          <t>1G-GZRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R003-F007-W138</t>
+          <t>1G-GZRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -26384,7 +26384,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F001-W139</t>
+          <t>1G-GZRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F002-W140</t>
+          <t>1G-GZRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F003-W141</t>
+          <t>1G-GZRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F004-W142</t>
+          <t>1G-GZRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F005-W143</t>
+          <t>1G-GZRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F006-W144</t>
+          <t>1G-GZRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R005-F007-W145</t>
+          <t>1G-GZRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F001-W146</t>
+          <t>1G-GZRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F002-W147</t>
+          <t>1G-GZRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr">
@@ -27176,7 +27176,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F003-W148</t>
+          <t>1G-GZRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F004-W149</t>
+          <t>1G-GZRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -27352,7 +27352,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F005-W150</t>
+          <t>1G-GZRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -27440,7 +27440,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F006-W151</t>
+          <t>1G-GZRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
@@ -27528,7 +27528,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>1G-GZRQ-GQ-R007-F007-W152</t>
+          <t>1G-GZRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -27616,7 +27616,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F001-W001</t>
+          <t>2G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr"/>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F002-W002</t>
+          <t>2G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F003-W003</t>
+          <t>2G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr"/>
@@ -27868,7 +27868,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F004-W004</t>
+          <t>2G-GGRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr"/>
@@ -27952,7 +27952,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F005-W005</t>
+          <t>2G-GGRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr"/>
@@ -28036,7 +28036,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F006-W006</t>
+          <t>2G-GGRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F007-W007</t>
+          <t>2G-GGRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr"/>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F008-W008</t>
+          <t>2G-GGRQ-GQ-L001-F008-W</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr"/>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F009-W009</t>
+          <t>2G-GGRQ-GQ-L001-F009-W</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr"/>
@@ -28372,7 +28372,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F010-W010</t>
+          <t>2G-GGRQ-GQ-L001-F010-W</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr"/>
@@ -28456,7 +28456,7 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F011-W011</t>
+          <t>2G-GGRQ-GQ-L001-F011-W</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr"/>
@@ -28540,7 +28540,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L001-F012-W012</t>
+          <t>2G-GGRQ-GQ-L001-F012-W</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr"/>
@@ -28624,7 +28624,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F001-W013</t>
+          <t>2G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr"/>
@@ -28708,7 +28708,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F002-W014</t>
+          <t>2G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr"/>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F003-W015</t>
+          <t>2G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr"/>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F004-W016</t>
+          <t>2G-GGRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr"/>
@@ -28960,7 +28960,7 @@
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F005-W017</t>
+          <t>2G-GGRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr"/>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F006-W018</t>
+          <t>2G-GGRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr"/>
@@ -29128,7 +29128,7 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F007-W019</t>
+          <t>2G-GGRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr"/>
@@ -29212,7 +29212,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F008-W020</t>
+          <t>2G-GGRQ-GQ-L003-F008-W</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr"/>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F009-W021</t>
+          <t>2G-GGRQ-GQ-L003-F009-W</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr"/>
@@ -29380,7 +29380,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F010-W022</t>
+          <t>2G-GGRQ-GQ-L003-F010-W</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr"/>
@@ -29464,7 +29464,7 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F011-W023</t>
+          <t>2G-GGRQ-GQ-L003-F011-W</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L003-F012-W024</t>
+          <t>2G-GGRQ-GQ-L003-F012-W</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr"/>
@@ -29632,7 +29632,7 @@
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F001-W025</t>
+          <t>2G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr"/>
@@ -29716,7 +29716,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F002-W026</t>
+          <t>2G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr"/>
@@ -29800,7 +29800,7 @@
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F003-W027</t>
+          <t>2G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr"/>
@@ -29884,7 +29884,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F004-W028</t>
+          <t>2G-GGRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr"/>
@@ -29968,7 +29968,7 @@
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F005-W029</t>
+          <t>2G-GGRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F006-W030</t>
+          <t>2G-GGRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr"/>
@@ -30136,7 +30136,7 @@
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F007-W031</t>
+          <t>2G-GGRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr"/>
@@ -30220,7 +30220,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F008-W032</t>
+          <t>2G-GGRQ-GQ-L005-F008-W</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr"/>
@@ -30304,7 +30304,7 @@
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F009-W033</t>
+          <t>2G-GGRQ-GQ-L005-F009-W</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr"/>
@@ -30388,7 +30388,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F010-W034</t>
+          <t>2G-GGRQ-GQ-L005-F010-W</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr"/>
@@ -30472,7 +30472,7 @@
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F011-W035</t>
+          <t>2G-GGRQ-GQ-L005-F011-W</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr"/>
@@ -30556,7 +30556,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L005-F012-W036</t>
+          <t>2G-GGRQ-GQ-L005-F012-W</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr"/>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F001-W037</t>
+          <t>2G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr"/>
@@ -30724,7 +30724,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F002-W038</t>
+          <t>2G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr"/>
@@ -30808,7 +30808,7 @@
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F003-W039</t>
+          <t>2G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr"/>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F004-W040</t>
+          <t>2G-GGRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr"/>
@@ -30976,7 +30976,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F005-W041</t>
+          <t>2G-GGRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr"/>
@@ -31060,7 +31060,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F006-W042</t>
+          <t>2G-GGRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr"/>
@@ -31144,7 +31144,7 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F007-W043</t>
+          <t>2G-GGRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr"/>
@@ -31228,7 +31228,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F008-W044</t>
+          <t>2G-GGRQ-GQ-L007-F008-W</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr"/>
@@ -31312,7 +31312,7 @@
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F009-W045</t>
+          <t>2G-GGRQ-GQ-L007-F009-W</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F010-W046</t>
+          <t>2G-GGRQ-GQ-L007-F010-W</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F011-W047</t>
+          <t>2G-GGRQ-GQ-L007-F011-W</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr"/>
@@ -31564,7 +31564,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-L007-F012-W048</t>
+          <t>2G-GGRQ-GQ-L007-F012-W</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr"/>
@@ -31648,7 +31648,7 @@
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F001-W049</t>
+          <t>2G-GGRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr"/>
@@ -31732,7 +31732,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F002-W050</t>
+          <t>2G-GGRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr"/>
@@ -31816,7 +31816,7 @@
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F003-W051</t>
+          <t>2G-GGRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr"/>
@@ -31900,7 +31900,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F004-W052</t>
+          <t>2G-GGRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr"/>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F005-W053</t>
+          <t>2G-GGRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr"/>
@@ -32068,7 +32068,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F006-W054</t>
+          <t>2G-GGRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr"/>
@@ -32152,7 +32152,7 @@
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F007-W055</t>
+          <t>2G-GGRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr"/>
@@ -32236,7 +32236,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F008-W056</t>
+          <t>2G-GGRQ-GQ-R001-F008-W</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr"/>
@@ -32320,7 +32320,7 @@
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F009-W057</t>
+          <t>2G-GGRQ-GQ-R001-F009-W</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr"/>
@@ -32404,7 +32404,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F010-W058</t>
+          <t>2G-GGRQ-GQ-R001-F010-W</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr"/>
@@ -32488,7 +32488,7 @@
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F011-W059</t>
+          <t>2G-GGRQ-GQ-R001-F011-W</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr"/>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R001-F012-W060</t>
+          <t>2G-GGRQ-GQ-R001-F012-W</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr"/>
@@ -32656,7 +32656,7 @@
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F001-W061</t>
+          <t>2G-GGRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr"/>
@@ -32740,7 +32740,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F002-W062</t>
+          <t>2G-GGRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr"/>
@@ -32824,7 +32824,7 @@
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F003-W063</t>
+          <t>2G-GGRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr"/>
@@ -32908,7 +32908,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F004-W064</t>
+          <t>2G-GGRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr"/>
@@ -32992,7 +32992,7 @@
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F005-W065</t>
+          <t>2G-GGRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr"/>
@@ -33076,7 +33076,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F006-W066</t>
+          <t>2G-GGRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr"/>
@@ -33160,7 +33160,7 @@
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F007-W067</t>
+          <t>2G-GGRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr"/>
@@ -33244,7 +33244,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F008-W068</t>
+          <t>2G-GGRQ-GQ-R003-F008-W</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr"/>
@@ -33328,7 +33328,7 @@
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F009-W069</t>
+          <t>2G-GGRQ-GQ-R003-F009-W</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F010-W070</t>
+          <t>2G-GGRQ-GQ-R003-F010-W</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr"/>
@@ -33496,7 +33496,7 @@
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F011-W071</t>
+          <t>2G-GGRQ-GQ-R003-F011-W</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr"/>
@@ -33580,7 +33580,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R003-F012-W072</t>
+          <t>2G-GGRQ-GQ-R003-F012-W</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr"/>
@@ -33664,7 +33664,7 @@
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F001-W073</t>
+          <t>2G-GGRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr"/>
@@ -33748,7 +33748,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F002-W074</t>
+          <t>2G-GGRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr"/>
@@ -33832,7 +33832,7 @@
       </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F003-W075</t>
+          <t>2G-GGRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="E387" s="4" t="inlineStr"/>
@@ -33916,7 +33916,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F004-W076</t>
+          <t>2G-GGRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F005-W077</t>
+          <t>2G-GGRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr"/>
@@ -34084,7 +34084,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F006-W078</t>
+          <t>2G-GGRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr"/>
@@ -34168,7 +34168,7 @@
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F007-W079</t>
+          <t>2G-GGRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr"/>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F008-W080</t>
+          <t>2G-GGRQ-GQ-R005-F008-W</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr"/>
@@ -34336,7 +34336,7 @@
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F009-W081</t>
+          <t>2G-GGRQ-GQ-R005-F009-W</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F010-W082</t>
+          <t>2G-GGRQ-GQ-R005-F010-W</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr"/>
@@ -34504,7 +34504,7 @@
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F011-W083</t>
+          <t>2G-GGRQ-GQ-R005-F011-W</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr"/>
@@ -34588,7 +34588,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R005-F012-W084</t>
+          <t>2G-GGRQ-GQ-R005-F012-W</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr"/>
@@ -34672,7 +34672,7 @@
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F001-W085</t>
+          <t>2G-GGRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F002-W086</t>
+          <t>2G-GGRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr"/>
@@ -34840,7 +34840,7 @@
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F003-W087</t>
+          <t>2G-GGRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F004-W088</t>
+          <t>2G-GGRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr"/>
@@ -35008,7 +35008,7 @@
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F005-W089</t>
+          <t>2G-GGRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr"/>
@@ -35092,7 +35092,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F006-W090</t>
+          <t>2G-GGRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr"/>
@@ -35176,7 +35176,7 @@
       </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F007-W091</t>
+          <t>2G-GGRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="E403" s="4" t="inlineStr"/>
@@ -35260,7 +35260,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F008-W092</t>
+          <t>2G-GGRQ-GQ-R007-F008-W</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F009-W093</t>
+          <t>2G-GGRQ-GQ-R007-F009-W</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr"/>
@@ -35428,7 +35428,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F010-W094</t>
+          <t>2G-GGRQ-GQ-R007-F010-W</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr"/>
@@ -35512,7 +35512,7 @@
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F011-W095</t>
+          <t>2G-GGRQ-GQ-R007-F011-W</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr"/>
@@ -35596,7 +35596,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>2G-GGRQ-GQ-R007-F012-W096</t>
+          <t>2G-GGRQ-GQ-R007-F012-W</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr"/>
@@ -35680,7 +35680,7 @@
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F001-W097</t>
+          <t>2G-GZRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E409" s="4" t="inlineStr">
@@ -35768,7 +35768,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F002-W098</t>
+          <t>2G-GZRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -35856,7 +35856,7 @@
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F003-W099</t>
+          <t>2G-GZRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr">
@@ -35944,7 +35944,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F004-W100</t>
+          <t>2G-GZRQ-GQ-L001-F004-W</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -36032,7 +36032,7 @@
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F005-W101</t>
+          <t>2G-GZRQ-GQ-L001-F005-W</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F006-W102</t>
+          <t>2G-GZRQ-GQ-L001-F006-W</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -36208,7 +36208,7 @@
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L001-F007-W103</t>
+          <t>2G-GZRQ-GQ-L001-F007-W</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F001-W104</t>
+          <t>2G-GZRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -36384,7 +36384,7 @@
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F002-W105</t>
+          <t>2G-GZRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F003-W106</t>
+          <t>2G-GZRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F004-W107</t>
+          <t>2G-GZRQ-GQ-L003-F004-W</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr">
@@ -36648,7 +36648,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F005-W108</t>
+          <t>2G-GZRQ-GQ-L003-F005-W</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -36736,7 +36736,7 @@
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F006-W109</t>
+          <t>2G-GZRQ-GQ-L003-F006-W</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr">
@@ -36824,7 +36824,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L003-F007-W110</t>
+          <t>2G-GZRQ-GQ-L003-F007-W</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F001-W111</t>
+          <t>2G-GZRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E423" s="4" t="inlineStr">
@@ -37000,7 +37000,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F002-W112</t>
+          <t>2G-GZRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F003-W113</t>
+          <t>2G-GZRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E425" s="4" t="inlineStr">
@@ -37176,7 +37176,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F004-W114</t>
+          <t>2G-GZRQ-GQ-L005-F004-W</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -37264,7 +37264,7 @@
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F005-W115</t>
+          <t>2G-GZRQ-GQ-L005-F005-W</t>
         </is>
       </c>
       <c r="E427" s="4" t="inlineStr">
@@ -37352,7 +37352,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F006-W116</t>
+          <t>2G-GZRQ-GQ-L005-F006-W</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -37440,7 +37440,7 @@
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L005-F007-W117</t>
+          <t>2G-GZRQ-GQ-L005-F007-W</t>
         </is>
       </c>
       <c r="E429" s="4" t="inlineStr">
@@ -37528,7 +37528,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F001-W118</t>
+          <t>2G-GZRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -37616,7 +37616,7 @@
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F002-W119</t>
+          <t>2G-GZRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E431" s="4" t="inlineStr">
@@ -37704,7 +37704,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F003-W120</t>
+          <t>2G-GZRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -37792,7 +37792,7 @@
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F004-W121</t>
+          <t>2G-GZRQ-GQ-L007-F004-W</t>
         </is>
       </c>
       <c r="E433" s="4" t="inlineStr">
@@ -37880,7 +37880,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F005-W122</t>
+          <t>2G-GZRQ-GQ-L007-F005-W</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -37968,7 +37968,7 @@
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F006-W123</t>
+          <t>2G-GZRQ-GQ-L007-F006-W</t>
         </is>
       </c>
       <c r="E435" s="4" t="inlineStr">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-L007-F007-W124</t>
+          <t>2G-GZRQ-GQ-L007-F007-W</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -38144,7 +38144,7 @@
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F001-W125</t>
+          <t>2G-GZRQ-GQ-R001-F001-W</t>
         </is>
       </c>
       <c r="E437" s="4" t="inlineStr">
@@ -38232,7 +38232,7 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F002-W126</t>
+          <t>2G-GZRQ-GQ-R001-F002-W</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
@@ -38320,7 +38320,7 @@
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F003-W127</t>
+          <t>2G-GZRQ-GQ-R001-F003-W</t>
         </is>
       </c>
       <c r="E439" s="4" t="inlineStr">
@@ -38408,7 +38408,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F004-W128</t>
+          <t>2G-GZRQ-GQ-R001-F004-W</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -38496,7 +38496,7 @@
       </c>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F005-W129</t>
+          <t>2G-GZRQ-GQ-R001-F005-W</t>
         </is>
       </c>
       <c r="E441" s="4" t="inlineStr">
@@ -38584,7 +38584,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F006-W130</t>
+          <t>2G-GZRQ-GQ-R001-F006-W</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -38672,7 +38672,7 @@
       </c>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R001-F007-W131</t>
+          <t>2G-GZRQ-GQ-R001-F007-W</t>
         </is>
       </c>
       <c r="E443" s="4" t="inlineStr">
@@ -38760,7 +38760,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F001-W132</t>
+          <t>2G-GZRQ-GQ-R003-F001-W</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
@@ -38848,7 +38848,7 @@
       </c>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F002-W133</t>
+          <t>2G-GZRQ-GQ-R003-F002-W</t>
         </is>
       </c>
       <c r="E445" s="4" t="inlineStr">
@@ -38936,7 +38936,7 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F003-W134</t>
+          <t>2G-GZRQ-GQ-R003-F003-W</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -39024,7 +39024,7 @@
       </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F004-W135</t>
+          <t>2G-GZRQ-GQ-R003-F004-W</t>
         </is>
       </c>
       <c r="E447" s="4" t="inlineStr">
@@ -39112,7 +39112,7 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F005-W136</t>
+          <t>2G-GZRQ-GQ-R003-F005-W</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F006-W137</t>
+          <t>2G-GZRQ-GQ-R003-F006-W</t>
         </is>
       </c>
       <c r="E449" s="4" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R003-F007-W138</t>
+          <t>2G-GZRQ-GQ-R003-F007-W</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
@@ -39376,7 +39376,7 @@
       </c>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F001-W139</t>
+          <t>2G-GZRQ-GQ-R005-F001-W</t>
         </is>
       </c>
       <c r="E451" s="4" t="inlineStr">
@@ -39464,7 +39464,7 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F002-W140</t>
+          <t>2G-GZRQ-GQ-R005-F002-W</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
@@ -39552,7 +39552,7 @@
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F003-W141</t>
+          <t>2G-GZRQ-GQ-R005-F003-W</t>
         </is>
       </c>
       <c r="E453" s="4" t="inlineStr">
@@ -39640,7 +39640,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F004-W142</t>
+          <t>2G-GZRQ-GQ-R005-F004-W</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -39728,7 +39728,7 @@
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F005-W143</t>
+          <t>2G-GZRQ-GQ-R005-F005-W</t>
         </is>
       </c>
       <c r="E455" s="4" t="inlineStr">
@@ -39816,7 +39816,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F006-W144</t>
+          <t>2G-GZRQ-GQ-R005-F006-W</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -39904,7 +39904,7 @@
       </c>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R005-F007-W145</t>
+          <t>2G-GZRQ-GQ-R005-F007-W</t>
         </is>
       </c>
       <c r="E457" s="4" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F001-W146</t>
+          <t>2G-GZRQ-GQ-R007-F001-W</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -40080,7 +40080,7 @@
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F002-W147</t>
+          <t>2G-GZRQ-GQ-R007-F002-W</t>
         </is>
       </c>
       <c r="E459" s="4" t="inlineStr">
@@ -40168,7 +40168,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F003-W148</t>
+          <t>2G-GZRQ-GQ-R007-F003-W</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -40256,7 +40256,7 @@
       </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F004-W149</t>
+          <t>2G-GZRQ-GQ-R007-F004-W</t>
         </is>
       </c>
       <c r="E461" s="4" t="inlineStr">
@@ -40344,7 +40344,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F005-W150</t>
+          <t>2G-GZRQ-GQ-R007-F005-W</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -40432,7 +40432,7 @@
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F006-W151</t>
+          <t>2G-GZRQ-GQ-R007-F006-W</t>
         </is>
       </c>
       <c r="E463" s="4" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>2G-GZRQ-GQ-R007-F007-W152</t>
+          <t>2G-GZRQ-GQ-R007-F007-W</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">

--- a/data-cleaning/verified/导入_全部批次.xlsx
+++ b/data-cleaning/verified/导入_全部批次.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="145" customHeight="1">
+    <row r="2" ht="107" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -619,8 +619,16 @@
           <t>1G-GGRQ-GQ-L002-F004-W</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -631,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→304H</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -684,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="145" customHeight="1">
+    <row r="3" ht="107" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -703,8 +711,16 @@
           <t>1G-GGRQ-GQ-L002-F005-W</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
@@ -715,7 +731,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -768,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="145" customHeight="1">
+    <row r="4" ht="107" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -787,8 +803,16 @@
           <t>1G-GGRQ-GQ-L002-F006-W</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
@@ -799,7 +823,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -852,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="145" customHeight="1">
+    <row r="5" ht="107" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -871,8 +895,16 @@
           <t>1G-GGRQ-GQ-L002-F007-W</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
@@ -883,7 +915,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -936,7 +968,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="145" customHeight="1">
+    <row r="6" ht="107" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -955,8 +987,16 @@
           <t>1G-GGRQ-GQ-L002-F008-W</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
@@ -967,7 +1007,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1020,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="145" customHeight="1">
+    <row r="7" ht="107" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1039,8 +1079,16 @@
           <t>1G-GGRQ-GQ-L002-F009-W</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
@@ -1051,7 +1099,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1104,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="145" customHeight="1">
+    <row r="8" ht="107" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1123,8 +1171,16 @@
           <t>1G-GGRQ-GQ-L002-F010-W</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
@@ -1135,7 +1191,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1188,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="145" customHeight="1">
+    <row r="9" ht="107" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1207,8 +1263,16 @@
           <t>1G-GGRQ-GQ-L002-F014-W</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
@@ -1219,7 +1283,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1272,7 +1336,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="145" customHeight="1">
+    <row r="10" ht="107" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1291,8 +1355,16 @@
           <t>1G-GGRQ-GQ-L002-F015-W</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
@@ -1303,7 +1375,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1356,7 +1428,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="145" customHeight="1">
+    <row r="11" ht="107" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1375,8 +1447,16 @@
           <t>1G-GGRQ-GQ-L002-F016-W</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
@@ -1387,7 +1467,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1440,7 +1520,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="145" customHeight="1">
+    <row r="12" ht="107" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1459,8 +1539,16 @@
           <t>1G-GGRQ-GQ-L002-F017-W</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
@@ -1471,7 +1559,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1524,7 +1612,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="145" customHeight="1">
+    <row r="13" ht="107" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1543,8 +1631,16 @@
           <t>1G-GGRQ-GQ-L002-F018-W</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
@@ -1555,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1608,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="145" customHeight="1">
+    <row r="14" ht="107" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1627,8 +1723,16 @@
           <t>1G-GGRQ-GQ-L002-F019-W</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
@@ -1639,7 +1743,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1692,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="145" customHeight="1">
+    <row r="15" ht="107" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1711,8 +1815,16 @@
           <t>1G-GGRQ-GQ-L002-F020-W</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
@@ -1723,7 +1835,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1776,7 +1888,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="145" customHeight="1">
+    <row r="16" ht="107" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1795,8 +1907,16 @@
           <t>1G-GGRQ-GQ-L002-F021-W</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
@@ -1807,7 +1927,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→304H</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1860,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="145" customHeight="1">
+    <row r="17" ht="107" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1879,8 +1999,16 @@
           <t>1G-GGRQ-GQ-L002-F022-W</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
@@ -1891,7 +2019,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→304H</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1944,7 +2072,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="145" customHeight="1">
+    <row r="18" ht="107" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1963,8 +2091,16 @@
           <t>1G-GGRQ-GQ-L031-F004-W</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
@@ -1975,7 +2111,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→304H</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2028,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="145" customHeight="1">
+    <row r="19" ht="107" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2047,8 +2183,16 @@
           <t>1G-GGRQ-GQ-L031-F005-W</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
@@ -2059,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2256,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="145" customHeight="1">
+    <row r="20" ht="107" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2131,8 +2275,16 @@
           <t>1G-GGRQ-GQ-L031-F006-W</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -2143,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2196,7 +2348,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="145" customHeight="1">
+    <row r="21" ht="107" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2215,8 +2367,16 @@
           <t>1G-GGRQ-GQ-L031-F007-W</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
@@ -2227,7 +2387,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2280,7 +2440,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="145" customHeight="1">
+    <row r="22" ht="107" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2299,8 +2459,16 @@
           <t>1G-GGRQ-GQ-L031-F008-W</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
@@ -2311,7 +2479,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2364,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="145" customHeight="1">
+    <row r="23" ht="107" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2383,8 +2551,16 @@
           <t>1G-GGRQ-GQ-L031-F009-W</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
@@ -2395,7 +2571,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2448,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="145" customHeight="1">
+    <row r="24" ht="107" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2467,8 +2643,16 @@
           <t>1G-GGRQ-GQ-L031-F010-W</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
@@ -2479,7 +2663,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2532,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="145" customHeight="1">
+    <row r="25" ht="107" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2551,8 +2735,16 @@
           <t>1G-GGRQ-GQ-L031-F014-W</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
@@ -2563,7 +2755,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2616,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="145" customHeight="1">
+    <row r="26" ht="107" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2635,8 +2827,16 @@
           <t>1G-GGRQ-GQ-L031-F015-W</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
@@ -2647,7 +2847,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2700,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="145" customHeight="1">
+    <row r="27" ht="107" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2719,8 +2919,16 @@
           <t>1G-GGRQ-GQ-L031-F016-W</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
@@ -2731,7 +2939,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2784,7 +2992,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="145" customHeight="1">
+    <row r="28" ht="107" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2803,8 +3011,16 @@
           <t>1G-GGRQ-GQ-L031-F017-W</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
@@ -2815,7 +3031,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2868,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="145" customHeight="1">
+    <row r="29" ht="107" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2887,8 +3103,16 @@
           <t>1G-GGRQ-GQ-L031-F018-W</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
@@ -2899,7 +3123,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2952,7 +3176,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="145" customHeight="1">
+    <row r="30" ht="107" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2971,8 +3195,16 @@
           <t>1G-GGRQ-GQ-L031-F019-W</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
@@ -2983,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3036,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="145" customHeight="1">
+    <row r="31" ht="107" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3055,8 +3287,16 @@
           <t>1G-GGRQ-GQ-L031-F020-W</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
@@ -3067,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3120,7 +3360,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="145" customHeight="1">
+    <row r="32" ht="107" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3139,8 +3379,16 @@
           <t>1G-GGRQ-GQ-L031-F021-W</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
@@ -3151,7 +3399,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→304H</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3204,7 +3452,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="145" customHeight="1">
+    <row r="33" ht="107" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3223,8 +3471,16 @@
           <t>1G-GGRQ-GQ-L031-F022-W</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
@@ -3235,7 +3491,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→304H</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -6179,7 +6435,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6267,7 +6523,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6355,7 +6611,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6443,7 +6699,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6531,7 +6787,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6619,7 +6875,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6707,7 +6963,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6756,7 +7012,7 @@
       </c>
       <c r="V71" s="4" t="inlineStr"/>
     </row>
-    <row r="72" ht="88" customHeight="1">
+    <row r="72" ht="107" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6795,7 +7051,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6848,7 +7104,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="88" customHeight="1">
+    <row r="73" ht="107" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6887,7 +7143,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6979,7 +7235,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7067,7 +7323,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7155,7 +7411,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7243,7 +7499,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7331,7 +7587,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7419,7 +7675,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7507,7 +7763,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7595,7 +7851,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7683,7 +7939,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7732,7 +7988,7 @@
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
-    <row r="83" ht="88" customHeight="1">
+    <row r="83" ht="107" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7771,7 +8027,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7863,7 +8119,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -7951,7 +8207,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8039,7 +8295,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8127,7 +8383,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8215,7 +8471,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8264,7 +8520,7 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="88" customHeight="1">
+    <row r="89" ht="107" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8303,7 +8559,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8395,7 +8651,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8483,7 +8739,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8571,7 +8827,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8659,7 +8915,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -8747,7 +9003,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -8835,7 +9091,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -8923,7 +9179,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -9011,7 +9267,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9099,7 +9355,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9187,7 +9443,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9275,7 +9531,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -9363,7 +9619,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9451,7 +9707,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9539,7 +9795,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9627,7 +9883,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9715,7 +9971,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -9803,7 +10059,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -9891,7 +10147,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -9979,7 +10235,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -10067,7 +10323,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -10155,7 +10411,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -10243,7 +10499,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -10331,7 +10587,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10380,7 +10636,7 @@
       </c>
       <c r="V112" s="2" t="inlineStr"/>
     </row>
-    <row r="113" ht="88" customHeight="1">
+    <row r="113" ht="107" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10419,7 +10675,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10511,7 +10767,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10599,7 +10855,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -10687,7 +10943,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -10775,7 +11031,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -10863,7 +11119,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -10951,7 +11207,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -11039,7 +11295,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -11127,7 +11383,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -11215,7 +11471,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -11303,7 +11559,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -11391,7 +11647,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11479,7 +11735,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11567,7 +11823,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -11655,7 +11911,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -11743,7 +11999,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -11808,7 +12064,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W</t>
+          <t>1G-GGRQ-GQ-L001-F024-W</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -11831,7 +12087,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -11896,7 +12152,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W</t>
+          <t>1G-GGRQ-GQ-L002-F024-W</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -11919,7 +12175,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -11984,7 +12240,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W</t>
+          <t>1G-GGRQ-GQ-L003-F024-W</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12007,7 +12263,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -12072,7 +12328,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W</t>
+          <t>1G-GGRQ-GQ-L004-F024-W</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -12095,7 +12351,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -12160,7 +12416,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W</t>
+          <t>1G-GGRQ-GQ-L005-F024-W</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12183,7 +12439,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -12248,7 +12504,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W</t>
+          <t>1G-GGRQ-GQ-L006-F024-W</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -12271,7 +12527,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -12336,7 +12592,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W</t>
+          <t>1G-GGRQ-GQ-L007-F024-W</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12359,7 +12615,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -12424,7 +12680,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W</t>
+          <t>1G-GGRQ-GQ-L008-F024-W</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -12447,7 +12703,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -12512,7 +12768,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W</t>
+          <t>1G-GGRQ-GQ-L009-F024-W</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12535,7 +12791,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -12600,7 +12856,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W</t>
+          <t>1G-GGRQ-GQ-L010-F024-W</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -12623,7 +12879,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -12688,7 +12944,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W</t>
+          <t>1G-GGRQ-GQ-L011-F024-W</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -12711,7 +12967,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -12776,7 +13032,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W</t>
+          <t>1G-GGRQ-GQ-L012-F024-W</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -12799,7 +13055,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -12864,7 +13120,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W</t>
+          <t>1G-GGRQ-GQ-L013-F024-W</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -12887,7 +13143,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -12952,7 +13208,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W</t>
+          <t>1G-GGRQ-GQ-L014-F024-W</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -12975,7 +13231,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -13040,7 +13296,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W</t>
+          <t>1G-GGRQ-GQ-L015-F024-W</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -13063,7 +13319,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -13128,7 +13384,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W</t>
+          <t>1G-GGRQ-GQ-L016-F024-W</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -13151,7 +13407,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -13216,7 +13472,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W</t>
+          <t>1G-GGRQ-GQ-L017-F024-W</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -13239,7 +13495,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -13304,7 +13560,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W</t>
+          <t>1G-GGRQ-GQ-L018-F024-W</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -13327,7 +13583,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -13392,7 +13648,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W</t>
+          <t>1G-GGRQ-GQ-L019-F024-W</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13415,7 +13671,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -13480,7 +13736,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W</t>
+          <t>1G-GGRQ-GQ-L020-F024-W</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -13503,7 +13759,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -13568,7 +13824,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W</t>
+          <t>1G-GGRQ-GQ-L021-F024-W</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13591,7 +13847,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -13656,7 +13912,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W</t>
+          <t>1G-GGRQ-GQ-L022-F024-W</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -13679,7 +13935,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -13744,7 +14000,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W</t>
+          <t>1G-GGRQ-GQ-L023-F024-W</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -13767,7 +14023,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -13832,7 +14088,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W</t>
+          <t>1G-GGRQ-GQ-L024-F024-W</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -13855,7 +14111,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -13920,7 +14176,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W</t>
+          <t>1G-GGRQ-GQ-L025-F024-W</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -13943,7 +14199,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -14008,7 +14264,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W</t>
+          <t>1G-GGRQ-GQ-L026-F024-W</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -14031,7 +14287,7 @@
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -14096,7 +14352,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W</t>
+          <t>1G-GGRQ-GQ-L027-F024-W</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -14119,7 +14375,7 @@
       <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -14184,7 +14440,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W</t>
+          <t>1G-GGRQ-GQ-L028-F024-W</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -14207,7 +14463,7 @@
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -14272,7 +14528,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W</t>
+          <t>1G-GGRQ-GQ-L029-F024-W</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -14295,7 +14551,7 @@
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -14360,7 +14616,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W</t>
+          <t>1G-GGRQ-GQ-L030-F024-W</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -14383,7 +14639,7 @@
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -14448,7 +14704,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W</t>
+          <t>1G-GGRQ-GQ-L031-F024-W</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -14471,7 +14727,7 @@
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -14536,7 +14792,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W</t>
+          <t>1G-GGRQ-GQ-L032-F024-W</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -14559,7 +14815,7 @@
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -14639,7 +14895,7 @@
       <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -14723,7 +14979,7 @@
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -14807,7 +15063,7 @@
       <c r="J163" s="4" t="inlineStr"/>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -14891,7 +15147,7 @@
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -14975,7 +15231,7 @@
       <c r="J165" s="4" t="inlineStr"/>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -15059,7 +15315,7 @@
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -15143,7 +15399,7 @@
       <c r="J167" s="4" t="inlineStr"/>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -15227,7 +15483,7 @@
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -15311,7 +15567,7 @@
       <c r="J169" s="4" t="inlineStr"/>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -15395,7 +15651,7 @@
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -15479,7 +15735,7 @@
       <c r="J171" s="4" t="inlineStr"/>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -15563,7 +15819,7 @@
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -15647,7 +15903,7 @@
       <c r="J173" s="4" t="inlineStr"/>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -15731,7 +15987,7 @@
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -15815,7 +16071,7 @@
       <c r="J175" s="4" t="inlineStr"/>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -15899,7 +16155,7 @@
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -15983,7 +16239,7 @@
       <c r="J177" s="4" t="inlineStr"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -16067,7 +16323,7 @@
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -16151,7 +16407,7 @@
       <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -16235,7 +16491,7 @@
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -16319,7 +16575,7 @@
       <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -16403,7 +16659,7 @@
       <c r="J182" s="2" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
@@ -16487,7 +16743,7 @@
       <c r="J183" s="4" t="inlineStr"/>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L183" s="4" t="inlineStr">
@@ -16571,7 +16827,7 @@
       <c r="J184" s="2" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
@@ -16655,7 +16911,7 @@
       <c r="J185" s="4" t="inlineStr"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L185" s="4" t="inlineStr">
@@ -16739,7 +16995,7 @@
       <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
@@ -16823,7 +17079,7 @@
       <c r="J187" s="4" t="inlineStr"/>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L187" s="4" t="inlineStr">
@@ -16907,7 +17163,7 @@
       <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
@@ -16991,7 +17247,7 @@
       <c r="J189" s="4" t="inlineStr"/>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L189" s="4" t="inlineStr">
@@ -17075,7 +17331,7 @@
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -17159,7 +17415,7 @@
       <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L191" s="4" t="inlineStr">
@@ -17243,7 +17499,7 @@
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
@@ -17327,7 +17583,7 @@
       <c r="J193" s="4" t="inlineStr"/>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L193" s="4" t="inlineStr">
@@ -17411,7 +17667,7 @@
       <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -17495,7 +17751,7 @@
       <c r="J195" s="4" t="inlineStr"/>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L195" s="4" t="inlineStr">
@@ -17579,7 +17835,7 @@
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -17663,7 +17919,7 @@
       <c r="J197" s="4" t="inlineStr"/>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L197" s="4" t="inlineStr">
@@ -17747,7 +18003,7 @@
       <c r="J198" s="2" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
@@ -17831,7 +18087,7 @@
       <c r="J199" s="4" t="inlineStr"/>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L199" s="4" t="inlineStr">
@@ -17915,7 +18171,7 @@
       <c r="J200" s="2" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -17999,7 +18255,7 @@
       <c r="J201" s="4" t="inlineStr"/>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L201" s="4" t="inlineStr">
@@ -18083,7 +18339,7 @@
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
@@ -18167,7 +18423,7 @@
       <c r="J203" s="4" t="inlineStr"/>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L203" s="4" t="inlineStr">
@@ -18251,7 +18507,7 @@
       <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -18335,7 +18591,7 @@
       <c r="J205" s="4" t="inlineStr"/>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
@@ -18419,7 +18675,7 @@
       <c r="J206" s="2" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -18503,7 +18759,7 @@
       <c r="J207" s="4" t="inlineStr"/>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L207" s="4" t="inlineStr">
@@ -18587,7 +18843,7 @@
       <c r="J208" s="2" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
@@ -18671,7 +18927,7 @@
       <c r="J209" s="4" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L209" s="4" t="inlineStr">
@@ -18755,7 +19011,7 @@
       <c r="J210" s="2" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L210" s="2" t="inlineStr">
@@ -18839,7 +19095,7 @@
       <c r="J211" s="4" t="inlineStr"/>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L211" s="4" t="inlineStr">
@@ -18923,7 +19179,7 @@
       <c r="J212" s="2" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -19007,7 +19263,7 @@
       <c r="J213" s="4" t="inlineStr"/>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L213" s="4" t="inlineStr">
@@ -19091,7 +19347,7 @@
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -19175,7 +19431,7 @@
       <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L215" s="4" t="inlineStr">
@@ -19259,7 +19515,7 @@
       <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -19343,7 +19599,7 @@
       <c r="J217" s="4" t="inlineStr"/>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L217" s="4" t="inlineStr">
@@ -19427,7 +19683,7 @@
       <c r="J218" s="2" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -19511,7 +19767,7 @@
       <c r="J219" s="4" t="inlineStr"/>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L219" s="4" t="inlineStr">
@@ -19595,7 +19851,7 @@
       <c r="J220" s="2" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
@@ -19679,7 +19935,7 @@
       <c r="J221" s="4" t="inlineStr"/>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L221" s="4" t="inlineStr">
@@ -19763,7 +20019,7 @@
       <c r="J222" s="2" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L222" s="2" t="inlineStr">
@@ -19847,7 +20103,7 @@
       <c r="J223" s="4" t="inlineStr"/>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L223" s="4" t="inlineStr">
@@ -19931,7 +20187,7 @@
       <c r="J224" s="2" t="inlineStr"/>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L224" s="2" t="inlineStr">
@@ -20015,7 +20271,7 @@
       <c r="J225" s="4" t="inlineStr"/>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L225" s="4" t="inlineStr">
@@ -20099,7 +20355,7 @@
       <c r="J226" s="2" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
@@ -20183,7 +20439,7 @@
       <c r="J227" s="4" t="inlineStr"/>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L227" s="4" t="inlineStr">
@@ -20267,7 +20523,7 @@
       <c r="J228" s="2" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L228" s="2" t="inlineStr">
@@ -20351,7 +20607,7 @@
       <c r="J229" s="4" t="inlineStr"/>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L229" s="4" t="inlineStr">
@@ -20435,7 +20691,7 @@
       <c r="J230" s="2" t="inlineStr"/>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L230" s="2" t="inlineStr">
@@ -20519,7 +20775,7 @@
       <c r="J231" s="4" t="inlineStr"/>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L231" s="4" t="inlineStr">
@@ -20603,7 +20859,7 @@
       <c r="J232" s="2" t="inlineStr"/>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L232" s="2" t="inlineStr">
@@ -20687,7 +20943,7 @@
       <c r="J233" s="4" t="inlineStr"/>
       <c r="K233" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L233" s="4" t="inlineStr">
@@ -20771,7 +21027,7 @@
       <c r="J234" s="2" t="inlineStr"/>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L234" s="2" t="inlineStr">
@@ -20855,7 +21111,7 @@
       <c r="J235" s="4" t="inlineStr"/>
       <c r="K235" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L235" s="4" t="inlineStr">
@@ -20939,7 +21195,7 @@
       <c r="J236" s="2" t="inlineStr"/>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L236" s="2" t="inlineStr">
@@ -21023,7 +21279,7 @@
       <c r="J237" s="4" t="inlineStr"/>
       <c r="K237" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L237" s="4" t="inlineStr">
@@ -21107,7 +21363,7 @@
       <c r="J238" s="2" t="inlineStr"/>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L238" s="2" t="inlineStr">
@@ -21191,7 +21447,7 @@
       <c r="J239" s="4" t="inlineStr"/>
       <c r="K239" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L239" s="4" t="inlineStr">
@@ -21275,7 +21531,7 @@
       <c r="J240" s="2" t="inlineStr"/>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L240" s="2" t="inlineStr">
@@ -21359,7 +21615,7 @@
       <c r="J241" s="4" t="inlineStr"/>
       <c r="K241" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L241" s="4" t="inlineStr">
@@ -21443,7 +21699,7 @@
       <c r="J242" s="2" t="inlineStr"/>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L242" s="2" t="inlineStr">
@@ -21527,7 +21783,7 @@
       <c r="J243" s="4" t="inlineStr"/>
       <c r="K243" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L243" s="4" t="inlineStr">
@@ -21611,7 +21867,7 @@
       <c r="J244" s="2" t="inlineStr"/>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
@@ -21695,7 +21951,7 @@
       <c r="J245" s="4" t="inlineStr"/>
       <c r="K245" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L245" s="4" t="inlineStr">
@@ -21779,7 +22035,7 @@
       <c r="J246" s="2" t="inlineStr"/>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
@@ -21863,7 +22119,7 @@
       <c r="J247" s="4" t="inlineStr"/>
       <c r="K247" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L247" s="4" t="inlineStr">
@@ -21947,7 +22203,7 @@
       <c r="J248" s="2" t="inlineStr"/>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L248" s="2" t="inlineStr">
@@ -22031,7 +22287,7 @@
       <c r="J249" s="4" t="inlineStr"/>
       <c r="K249" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L249" s="4" t="inlineStr">
@@ -22115,7 +22371,7 @@
       <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -22199,7 +22455,7 @@
       <c r="J251" s="4" t="inlineStr"/>
       <c r="K251" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L251" s="4" t="inlineStr">
@@ -22283,7 +22539,7 @@
       <c r="J252" s="2" t="inlineStr"/>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
@@ -22367,7 +22623,7 @@
       <c r="J253" s="4" t="inlineStr"/>
       <c r="K253" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L253" s="4" t="inlineStr">
@@ -22451,7 +22707,7 @@
       <c r="J254" s="2" t="inlineStr"/>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L254" s="2" t="inlineStr">
@@ -22535,7 +22791,7 @@
       <c r="J255" s="4" t="inlineStr"/>
       <c r="K255" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L255" s="4" t="inlineStr">
@@ -22619,7 +22875,7 @@
       <c r="J256" s="2" t="inlineStr"/>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L256" s="2" t="inlineStr">
@@ -22707,7 +22963,7 @@
       <c r="J257" s="4" t="inlineStr"/>
       <c r="K257" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L257" s="4" t="inlineStr">
@@ -22795,7 +23051,7 @@
       <c r="J258" s="2" t="inlineStr"/>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L258" s="2" t="inlineStr">
@@ -22883,7 +23139,7 @@
       <c r="J259" s="4" t="inlineStr"/>
       <c r="K259" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L259" s="4" t="inlineStr">
@@ -22971,7 +23227,7 @@
       <c r="J260" s="2" t="inlineStr"/>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
@@ -23059,7 +23315,7 @@
       <c r="J261" s="4" t="inlineStr"/>
       <c r="K261" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L261" s="4" t="inlineStr">
@@ -23147,7 +23403,7 @@
       <c r="J262" s="2" t="inlineStr"/>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
@@ -23235,7 +23491,7 @@
       <c r="J263" s="4" t="inlineStr"/>
       <c r="K263" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L263" s="4" t="inlineStr">
@@ -23323,7 +23579,7 @@
       <c r="J264" s="2" t="inlineStr"/>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L264" s="2" t="inlineStr">
@@ -23411,7 +23667,7 @@
       <c r="J265" s="4" t="inlineStr"/>
       <c r="K265" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L265" s="4" t="inlineStr">
@@ -23499,7 +23755,7 @@
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
@@ -23587,7 +23843,7 @@
       <c r="J267" s="4" t="inlineStr"/>
       <c r="K267" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L267" s="4" t="inlineStr">
@@ -23675,7 +23931,7 @@
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L268" s="2" t="inlineStr">
@@ -23763,7 +24019,7 @@
       <c r="J269" s="4" t="inlineStr"/>
       <c r="K269" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L269" s="4" t="inlineStr">
@@ -23851,7 +24107,7 @@
       <c r="J270" s="2" t="inlineStr"/>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L270" s="2" t="inlineStr">
@@ -23939,7 +24195,7 @@
       <c r="J271" s="4" t="inlineStr"/>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
@@ -24027,7 +24283,7 @@
       <c r="J272" s="2" t="inlineStr"/>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L272" s="2" t="inlineStr">
@@ -24115,7 +24371,7 @@
       <c r="J273" s="4" t="inlineStr"/>
       <c r="K273" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L273" s="4" t="inlineStr">
@@ -24203,7 +24459,7 @@
       <c r="J274" s="2" t="inlineStr"/>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L274" s="2" t="inlineStr">
@@ -24291,7 +24547,7 @@
       <c r="J275" s="4" t="inlineStr"/>
       <c r="K275" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L275" s="4" t="inlineStr">
@@ -24379,7 +24635,7 @@
       <c r="J276" s="2" t="inlineStr"/>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L276" s="2" t="inlineStr">
@@ -24467,7 +24723,7 @@
       <c r="J277" s="4" t="inlineStr"/>
       <c r="K277" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L277" s="4" t="inlineStr">
@@ -24555,7 +24811,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr">
@@ -24643,7 +24899,7 @@
       <c r="J279" s="4" t="inlineStr"/>
       <c r="K279" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L279" s="4" t="inlineStr">
@@ -24731,7 +24987,7 @@
       <c r="J280" s="2" t="inlineStr"/>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L280" s="2" t="inlineStr">
@@ -24819,7 +25075,7 @@
       <c r="J281" s="4" t="inlineStr"/>
       <c r="K281" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L281" s="4" t="inlineStr">
@@ -24907,7 +25163,7 @@
       <c r="J282" s="2" t="inlineStr"/>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L282" s="2" t="inlineStr">
@@ -24995,7 +25251,7 @@
       <c r="J283" s="4" t="inlineStr"/>
       <c r="K283" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L283" s="4" t="inlineStr">
@@ -25083,7 +25339,7 @@
       <c r="J284" s="2" t="inlineStr"/>
       <c r="K284" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L284" s="2" t="inlineStr">
@@ -25171,7 +25427,7 @@
       <c r="J285" s="4" t="inlineStr"/>
       <c r="K285" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L285" s="4" t="inlineStr">
@@ -25259,7 +25515,7 @@
       <c r="J286" s="2" t="inlineStr"/>
       <c r="K286" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L286" s="2" t="inlineStr">
@@ -25347,7 +25603,7 @@
       <c r="J287" s="4" t="inlineStr"/>
       <c r="K287" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L287" s="4" t="inlineStr">
@@ -25435,7 +25691,7 @@
       <c r="J288" s="2" t="inlineStr"/>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L288" s="2" t="inlineStr">
@@ -25523,7 +25779,7 @@
       <c r="J289" s="4" t="inlineStr"/>
       <c r="K289" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L289" s="4" t="inlineStr">
@@ -25611,7 +25867,7 @@
       <c r="J290" s="2" t="inlineStr"/>
       <c r="K290" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L290" s="2" t="inlineStr">
@@ -25699,7 +25955,7 @@
       <c r="J291" s="4" t="inlineStr"/>
       <c r="K291" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L291" s="4" t="inlineStr">
@@ -25787,7 +26043,7 @@
       <c r="J292" s="2" t="inlineStr"/>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L292" s="2" t="inlineStr">
@@ -25875,7 +26131,7 @@
       <c r="J293" s="4" t="inlineStr"/>
       <c r="K293" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L293" s="4" t="inlineStr">
@@ -25963,7 +26219,7 @@
       <c r="J294" s="2" t="inlineStr"/>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L294" s="2" t="inlineStr">
@@ -26051,7 +26307,7 @@
       <c r="J295" s="4" t="inlineStr"/>
       <c r="K295" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L295" s="4" t="inlineStr">
@@ -26139,7 +26395,7 @@
       <c r="J296" s="2" t="inlineStr"/>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L296" s="2" t="inlineStr">
@@ -26227,7 +26483,7 @@
       <c r="J297" s="4" t="inlineStr"/>
       <c r="K297" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L297" s="4" t="inlineStr">
@@ -26315,7 +26571,7 @@
       <c r="J298" s="2" t="inlineStr"/>
       <c r="K298" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L298" s="2" t="inlineStr">
@@ -26403,7 +26659,7 @@
       <c r="J299" s="4" t="inlineStr"/>
       <c r="K299" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L299" s="4" t="inlineStr">
@@ -26491,7 +26747,7 @@
       <c r="J300" s="2" t="inlineStr"/>
       <c r="K300" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L300" s="2" t="inlineStr">
@@ -26579,7 +26835,7 @@
       <c r="J301" s="4" t="inlineStr"/>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L301" s="4" t="inlineStr">
@@ -26667,7 +26923,7 @@
       <c r="J302" s="2" t="inlineStr"/>
       <c r="K302" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L302" s="2" t="inlineStr">
@@ -26755,7 +27011,7 @@
       <c r="J303" s="4" t="inlineStr"/>
       <c r="K303" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L303" s="4" t="inlineStr">
@@ -26843,7 +27099,7 @@
       <c r="J304" s="2" t="inlineStr"/>
       <c r="K304" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L304" s="2" t="inlineStr">
@@ -26931,7 +27187,7 @@
       <c r="J305" s="4" t="inlineStr"/>
       <c r="K305" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L305" s="4" t="inlineStr">
@@ -27019,7 +27275,7 @@
       <c r="J306" s="2" t="inlineStr"/>
       <c r="K306" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L306" s="2" t="inlineStr">
@@ -27107,7 +27363,7 @@
       <c r="J307" s="4" t="inlineStr"/>
       <c r="K307" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L307" s="4" t="inlineStr">
@@ -27195,7 +27451,7 @@
       <c r="J308" s="2" t="inlineStr"/>
       <c r="K308" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L308" s="2" t="inlineStr">
@@ -27283,7 +27539,7 @@
       <c r="J309" s="4" t="inlineStr"/>
       <c r="K309" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L309" s="4" t="inlineStr">
@@ -27371,7 +27627,7 @@
       <c r="J310" s="2" t="inlineStr"/>
       <c r="K310" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L310" s="2" t="inlineStr">
@@ -27459,7 +27715,7 @@
       <c r="J311" s="4" t="inlineStr"/>
       <c r="K311" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L311" s="4" t="inlineStr">
@@ -27547,7 +27803,7 @@
       <c r="J312" s="2" t="inlineStr"/>
       <c r="K312" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2022年1号机A修；日期精度=年，月日未提供；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L312" s="2" t="inlineStr">
@@ -27631,7 +27887,7 @@
       <c r="J313" s="4" t="inlineStr"/>
       <c r="K313" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L313" s="4" t="inlineStr">
@@ -27715,7 +27971,7 @@
       <c r="J314" s="2" t="inlineStr"/>
       <c r="K314" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L314" s="2" t="inlineStr">
@@ -27799,7 +28055,7 @@
       <c r="J315" s="4" t="inlineStr"/>
       <c r="K315" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L315" s="4" t="inlineStr">
@@ -27883,7 +28139,7 @@
       <c r="J316" s="2" t="inlineStr"/>
       <c r="K316" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L316" s="2" t="inlineStr">
@@ -27967,7 +28223,7 @@
       <c r="J317" s="4" t="inlineStr"/>
       <c r="K317" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L317" s="4" t="inlineStr">
@@ -28051,7 +28307,7 @@
       <c r="J318" s="2" t="inlineStr"/>
       <c r="K318" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L318" s="2" t="inlineStr">
@@ -28135,7 +28391,7 @@
       <c r="J319" s="4" t="inlineStr"/>
       <c r="K319" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L319" s="4" t="inlineStr">
@@ -28219,7 +28475,7 @@
       <c r="J320" s="2" t="inlineStr"/>
       <c r="K320" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L320" s="2" t="inlineStr">
@@ -28303,7 +28559,7 @@
       <c r="J321" s="4" t="inlineStr"/>
       <c r="K321" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L321" s="4" t="inlineStr">
@@ -28387,7 +28643,7 @@
       <c r="J322" s="2" t="inlineStr"/>
       <c r="K322" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L322" s="2" t="inlineStr">
@@ -28471,7 +28727,7 @@
       <c r="J323" s="4" t="inlineStr"/>
       <c r="K323" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L323" s="4" t="inlineStr">
@@ -28555,7 +28811,7 @@
       <c r="J324" s="2" t="inlineStr"/>
       <c r="K324" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L324" s="2" t="inlineStr">
@@ -28639,7 +28895,7 @@
       <c r="J325" s="4" t="inlineStr"/>
       <c r="K325" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L325" s="4" t="inlineStr">
@@ -28723,7 +28979,7 @@
       <c r="J326" s="2" t="inlineStr"/>
       <c r="K326" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L326" s="2" t="inlineStr">
@@ -28807,7 +29063,7 @@
       <c r="J327" s="4" t="inlineStr"/>
       <c r="K327" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L327" s="4" t="inlineStr">
@@ -28891,7 +29147,7 @@
       <c r="J328" s="2" t="inlineStr"/>
       <c r="K328" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L328" s="2" t="inlineStr">
@@ -28975,7 +29231,7 @@
       <c r="J329" s="4" t="inlineStr"/>
       <c r="K329" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L329" s="4" t="inlineStr">
@@ -29059,7 +29315,7 @@
       <c r="J330" s="2" t="inlineStr"/>
       <c r="K330" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L330" s="2" t="inlineStr">
@@ -29143,7 +29399,7 @@
       <c r="J331" s="4" t="inlineStr"/>
       <c r="K331" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L331" s="4" t="inlineStr">
@@ -29227,7 +29483,7 @@
       <c r="J332" s="2" t="inlineStr"/>
       <c r="K332" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L332" s="2" t="inlineStr">
@@ -29311,7 +29567,7 @@
       <c r="J333" s="4" t="inlineStr"/>
       <c r="K333" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L333" s="4" t="inlineStr">
@@ -29395,7 +29651,7 @@
       <c r="J334" s="2" t="inlineStr"/>
       <c r="K334" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L334" s="2" t="inlineStr">
@@ -29479,7 +29735,7 @@
       <c r="J335" s="4" t="inlineStr"/>
       <c r="K335" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L335" s="4" t="inlineStr">
@@ -29563,7 +29819,7 @@
       <c r="J336" s="2" t="inlineStr"/>
       <c r="K336" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L336" s="2" t="inlineStr">
@@ -29647,7 +29903,7 @@
       <c r="J337" s="4" t="inlineStr"/>
       <c r="K337" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L337" s="4" t="inlineStr">
@@ -29731,7 +29987,7 @@
       <c r="J338" s="2" t="inlineStr"/>
       <c r="K338" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L338" s="2" t="inlineStr">
@@ -29815,7 +30071,7 @@
       <c r="J339" s="4" t="inlineStr"/>
       <c r="K339" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L339" s="4" t="inlineStr">
@@ -29899,7 +30155,7 @@
       <c r="J340" s="2" t="inlineStr"/>
       <c r="K340" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L340" s="2" t="inlineStr">
@@ -29983,7 +30239,7 @@
       <c r="J341" s="4" t="inlineStr"/>
       <c r="K341" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L341" s="4" t="inlineStr">
@@ -30067,7 +30323,7 @@
       <c r="J342" s="2" t="inlineStr"/>
       <c r="K342" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L342" s="2" t="inlineStr">
@@ -30151,7 +30407,7 @@
       <c r="J343" s="4" t="inlineStr"/>
       <c r="K343" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L343" s="4" t="inlineStr">
@@ -30235,7 +30491,7 @@
       <c r="J344" s="2" t="inlineStr"/>
       <c r="K344" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L344" s="2" t="inlineStr">
@@ -30319,7 +30575,7 @@
       <c r="J345" s="4" t="inlineStr"/>
       <c r="K345" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L345" s="4" t="inlineStr">
@@ -30403,7 +30659,7 @@
       <c r="J346" s="2" t="inlineStr"/>
       <c r="K346" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L346" s="2" t="inlineStr">
@@ -30487,7 +30743,7 @@
       <c r="J347" s="4" t="inlineStr"/>
       <c r="K347" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L347" s="4" t="inlineStr">
@@ -30571,7 +30827,7 @@
       <c r="J348" s="2" t="inlineStr"/>
       <c r="K348" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L348" s="2" t="inlineStr">
@@ -30655,7 +30911,7 @@
       <c r="J349" s="4" t="inlineStr"/>
       <c r="K349" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L349" s="4" t="inlineStr">
@@ -30739,7 +30995,7 @@
       <c r="J350" s="2" t="inlineStr"/>
       <c r="K350" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L350" s="2" t="inlineStr">
@@ -30823,7 +31079,7 @@
       <c r="J351" s="4" t="inlineStr"/>
       <c r="K351" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L351" s="4" t="inlineStr">
@@ -30907,7 +31163,7 @@
       <c r="J352" s="2" t="inlineStr"/>
       <c r="K352" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L352" s="2" t="inlineStr">
@@ -30991,7 +31247,7 @@
       <c r="J353" s="4" t="inlineStr"/>
       <c r="K353" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L353" s="4" t="inlineStr">
@@ -31075,7 +31331,7 @@
       <c r="J354" s="2" t="inlineStr"/>
       <c r="K354" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L354" s="2" t="inlineStr">
@@ -31159,7 +31415,7 @@
       <c r="J355" s="4" t="inlineStr"/>
       <c r="K355" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L355" s="4" t="inlineStr">
@@ -31243,7 +31499,7 @@
       <c r="J356" s="2" t="inlineStr"/>
       <c r="K356" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L356" s="2" t="inlineStr">
@@ -31327,7 +31583,7 @@
       <c r="J357" s="4" t="inlineStr"/>
       <c r="K357" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L357" s="4" t="inlineStr">
@@ -31411,7 +31667,7 @@
       <c r="J358" s="2" t="inlineStr"/>
       <c r="K358" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L358" s="2" t="inlineStr">
@@ -31495,7 +31751,7 @@
       <c r="J359" s="4" t="inlineStr"/>
       <c r="K359" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L359" s="4" t="inlineStr">
@@ -31579,7 +31835,7 @@
       <c r="J360" s="2" t="inlineStr"/>
       <c r="K360" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L360" s="2" t="inlineStr">
@@ -31663,7 +31919,7 @@
       <c r="J361" s="4" t="inlineStr"/>
       <c r="K361" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L361" s="4" t="inlineStr">
@@ -31747,7 +32003,7 @@
       <c r="J362" s="2" t="inlineStr"/>
       <c r="K362" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L362" s="2" t="inlineStr">
@@ -31831,7 +32087,7 @@
       <c r="J363" s="4" t="inlineStr"/>
       <c r="K363" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L363" s="4" t="inlineStr">
@@ -31915,7 +32171,7 @@
       <c r="J364" s="2" t="inlineStr"/>
       <c r="K364" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L364" s="2" t="inlineStr">
@@ -31999,7 +32255,7 @@
       <c r="J365" s="4" t="inlineStr"/>
       <c r="K365" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L365" s="4" t="inlineStr">
@@ -32083,7 +32339,7 @@
       <c r="J366" s="2" t="inlineStr"/>
       <c r="K366" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L366" s="2" t="inlineStr">
@@ -32167,7 +32423,7 @@
       <c r="J367" s="4" t="inlineStr"/>
       <c r="K367" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L367" s="4" t="inlineStr">
@@ -32251,7 +32507,7 @@
       <c r="J368" s="2" t="inlineStr"/>
       <c r="K368" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L368" s="2" t="inlineStr">
@@ -32335,7 +32591,7 @@
       <c r="J369" s="4" t="inlineStr"/>
       <c r="K369" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L369" s="4" t="inlineStr">
@@ -32419,7 +32675,7 @@
       <c r="J370" s="2" t="inlineStr"/>
       <c r="K370" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L370" s="2" t="inlineStr">
@@ -32503,7 +32759,7 @@
       <c r="J371" s="4" t="inlineStr"/>
       <c r="K371" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L371" s="4" t="inlineStr">
@@ -32587,7 +32843,7 @@
       <c r="J372" s="2" t="inlineStr"/>
       <c r="K372" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L372" s="2" t="inlineStr">
@@ -32671,7 +32927,7 @@
       <c r="J373" s="4" t="inlineStr"/>
       <c r="K373" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L373" s="4" t="inlineStr">
@@ -32755,7 +33011,7 @@
       <c r="J374" s="2" t="inlineStr"/>
       <c r="K374" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L374" s="2" t="inlineStr">
@@ -32839,7 +33095,7 @@
       <c r="J375" s="4" t="inlineStr"/>
       <c r="K375" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L375" s="4" t="inlineStr">
@@ -32923,7 +33179,7 @@
       <c r="J376" s="2" t="inlineStr"/>
       <c r="K376" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L376" s="2" t="inlineStr">
@@ -33007,7 +33263,7 @@
       <c r="J377" s="4" t="inlineStr"/>
       <c r="K377" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L377" s="4" t="inlineStr">
@@ -33091,7 +33347,7 @@
       <c r="J378" s="2" t="inlineStr"/>
       <c r="K378" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L378" s="2" t="inlineStr">
@@ -33175,7 +33431,7 @@
       <c r="J379" s="4" t="inlineStr"/>
       <c r="K379" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L379" s="4" t="inlineStr">
@@ -33259,7 +33515,7 @@
       <c r="J380" s="2" t="inlineStr"/>
       <c r="K380" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L380" s="2" t="inlineStr">
@@ -33343,7 +33599,7 @@
       <c r="J381" s="4" t="inlineStr"/>
       <c r="K381" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L381" s="4" t="inlineStr">
@@ -33427,7 +33683,7 @@
       <c r="J382" s="2" t="inlineStr"/>
       <c r="K382" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L382" s="2" t="inlineStr">
@@ -33511,7 +33767,7 @@
       <c r="J383" s="4" t="inlineStr"/>
       <c r="K383" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L383" s="4" t="inlineStr">
@@ -33595,7 +33851,7 @@
       <c r="J384" s="2" t="inlineStr"/>
       <c r="K384" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L384" s="2" t="inlineStr">
@@ -33679,7 +33935,7 @@
       <c r="J385" s="4" t="inlineStr"/>
       <c r="K385" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L385" s="4" t="inlineStr">
@@ -33763,7 +34019,7 @@
       <c r="J386" s="2" t="inlineStr"/>
       <c r="K386" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L386" s="2" t="inlineStr">
@@ -33847,7 +34103,7 @@
       <c r="J387" s="4" t="inlineStr"/>
       <c r="K387" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L387" s="4" t="inlineStr">
@@ -33931,7 +34187,7 @@
       <c r="J388" s="2" t="inlineStr"/>
       <c r="K388" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L388" s="2" t="inlineStr">
@@ -34015,7 +34271,7 @@
       <c r="J389" s="4" t="inlineStr"/>
       <c r="K389" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L389" s="4" t="inlineStr">
@@ -34099,7 +34355,7 @@
       <c r="J390" s="2" t="inlineStr"/>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L390" s="2" t="inlineStr">
@@ -34183,7 +34439,7 @@
       <c r="J391" s="4" t="inlineStr"/>
       <c r="K391" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L391" s="4" t="inlineStr">
@@ -34267,7 +34523,7 @@
       <c r="J392" s="2" t="inlineStr"/>
       <c r="K392" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L392" s="2" t="inlineStr">
@@ -34351,7 +34607,7 @@
       <c r="J393" s="4" t="inlineStr"/>
       <c r="K393" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L393" s="4" t="inlineStr">
@@ -34435,7 +34691,7 @@
       <c r="J394" s="2" t="inlineStr"/>
       <c r="K394" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L394" s="2" t="inlineStr">
@@ -34519,7 +34775,7 @@
       <c r="J395" s="4" t="inlineStr"/>
       <c r="K395" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L395" s="4" t="inlineStr">
@@ -34603,7 +34859,7 @@
       <c r="J396" s="2" t="inlineStr"/>
       <c r="K396" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L396" s="2" t="inlineStr">
@@ -34687,7 +34943,7 @@
       <c r="J397" s="4" t="inlineStr"/>
       <c r="K397" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L397" s="4" t="inlineStr">
@@ -34771,7 +35027,7 @@
       <c r="J398" s="2" t="inlineStr"/>
       <c r="K398" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L398" s="2" t="inlineStr">
@@ -34855,7 +35111,7 @@
       <c r="J399" s="4" t="inlineStr"/>
       <c r="K399" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L399" s="4" t="inlineStr">
@@ -34939,7 +35195,7 @@
       <c r="J400" s="2" t="inlineStr"/>
       <c r="K400" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L400" s="2" t="inlineStr">
@@ -35023,7 +35279,7 @@
       <c r="J401" s="4" t="inlineStr"/>
       <c r="K401" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L401" s="4" t="inlineStr">
@@ -35107,7 +35363,7 @@
       <c r="J402" s="2" t="inlineStr"/>
       <c r="K402" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L402" s="2" t="inlineStr">
@@ -35191,7 +35447,7 @@
       <c r="J403" s="4" t="inlineStr"/>
       <c r="K403" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L403" s="4" t="inlineStr">
@@ -35275,7 +35531,7 @@
       <c r="J404" s="2" t="inlineStr"/>
       <c r="K404" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L404" s="2" t="inlineStr">
@@ -35359,7 +35615,7 @@
       <c r="J405" s="4" t="inlineStr"/>
       <c r="K405" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L405" s="4" t="inlineStr">
@@ -35443,7 +35699,7 @@
       <c r="J406" s="2" t="inlineStr"/>
       <c r="K406" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L406" s="2" t="inlineStr">
@@ -35527,7 +35783,7 @@
       <c r="J407" s="4" t="inlineStr"/>
       <c r="K407" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L407" s="4" t="inlineStr">
@@ -35611,7 +35867,7 @@
       <c r="J408" s="2" t="inlineStr"/>
       <c r="K408" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L408" s="2" t="inlineStr">
@@ -35699,7 +35955,7 @@
       <c r="J409" s="4" t="inlineStr"/>
       <c r="K409" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L409" s="4" t="inlineStr">
@@ -35787,7 +36043,7 @@
       <c r="J410" s="2" t="inlineStr"/>
       <c r="K410" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L410" s="2" t="inlineStr">
@@ -35875,7 +36131,7 @@
       <c r="J411" s="4" t="inlineStr"/>
       <c r="K411" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L411" s="4" t="inlineStr">
@@ -35963,7 +36219,7 @@
       <c r="J412" s="2" t="inlineStr"/>
       <c r="K412" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L412" s="2" t="inlineStr">
@@ -36051,7 +36307,7 @@
       <c r="J413" s="4" t="inlineStr"/>
       <c r="K413" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L413" s="4" t="inlineStr">
@@ -36139,7 +36395,7 @@
       <c r="J414" s="2" t="inlineStr"/>
       <c r="K414" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L414" s="2" t="inlineStr">
@@ -36227,7 +36483,7 @@
       <c r="J415" s="4" t="inlineStr"/>
       <c r="K415" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L415" s="4" t="inlineStr">
@@ -36315,7 +36571,7 @@
       <c r="J416" s="2" t="inlineStr"/>
       <c r="K416" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L416" s="2" t="inlineStr">
@@ -36403,7 +36659,7 @@
       <c r="J417" s="4" t="inlineStr"/>
       <c r="K417" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L417" s="4" t="inlineStr">
@@ -36491,7 +36747,7 @@
       <c r="J418" s="2" t="inlineStr"/>
       <c r="K418" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L418" s="2" t="inlineStr">
@@ -36579,7 +36835,7 @@
       <c r="J419" s="4" t="inlineStr"/>
       <c r="K419" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L419" s="4" t="inlineStr">
@@ -36667,7 +36923,7 @@
       <c r="J420" s="2" t="inlineStr"/>
       <c r="K420" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L420" s="2" t="inlineStr">
@@ -36755,7 +37011,7 @@
       <c r="J421" s="4" t="inlineStr"/>
       <c r="K421" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L421" s="4" t="inlineStr">
@@ -36843,7 +37099,7 @@
       <c r="J422" s="2" t="inlineStr"/>
       <c r="K422" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L422" s="2" t="inlineStr">
@@ -36931,7 +37187,7 @@
       <c r="J423" s="4" t="inlineStr"/>
       <c r="K423" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L423" s="4" t="inlineStr">
@@ -37019,7 +37275,7 @@
       <c r="J424" s="2" t="inlineStr"/>
       <c r="K424" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L424" s="2" t="inlineStr">
@@ -37107,7 +37363,7 @@
       <c r="J425" s="4" t="inlineStr"/>
       <c r="K425" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L425" s="4" t="inlineStr">
@@ -37195,7 +37451,7 @@
       <c r="J426" s="2" t="inlineStr"/>
       <c r="K426" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L426" s="2" t="inlineStr">
@@ -37283,7 +37539,7 @@
       <c r="J427" s="4" t="inlineStr"/>
       <c r="K427" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L427" s="4" t="inlineStr">
@@ -37371,7 +37627,7 @@
       <c r="J428" s="2" t="inlineStr"/>
       <c r="K428" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L428" s="2" t="inlineStr">
@@ -37459,7 +37715,7 @@
       <c r="J429" s="4" t="inlineStr"/>
       <c r="K429" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L429" s="4" t="inlineStr">
@@ -37547,7 +37803,7 @@
       <c r="J430" s="2" t="inlineStr"/>
       <c r="K430" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L430" s="2" t="inlineStr">
@@ -37635,7 +37891,7 @@
       <c r="J431" s="4" t="inlineStr"/>
       <c r="K431" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L431" s="4" t="inlineStr">
@@ -37723,7 +37979,7 @@
       <c r="J432" s="2" t="inlineStr"/>
       <c r="K432" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L432" s="2" t="inlineStr">
@@ -37811,7 +38067,7 @@
       <c r="J433" s="4" t="inlineStr"/>
       <c r="K433" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L433" s="4" t="inlineStr">
@@ -37899,7 +38155,7 @@
       <c r="J434" s="2" t="inlineStr"/>
       <c r="K434" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L434" s="2" t="inlineStr">
@@ -37987,7 +38243,7 @@
       <c r="J435" s="4" t="inlineStr"/>
       <c r="K435" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L435" s="4" t="inlineStr">
@@ -38075,7 +38331,7 @@
       <c r="J436" s="2" t="inlineStr"/>
       <c r="K436" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L436" s="2" t="inlineStr">
@@ -38163,7 +38419,7 @@
       <c r="J437" s="4" t="inlineStr"/>
       <c r="K437" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L437" s="4" t="inlineStr">
@@ -38251,7 +38507,7 @@
       <c r="J438" s="2" t="inlineStr"/>
       <c r="K438" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L438" s="2" t="inlineStr">
@@ -38339,7 +38595,7 @@
       <c r="J439" s="4" t="inlineStr"/>
       <c r="K439" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L439" s="4" t="inlineStr">
@@ -38427,7 +38683,7 @@
       <c r="J440" s="2" t="inlineStr"/>
       <c r="K440" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L440" s="2" t="inlineStr">
@@ -38515,7 +38771,7 @@
       <c r="J441" s="4" t="inlineStr"/>
       <c r="K441" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L441" s="4" t="inlineStr">
@@ -38603,7 +38859,7 @@
       <c r="J442" s="2" t="inlineStr"/>
       <c r="K442" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L442" s="2" t="inlineStr">
@@ -38691,7 +38947,7 @@
       <c r="J443" s="4" t="inlineStr"/>
       <c r="K443" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L443" s="4" t="inlineStr">
@@ -38779,7 +39035,7 @@
       <c r="J444" s="2" t="inlineStr"/>
       <c r="K444" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L444" s="2" t="inlineStr">
@@ -38867,7 +39123,7 @@
       <c r="J445" s="4" t="inlineStr"/>
       <c r="K445" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L445" s="4" t="inlineStr">
@@ -38955,7 +39211,7 @@
       <c r="J446" s="2" t="inlineStr"/>
       <c r="K446" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L446" s="2" t="inlineStr">
@@ -39043,7 +39299,7 @@
       <c r="J447" s="4" t="inlineStr"/>
       <c r="K447" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L447" s="4" t="inlineStr">
@@ -39131,7 +39387,7 @@
       <c r="J448" s="2" t="inlineStr"/>
       <c r="K448" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L448" s="2" t="inlineStr">
@@ -39219,7 +39475,7 @@
       <c r="J449" s="4" t="inlineStr"/>
       <c r="K449" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L449" s="4" t="inlineStr">
@@ -39307,7 +39563,7 @@
       <c r="J450" s="2" t="inlineStr"/>
       <c r="K450" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L450" s="2" t="inlineStr">
@@ -39395,7 +39651,7 @@
       <c r="J451" s="4" t="inlineStr"/>
       <c r="K451" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L451" s="4" t="inlineStr">
@@ -39483,7 +39739,7 @@
       <c r="J452" s="2" t="inlineStr"/>
       <c r="K452" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L452" s="2" t="inlineStr">
@@ -39571,7 +39827,7 @@
       <c r="J453" s="4" t="inlineStr"/>
       <c r="K453" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L453" s="4" t="inlineStr">
@@ -39659,7 +39915,7 @@
       <c r="J454" s="2" t="inlineStr"/>
       <c r="K454" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L454" s="2" t="inlineStr">
@@ -39747,7 +40003,7 @@
       <c r="J455" s="4" t="inlineStr"/>
       <c r="K455" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L455" s="4" t="inlineStr">
@@ -39835,7 +40091,7 @@
       <c r="J456" s="2" t="inlineStr"/>
       <c r="K456" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L456" s="2" t="inlineStr">
@@ -39923,7 +40179,7 @@
       <c r="J457" s="4" t="inlineStr"/>
       <c r="K457" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L457" s="4" t="inlineStr">
@@ -40011,7 +40267,7 @@
       <c r="J458" s="2" t="inlineStr"/>
       <c r="K458" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L458" s="2" t="inlineStr">
@@ -40099,7 +40355,7 @@
       <c r="J459" s="4" t="inlineStr"/>
       <c r="K459" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L459" s="4" t="inlineStr">
@@ -40187,7 +40443,7 @@
       <c r="J460" s="2" t="inlineStr"/>
       <c r="K460" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L460" s="2" t="inlineStr">
@@ -40275,7 +40531,7 @@
       <c r="J461" s="4" t="inlineStr"/>
       <c r="K461" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L461" s="4" t="inlineStr">
@@ -40363,7 +40619,7 @@
       <c r="J462" s="2" t="inlineStr"/>
       <c r="K462" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L462" s="2" t="inlineStr">
@@ -40451,7 +40707,7 @@
       <c r="J463" s="4" t="inlineStr"/>
       <c r="K463" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L463" s="4" t="inlineStr">
@@ -40539,7 +40795,7 @@
       <c r="J464" s="2" t="inlineStr"/>
       <c r="K464" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2021年2号机A修；日期精度=年，月日未提供；来源ID：2021年2号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP304H / T91 / 12CrMoVG；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；备注弯头区带与24根几何的对应仅2026高过已确认；本行材质不按清单流水推断</t>
         </is>
       </c>
       <c r="L464" s="2" t="inlineStr">

--- a/data-cleaning/verified/导入_全部批次.xlsx
+++ b/data-cleaning/verified/导入_全部批次.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -823,7 +823,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -915,7 +915,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -3123,7 +3123,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -3215,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -3307,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="88" customHeight="1">
+    <row r="66" ht="107" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V66" s="2" t="inlineStr"/>
     </row>
-    <row r="67" ht="88" customHeight="1">
+    <row r="67" ht="107" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -6615,7 +6615,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="V67" s="4" t="inlineStr"/>
     </row>
-    <row r="68" ht="88" customHeight="1">
+    <row r="68" ht="107" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="V68" s="2" t="inlineStr"/>
     </row>
-    <row r="69" ht="88" customHeight="1">
+    <row r="69" ht="107" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -6791,7 +6791,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="V69" s="4" t="inlineStr"/>
     </row>
-    <row r="70" ht="88" customHeight="1">
+    <row r="70" ht="107" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="V70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" ht="88" customHeight="1">
+    <row r="71" ht="107" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -6967,7 +6967,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="V71" s="4" t="inlineStr"/>
     </row>
-    <row r="72" ht="88" customHeight="1">
+    <row r="72" ht="107" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="V72" s="2" t="inlineStr"/>
     </row>
-    <row r="73" ht="88" customHeight="1">
+    <row r="73" ht="107" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -7143,7 +7143,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -7196,7 +7196,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="88" customHeight="1">
+    <row r="74" ht="107" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="88" customHeight="1">
+    <row r="75" ht="107" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7327,7 +7327,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="V75" s="4" t="inlineStr"/>
     </row>
-    <row r="76" ht="88" customHeight="1">
+    <row r="76" ht="107" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V76" s="2" t="inlineStr"/>
     </row>
-    <row r="77" ht="88" customHeight="1">
+    <row r="77" ht="107" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -7503,7 +7503,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="V77" s="4" t="inlineStr"/>
     </row>
-    <row r="78" ht="88" customHeight="1">
+    <row r="78" ht="107" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="V78" s="2" t="inlineStr"/>
     </row>
-    <row r="79" ht="88" customHeight="1">
+    <row r="79" ht="107" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -7679,7 +7679,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="V79" s="4" t="inlineStr"/>
     </row>
-    <row r="80" ht="88" customHeight="1">
+    <row r="80" ht="107" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="V80" s="2" t="inlineStr"/>
     </row>
-    <row r="81" ht="88" customHeight="1">
+    <row r="81" ht="107" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="V81" s="4" t="inlineStr"/>
     </row>
-    <row r="82" ht="88" customHeight="1">
+    <row r="82" ht="107" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
-    <row r="83" ht="88" customHeight="1">
+    <row r="83" ht="107" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="V83" s="4" t="inlineStr"/>
     </row>
-    <row r="84" ht="88" customHeight="1">
+    <row r="84" ht="107" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -8172,7 +8172,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="88" customHeight="1">
+    <row r="85" ht="107" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -8211,7 +8211,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="V85" s="4" t="inlineStr"/>
     </row>
-    <row r="86" ht="88" customHeight="1">
+    <row r="86" ht="107" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="V86" s="2" t="inlineStr"/>
     </row>
-    <row r="87" ht="88" customHeight="1">
+    <row r="87" ht="107" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -8387,7 +8387,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="V87" s="4" t="inlineStr"/>
     </row>
-    <row r="88" ht="88" customHeight="1">
+    <row r="88" ht="107" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="88" customHeight="1">
+    <row r="89" ht="107" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="V89" s="4" t="inlineStr"/>
     </row>
-    <row r="90" ht="88" customHeight="1">
+    <row r="90" ht="107" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -8651,7 +8651,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="88" customHeight="1">
+    <row r="91" ht="107" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -8743,7 +8743,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="V91" s="4" t="inlineStr"/>
     </row>
-    <row r="92" ht="88" customHeight="1">
+    <row r="92" ht="107" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="V92" s="2" t="inlineStr"/>
     </row>
-    <row r="93" ht="88" customHeight="1">
+    <row r="93" ht="107" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -8919,7 +8919,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="V93" s="4" t="inlineStr"/>
     </row>
-    <row r="94" ht="88" customHeight="1">
+    <row r="94" ht="107" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="V94" s="2" t="inlineStr"/>
     </row>
-    <row r="95" ht="88" customHeight="1">
+    <row r="95" ht="107" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -9095,7 +9095,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="V95" s="4" t="inlineStr"/>
     </row>
-    <row r="96" ht="88" customHeight="1">
+    <row r="96" ht="107" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="V96" s="2" t="inlineStr"/>
     </row>
-    <row r="97" ht="88" customHeight="1">
+    <row r="97" ht="107" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -9271,7 +9271,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="V97" s="4" t="inlineStr"/>
     </row>
-    <row r="98" ht="88" customHeight="1">
+    <row r="98" ht="107" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -9359,7 +9359,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="V98" s="2" t="inlineStr"/>
     </row>
-    <row r="99" ht="88" customHeight="1">
+    <row r="99" ht="107" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -9447,7 +9447,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="V99" s="4" t="inlineStr"/>
     </row>
-    <row r="100" ht="88" customHeight="1">
+    <row r="100" ht="107" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="V100" s="2" t="inlineStr"/>
     </row>
-    <row r="101" ht="88" customHeight="1">
+    <row r="101" ht="107" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -9623,7 +9623,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="V101" s="4" t="inlineStr"/>
     </row>
-    <row r="102" ht="88" customHeight="1">
+    <row r="102" ht="107" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="V102" s="2" t="inlineStr"/>
     </row>
-    <row r="103" ht="88" customHeight="1">
+    <row r="103" ht="107" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -9799,7 +9799,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="V103" s="4" t="inlineStr"/>
     </row>
-    <row r="104" ht="88" customHeight="1">
+    <row r="104" ht="107" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="V104" s="2" t="inlineStr"/>
     </row>
-    <row r="105" ht="88" customHeight="1">
+    <row r="105" ht="107" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -9975,7 +9975,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="V105" s="4" t="inlineStr"/>
     </row>
-    <row r="106" ht="88" customHeight="1">
+    <row r="106" ht="107" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="V106" s="2" t="inlineStr"/>
     </row>
-    <row r="107" ht="88" customHeight="1">
+    <row r="107" ht="107" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -10151,7 +10151,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="V107" s="4" t="inlineStr"/>
     </row>
-    <row r="108" ht="88" customHeight="1">
+    <row r="108" ht="107" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -10239,7 +10239,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="V108" s="2" t="inlineStr"/>
     </row>
-    <row r="109" ht="88" customHeight="1">
+    <row r="109" ht="107" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -10327,7 +10327,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="V109" s="4" t="inlineStr"/>
     </row>
-    <row r="110" ht="88" customHeight="1">
+    <row r="110" ht="107" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="V110" s="2" t="inlineStr"/>
     </row>
-    <row r="111" ht="88" customHeight="1">
+    <row r="111" ht="107" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -10503,7 +10503,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="V111" s="4" t="inlineStr"/>
     </row>
-    <row r="112" ht="88" customHeight="1">
+    <row r="112" ht="107" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="V112" s="2" t="inlineStr"/>
     </row>
-    <row r="113" ht="88" customHeight="1">
+    <row r="113" ht="107" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -10679,7 +10679,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="V113" s="4" t="inlineStr"/>
     </row>
-    <row r="114" ht="88" customHeight="1">
+    <row r="114" ht="107" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -10767,7 +10767,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="88" customHeight="1">
+    <row r="115" ht="107" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -10859,7 +10859,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="V115" s="4" t="inlineStr"/>
     </row>
-    <row r="116" ht="88" customHeight="1">
+    <row r="116" ht="107" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="V116" s="2" t="inlineStr"/>
     </row>
-    <row r="117" ht="88" customHeight="1">
+    <row r="117" ht="107" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -11035,7 +11035,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="V117" s="4" t="inlineStr"/>
     </row>
-    <row r="118" ht="88" customHeight="1">
+    <row r="118" ht="107" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="V118" s="2" t="inlineStr"/>
     </row>
-    <row r="119" ht="88" customHeight="1">
+    <row r="119" ht="107" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -11211,7 +11211,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="V119" s="4" t="inlineStr"/>
     </row>
-    <row r="120" ht="88" customHeight="1">
+    <row r="120" ht="107" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -11299,7 +11299,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="V120" s="2" t="inlineStr"/>
     </row>
-    <row r="121" ht="88" customHeight="1">
+    <row r="121" ht="107" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -11387,7 +11387,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="V121" s="4" t="inlineStr"/>
     </row>
-    <row r="122" ht="88" customHeight="1">
+    <row r="122" ht="107" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="V122" s="2" t="inlineStr"/>
     </row>
-    <row r="123" ht="88" customHeight="1">
+    <row r="123" ht="107" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -11563,7 +11563,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="V123" s="4" t="inlineStr"/>
     </row>
-    <row r="124" ht="88" customHeight="1">
+    <row r="124" ht="107" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -11651,7 +11651,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="V124" s="2" t="inlineStr"/>
     </row>
-    <row r="125" ht="88" customHeight="1">
+    <row r="125" ht="107" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -11739,7 +11739,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="V125" s="4" t="inlineStr"/>
     </row>
-    <row r="126" ht="88" customHeight="1">
+    <row r="126" ht="107" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="V126" s="2" t="inlineStr"/>
     </row>
-    <row r="127" ht="88" customHeight="1">
+    <row r="127" ht="107" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -11915,7 +11915,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="V127" s="4" t="inlineStr"/>
     </row>
-    <row r="128" ht="88" customHeight="1">
+    <row r="128" ht="107" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -12003,7 +12003,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="V128" s="2" t="inlineStr"/>
     </row>
-    <row r="129" ht="88" customHeight="1">
+    <row r="129" ht="107" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -12091,7 +12091,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -15442,7 +15442,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       <c r="J167" s="4" t="inlineStr"/>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
@@ -15547,7 +15547,7 @@
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
@@ -16007,7 +16007,7 @@
       <c r="J173" s="4" t="inlineStr"/>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
@@ -16467,7 +16467,7 @@
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
@@ -16651,7 +16651,7 @@
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
@@ -17111,7 +17111,7 @@
       <c r="J185" s="4" t="inlineStr"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L185" s="4" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
@@ -17571,7 +17571,7 @@
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
@@ -17663,7 +17663,7 @@
       <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L191" s="4" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
@@ -17755,7 +17755,7 @@
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
@@ -18215,7 +18215,7 @@
       <c r="J197" s="4" t="inlineStr"/>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L197" s="4" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr"/>
@@ -18675,7 +18675,7 @@
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
@@ -18767,7 +18767,7 @@
       <c r="J203" s="4" t="inlineStr"/>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L203" s="4" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr"/>
@@ -18859,7 +18859,7 @@
       <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr"/>
@@ -19319,7 +19319,7 @@
       <c r="J209" s="4" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L209" s="4" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr"/>
@@ -19779,7 +19779,7 @@
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -19858,7 +19858,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr"/>
@@ -19871,7 +19871,7 @@
       <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L215" s="4" t="inlineStr">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr"/>
@@ -19963,7 +19963,7 @@
       <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -20410,7 +20410,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr"/>
@@ -20423,7 +20423,7 @@
       <c r="J221" s="4" t="inlineStr"/>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L221" s="4" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr"/>
@@ -20883,7 +20883,7 @@
       <c r="J226" s="2" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr"/>
@@ -20975,7 +20975,7 @@
       <c r="J227" s="4" t="inlineStr"/>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L227" s="4" t="inlineStr">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr"/>
@@ -21067,7 +21067,7 @@
       <c r="J228" s="2" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L228" s="2" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr"/>
@@ -21527,7 +21527,7 @@
       <c r="J233" s="4" t="inlineStr"/>
       <c r="K233" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L233" s="4" t="inlineStr">
@@ -21974,7 +21974,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       <c r="J238" s="2" t="inlineStr"/>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L238" s="2" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr"/>
@@ -22079,7 +22079,7 @@
       <c r="J239" s="4" t="inlineStr"/>
       <c r="K239" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L239" s="4" t="inlineStr">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr"/>
@@ -22171,7 +22171,7 @@
       <c r="J240" s="2" t="inlineStr"/>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L240" s="2" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr"/>
@@ -22631,7 +22631,7 @@
       <c r="J245" s="4" t="inlineStr"/>
       <c r="K245" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L245" s="4" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr"/>
@@ -23091,7 +23091,7 @@
       <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -23170,7 +23170,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr"/>
@@ -23183,7 +23183,7 @@
       <c r="J251" s="4" t="inlineStr"/>
       <c r="K251" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L251" s="4" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr"/>
@@ -23275,7 +23275,7 @@
       <c r="J252" s="2" t="inlineStr"/>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       <c r="J257" s="4" t="inlineStr"/>
       <c r="K257" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L257" s="4" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr"/>
@@ -23919,7 +23919,7 @@
       <c r="J259" s="4" t="inlineStr"/>
       <c r="K259" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L259" s="4" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr"/>
@@ -24011,7 +24011,7 @@
       <c r="J260" s="2" t="inlineStr"/>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr"/>
@@ -24103,7 +24103,7 @@
       <c r="J261" s="4" t="inlineStr"/>
       <c r="K261" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L261" s="4" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr"/>
@@ -24563,7 +24563,7 @@
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr"/>
@@ -24655,7 +24655,7 @@
       <c r="J267" s="4" t="inlineStr"/>
       <c r="K267" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L267" s="4" t="inlineStr">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr"/>
@@ -24747,7 +24747,7 @@
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L268" s="2" t="inlineStr">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G273" s="4" t="inlineStr"/>
@@ -25207,7 +25207,7 @@
       <c r="J273" s="4" t="inlineStr"/>
       <c r="K273" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L273" s="4" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr"/>
@@ -25299,7 +25299,7 @@
       <c r="J274" s="2" t="inlineStr"/>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L274" s="2" t="inlineStr">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G275" s="4" t="inlineStr"/>
@@ -25391,7 +25391,7 @@
       <c r="J275" s="4" t="inlineStr"/>
       <c r="K275" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L275" s="4" t="inlineStr">
@@ -25838,7 +25838,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr"/>
@@ -25851,7 +25851,7 @@
       <c r="J280" s="2" t="inlineStr"/>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L280" s="2" t="inlineStr">
@@ -25930,7 +25930,7 @@
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G281" s="4" t="inlineStr"/>
@@ -25943,7 +25943,7 @@
       <c r="J281" s="4" t="inlineStr"/>
       <c r="K281" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L281" s="4" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr"/>
@@ -26035,7 +26035,7 @@
       <c r="J282" s="2" t="inlineStr"/>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L282" s="2" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr"/>
@@ -26495,7 +26495,7 @@
       <c r="J287" s="4" t="inlineStr"/>
       <c r="K287" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L287" s="4" t="inlineStr">
@@ -26574,7 +26574,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       <c r="J288" s="2" t="inlineStr"/>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L288" s="2" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr"/>
@@ -26679,7 +26679,7 @@
       <c r="J289" s="4" t="inlineStr"/>
       <c r="K289" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L289" s="4" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr"/>
@@ -27139,7 +27139,7 @@
       <c r="J294" s="2" t="inlineStr"/>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L294" s="2" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       <c r="J295" s="4" t="inlineStr"/>
       <c r="K295" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L295" s="4" t="inlineStr">
@@ -27310,7 +27310,7 @@
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr"/>
@@ -27323,7 +27323,7 @@
       <c r="J296" s="2" t="inlineStr"/>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L296" s="2" t="inlineStr">
@@ -27770,7 +27770,7 @@
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G301" s="4" t="inlineStr"/>
@@ -27783,7 +27783,7 @@
       <c r="J301" s="4" t="inlineStr"/>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L301" s="4" t="inlineStr">
@@ -27862,7 +27862,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr"/>
@@ -27875,7 +27875,7 @@
       <c r="J302" s="2" t="inlineStr"/>
       <c r="K302" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L302" s="2" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G303" s="4" t="inlineStr"/>
@@ -27967,7 +27967,7 @@
       <c r="J303" s="4" t="inlineStr"/>
       <c r="K303" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L303" s="4" t="inlineStr">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr"/>
@@ -28427,7 +28427,7 @@
       <c r="J308" s="2" t="inlineStr"/>
       <c r="K308" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L308" s="2" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr"/>
@@ -28519,7 +28519,7 @@
       <c r="J309" s="4" t="inlineStr"/>
       <c r="K309" s="4" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L309" s="4" t="inlineStr">
@@ -28598,7 +28598,7 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr"/>
@@ -28611,7 +28611,7 @@
       <c r="J310" s="2" t="inlineStr"/>
       <c r="K310" s="2" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L310" s="2" t="inlineStr">
@@ -29334,7 +29334,7 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr"/>
@@ -29347,7 +29347,7 @@
       <c r="J318" s="2" t="inlineStr"/>
       <c r="K318" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L318" s="2" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr"/>
@@ -29439,7 +29439,7 @@
       <c r="J319" s="4" t="inlineStr"/>
       <c r="K319" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L319" s="4" t="inlineStr">
@@ -29518,7 +29518,7 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr"/>
@@ -29531,7 +29531,7 @@
       <c r="J320" s="2" t="inlineStr"/>
       <c r="K320" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L320" s="2" t="inlineStr">
@@ -29978,7 +29978,7 @@
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G325" s="4" t="inlineStr"/>
@@ -29991,7 +29991,7 @@
       <c r="J325" s="4" t="inlineStr"/>
       <c r="K325" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L325" s="4" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr"/>
@@ -30451,7 +30451,7 @@
       <c r="J330" s="2" t="inlineStr"/>
       <c r="K330" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L330" s="2" t="inlineStr">
@@ -30530,7 +30530,7 @@
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G331" s="4" t="inlineStr"/>
@@ -30543,7 +30543,7 @@
       <c r="J331" s="4" t="inlineStr"/>
       <c r="K331" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L331" s="4" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr"/>
@@ -30635,7 +30635,7 @@
       <c r="J332" s="2" t="inlineStr"/>
       <c r="K332" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L332" s="2" t="inlineStr">
@@ -31082,7 +31082,7 @@
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr"/>
@@ -31095,7 +31095,7 @@
       <c r="J337" s="4" t="inlineStr"/>
       <c r="K337" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L337" s="4" t="inlineStr">
@@ -31542,7 +31542,7 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr"/>
@@ -31555,7 +31555,7 @@
       <c r="J342" s="2" t="inlineStr"/>
       <c r="K342" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L342" s="2" t="inlineStr">
@@ -31634,7 +31634,7 @@
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G343" s="4" t="inlineStr"/>
@@ -31647,7 +31647,7 @@
       <c r="J343" s="4" t="inlineStr"/>
       <c r="K343" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L343" s="4" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G344" s="2" t="inlineStr"/>
@@ -31739,7 +31739,7 @@
       <c r="J344" s="2" t="inlineStr"/>
       <c r="K344" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L344" s="2" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr"/>
@@ -32199,7 +32199,7 @@
       <c r="J349" s="4" t="inlineStr"/>
       <c r="K349" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L349" s="4" t="inlineStr">
@@ -32646,7 +32646,7 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr"/>
@@ -32659,7 +32659,7 @@
       <c r="J354" s="2" t="inlineStr"/>
       <c r="K354" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L354" s="2" t="inlineStr">
@@ -32738,7 +32738,7 @@
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr"/>
@@ -32751,7 +32751,7 @@
       <c r="J355" s="4" t="inlineStr"/>
       <c r="K355" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L355" s="4" t="inlineStr">
@@ -32830,7 +32830,7 @@
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G356" s="2" t="inlineStr"/>
@@ -32843,7 +32843,7 @@
       <c r="J356" s="2" t="inlineStr"/>
       <c r="K356" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L356" s="2" t="inlineStr">
@@ -33290,7 +33290,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr"/>
@@ -33303,7 +33303,7 @@
       <c r="J361" s="4" t="inlineStr"/>
       <c r="K361" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L361" s="4" t="inlineStr">
@@ -33750,7 +33750,7 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr"/>
@@ -33763,7 +33763,7 @@
       <c r="J366" s="2" t="inlineStr"/>
       <c r="K366" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L366" s="2" t="inlineStr">
@@ -33842,7 +33842,7 @@
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr"/>
@@ -33855,7 +33855,7 @@
       <c r="J367" s="4" t="inlineStr"/>
       <c r="K367" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L367" s="4" t="inlineStr">
@@ -33934,7 +33934,7 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr"/>
@@ -33947,7 +33947,7 @@
       <c r="J368" s="2" t="inlineStr"/>
       <c r="K368" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L368" s="2" t="inlineStr">
@@ -34394,7 +34394,7 @@
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr"/>
@@ -34407,7 +34407,7 @@
       <c r="J373" s="4" t="inlineStr"/>
       <c r="K373" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L373" s="4" t="inlineStr">
@@ -34854,7 +34854,7 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr"/>
@@ -34867,7 +34867,7 @@
       <c r="J378" s="2" t="inlineStr"/>
       <c r="K378" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L378" s="2" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G379" s="4" t="inlineStr"/>
@@ -34959,7 +34959,7 @@
       <c r="J379" s="4" t="inlineStr"/>
       <c r="K379" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L379" s="4" t="inlineStr">
@@ -35038,7 +35038,7 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr"/>
@@ -35051,7 +35051,7 @@
       <c r="J380" s="2" t="inlineStr"/>
       <c r="K380" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L380" s="2" t="inlineStr">
@@ -35498,7 +35498,7 @@
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr"/>
@@ -35511,7 +35511,7 @@
       <c r="J385" s="4" t="inlineStr"/>
       <c r="K385" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L385" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       <c r="J390" s="2" t="inlineStr"/>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L390" s="2" t="inlineStr">
@@ -36050,7 +36050,7 @@
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G391" s="4" t="inlineStr"/>
@@ -36063,7 +36063,7 @@
       <c r="J391" s="4" t="inlineStr"/>
       <c r="K391" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L391" s="4" t="inlineStr">
@@ -36142,7 +36142,7 @@
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr"/>
@@ -36155,7 +36155,7 @@
       <c r="J392" s="2" t="inlineStr"/>
       <c r="K392" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L392" s="2" t="inlineStr">
@@ -36602,7 +36602,7 @@
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr"/>
@@ -36615,7 +36615,7 @@
       <c r="J397" s="4" t="inlineStr"/>
       <c r="K397" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L397" s="4" t="inlineStr">
@@ -37062,7 +37062,7 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       <c r="J402" s="2" t="inlineStr"/>
       <c r="K402" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L402" s="2" t="inlineStr">
@@ -37154,7 +37154,7 @@
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G403" s="4" t="inlineStr"/>
@@ -37167,7 +37167,7 @@
       <c r="J403" s="4" t="inlineStr"/>
       <c r="K403" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L403" s="4" t="inlineStr">
@@ -37246,7 +37246,7 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
@@ -37259,7 +37259,7 @@
       <c r="J404" s="2" t="inlineStr"/>
       <c r="K404" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L404" s="2" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="F409" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G409" s="4" t="inlineStr"/>
@@ -37719,7 +37719,7 @@
       <c r="J409" s="4" t="inlineStr"/>
       <c r="K409" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F012=第12弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L409" s="4" t="inlineStr">
@@ -37890,7 +37890,7 @@
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G411" s="4" t="inlineStr"/>
@@ -37903,7 +37903,7 @@
       <c r="J411" s="4" t="inlineStr"/>
       <c r="K411" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L411" s="4" t="inlineStr">
@@ -37982,7 +37982,7 @@
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr"/>
@@ -37995,7 +37995,7 @@
       <c r="J412" s="2" t="inlineStr"/>
       <c r="K412" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L412" s="2" t="inlineStr">
@@ -38074,7 +38074,7 @@
       </c>
       <c r="F413" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G413" s="4" t="inlineStr"/>
@@ -38087,7 +38087,7 @@
       <c r="J413" s="4" t="inlineStr"/>
       <c r="K413" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L413" s="4" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr"/>
@@ -38547,7 +38547,7 @@
       <c r="J418" s="2" t="inlineStr"/>
       <c r="K418" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L418" s="2" t="inlineStr">
@@ -38626,7 +38626,7 @@
       </c>
       <c r="F419" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G419" s="4" t="inlineStr"/>
@@ -38639,7 +38639,7 @@
       <c r="J419" s="4" t="inlineStr"/>
       <c r="K419" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L419" s="4" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr"/>
@@ -38731,7 +38731,7 @@
       <c r="J420" s="2" t="inlineStr"/>
       <c r="K420" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L420" s="2" t="inlineStr">
@@ -39178,7 +39178,7 @@
       </c>
       <c r="F425" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G425" s="4" t="inlineStr"/>
@@ -39191,7 +39191,7 @@
       <c r="J425" s="4" t="inlineStr"/>
       <c r="K425" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L425" s="4" t="inlineStr">
@@ -39270,7 +39270,7 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr"/>
@@ -39283,7 +39283,7 @@
       <c r="J426" s="2" t="inlineStr"/>
       <c r="K426" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L426" s="2" t="inlineStr">
@@ -39362,7 +39362,7 @@
       </c>
       <c r="F427" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G427" s="4" t="inlineStr"/>
@@ -39375,7 +39375,7 @@
       <c r="J427" s="4" t="inlineStr"/>
       <c r="K427" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L427" s="4" t="inlineStr">
@@ -39822,7 +39822,7 @@
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr"/>
@@ -39835,7 +39835,7 @@
       <c r="J432" s="2" t="inlineStr"/>
       <c r="K432" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L432" s="2" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="F433" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G433" s="4" t="inlineStr"/>
@@ -39927,7 +39927,7 @@
       <c r="J433" s="4" t="inlineStr"/>
       <c r="K433" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L433" s="4" t="inlineStr">
@@ -40006,7 +40006,7 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr"/>
@@ -40019,7 +40019,7 @@
       <c r="J434" s="2" t="inlineStr"/>
       <c r="K434" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L434" s="2" t="inlineStr">
@@ -40466,7 +40466,7 @@
       </c>
       <c r="F439" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G439" s="4" t="inlineStr"/>
@@ -40479,7 +40479,7 @@
       <c r="J439" s="4" t="inlineStr"/>
       <c r="K439" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L439" s="4" t="inlineStr">
@@ -40558,7 +40558,7 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
@@ -40571,7 +40571,7 @@
       <c r="J440" s="2" t="inlineStr"/>
       <c r="K440" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L440" s="2" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="F441" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G441" s="4" t="inlineStr"/>
@@ -40663,7 +40663,7 @@
       <c r="J441" s="4" t="inlineStr"/>
       <c r="K441" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L441" s="4" t="inlineStr">
@@ -41110,7 +41110,7 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr"/>
@@ -41123,7 +41123,7 @@
       <c r="J446" s="2" t="inlineStr"/>
       <c r="K446" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L446" s="2" t="inlineStr">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="F447" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G447" s="4" t="inlineStr"/>
@@ -41215,7 +41215,7 @@
       <c r="J447" s="4" t="inlineStr"/>
       <c r="K447" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L447" s="4" t="inlineStr">
@@ -41294,7 +41294,7 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr"/>
@@ -41307,7 +41307,7 @@
       <c r="J448" s="2" t="inlineStr"/>
       <c r="K448" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L448" s="2" t="inlineStr">
@@ -41754,7 +41754,7 @@
       </c>
       <c r="F453" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G453" s="4" t="inlineStr"/>
@@ -41767,7 +41767,7 @@
       <c r="J453" s="4" t="inlineStr"/>
       <c r="K453" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L453" s="4" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr"/>
@@ -41859,7 +41859,7 @@
       <c r="J454" s="2" t="inlineStr"/>
       <c r="K454" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L454" s="2" t="inlineStr">
@@ -41938,7 +41938,7 @@
       </c>
       <c r="F455" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G455" s="4" t="inlineStr"/>
@@ -41951,7 +41951,7 @@
       <c r="J455" s="4" t="inlineStr"/>
       <c r="K455" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L455" s="4" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G460" s="2" t="inlineStr"/>
@@ -42411,7 +42411,7 @@
       <c r="J460" s="2" t="inlineStr"/>
       <c r="K460" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L460" s="2" t="inlineStr">
@@ -42490,7 +42490,7 @@
       </c>
       <c r="F461" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G461" s="4" t="inlineStr"/>
@@ -42503,7 +42503,7 @@
       <c r="J461" s="4" t="inlineStr"/>
       <c r="K461" s="4" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L461" s="4" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr"/>
@@ -42595,7 +42595,7 @@
       <c r="J462" s="2" t="inlineStr"/>
       <c r="K462" s="2" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→T91</t>
+          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L462" s="2" t="inlineStr">

--- a/data-cleaning/verified/导入_全部批次.xlsx
+++ b/data-cleaning/verified/导入_全部批次.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="126" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -600,7 +600,7 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="126" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -692,7 +692,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="126" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -784,7 +784,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="126" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -876,7 +876,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="126" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -968,7 +968,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="126" customHeight="1">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1060,7 +1060,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="126" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1152,7 +1152,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="126" customHeight="1">
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1244,7 +1244,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F014=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="126" customHeight="1">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1336,7 +1336,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F015=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="126" customHeight="1">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1428,7 +1428,7 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F016=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1520,7 +1520,7 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F017=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="126" customHeight="1">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1612,7 +1612,7 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F018=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="126" customHeight="1">
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1704,7 +1704,7 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F019=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="126" customHeight="1">
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1796,7 +1796,7 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F020=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="126" customHeight="1">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1888,7 +1888,7 @@
       <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F021=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="126" customHeight="1">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1980,7 +1980,7 @@
       <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F022=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="126" customHeight="1">
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2072,7 +2072,7 @@
       <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="126" customHeight="1">
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2164,7 +2164,7 @@
       <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="126" customHeight="1">
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2256,7 +2256,7 @@
       <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="126" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2348,7 +2348,7 @@
       <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="126" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2440,7 +2440,7 @@
       <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="126" customHeight="1">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2532,7 +2532,7 @@
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="126" customHeight="1">
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2624,7 +2624,7 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="126" customHeight="1">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2716,7 +2716,7 @@
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F014=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="126" customHeight="1">
+    <row r="26" ht="32" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2808,7 +2808,7 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F015=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="126" customHeight="1">
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2900,7 +2900,7 @@
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F016=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="126" customHeight="1">
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2992,7 +2992,7 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F017=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="126" customHeight="1">
+    <row r="29" ht="32" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3084,7 +3084,7 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F018=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="126" customHeight="1">
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3176,7 +3176,7 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F019=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="126" customHeight="1">
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3268,7 +3268,7 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F020=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="126" customHeight="1">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3360,7 +3360,7 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F021=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="126" customHeight="1">
+    <row r="33" ht="32" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3452,7 +3452,7 @@
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F022=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="69" customHeight="1">
+    <row r="34" ht="32" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3544,7 +3544,7 @@
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R6#001；位置：L001-F001；源位置：1号炉炉左至炉右第1屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="69" customHeight="1">
+    <row r="35" ht="32" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3636,7 +3636,7 @@
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R7#001；位置：L002-F001；源位置：1号炉炉左至炉右第2屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr">
@@ -3689,7 +3689,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="69" customHeight="1">
+    <row r="36" ht="32" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3728,7 +3728,7 @@
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R8#001；位置：L003-F001；源位置：1号炉炉左至炉右第3屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="69" customHeight="1">
+    <row r="37" ht="32" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3820,7 +3820,7 @@
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R9#001；位置：L004-F001；源位置：1号炉炉左至炉右第4屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="69" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3912,7 +3912,7 @@
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R10#001；位置：L005-F001；源位置：1号炉炉左至炉右第5屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="69" customHeight="1">
+    <row r="39" ht="32" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4004,7 +4004,7 @@
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R11#001；位置：L006-F001；源位置：1号炉炉左至炉右第6屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="69" customHeight="1">
+    <row r="40" ht="32" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4096,7 +4096,7 @@
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R12#001；位置：L007-F001；源位置：1号炉炉左至炉右第7屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L40" s="1" t="inlineStr">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="69" customHeight="1">
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4188,7 +4188,7 @@
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R13#001；位置：L008-F001；源位置：1号炉炉左至炉右第8屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L41" s="1" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="69" customHeight="1">
+    <row r="42" ht="32" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4280,7 +4280,7 @@
       <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R14#001；位置：L009-F001；源位置：1号炉炉左至炉右第9屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="69" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4372,7 +4372,7 @@
       <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R15#001；位置：L010-F001；源位置：1号炉炉左至炉右第10屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L43" s="1" t="inlineStr">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="69" customHeight="1">
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4464,7 +4464,7 @@
       <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R16#001；位置：L011-F001；源位置：1号炉炉左至炉右第11屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="69" customHeight="1">
+    <row r="45" ht="32" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4556,7 +4556,7 @@
       <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R17#001；位置：L012-F001；源位置：1号炉炉左至炉右第12屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L45" s="1" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="69" customHeight="1">
+    <row r="46" ht="32" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4648,7 +4648,7 @@
       <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R18#001；位置：L013-F001；源位置：1号炉炉左至炉右第13屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="69" customHeight="1">
+    <row r="47" ht="32" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4740,7 +4740,7 @@
       <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R19#001；位置：L014-F001；源位置：1号炉炉左至炉右第14屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -4793,7 +4793,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="69" customHeight="1">
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4832,7 +4832,7 @@
       <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R20#001；位置：L015-F001；源位置：1号炉炉左至炉右第15屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="69" customHeight="1">
+    <row r="49" ht="32" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4924,7 +4924,7 @@
       <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R21#001；位置：L016-F001；源位置：1号炉炉左至炉右第16屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L49" s="1" t="inlineStr">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="69" customHeight="1">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5016,7 +5016,7 @@
       <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R22#001；位置：L017-F001；源位置：1号炉炉左至炉右第17屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
@@ -5069,7 +5069,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="69" customHeight="1">
+    <row r="51" ht="32" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5108,7 +5108,7 @@
       <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R23#001；位置：L018-F001；源位置：1号炉炉左至炉右第18屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L51" s="1" t="inlineStr">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="69" customHeight="1">
+    <row r="52" ht="32" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5200,7 +5200,7 @@
       <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R24#001；位置：L019-F001；源位置：1号炉炉左至炉右第19屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="69" customHeight="1">
+    <row r="53" ht="32" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5292,7 +5292,7 @@
       <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R25#001；位置：L020-F001；源位置：1号炉炉左至炉右第20屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="69" customHeight="1">
+    <row r="54" ht="32" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5384,7 +5384,7 @@
       <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R26#001；位置：L021-F001；源位置：1号炉炉左至炉右第21屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="69" customHeight="1">
+    <row r="55" ht="32" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5476,7 +5476,7 @@
       <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R27#001；位置：L022-F001；源位置：1号炉炉左至炉右第22屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L55" s="1" t="inlineStr">
@@ -5529,7 +5529,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="69" customHeight="1">
+    <row r="56" ht="32" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5568,7 +5568,7 @@
       <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R28#001；位置：L023-F001；源位置：1号炉炉左至炉右第23屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="69" customHeight="1">
+    <row r="57" ht="32" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5660,7 +5660,7 @@
       <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R29#001；位置：L024-F001；源位置：1号炉炉左至炉右第24屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="69" customHeight="1">
+    <row r="58" ht="32" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5752,7 +5752,7 @@
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R30#001；位置：L025-F001；源位置：1号炉炉左至炉右第25屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L58" s="1" t="inlineStr">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="69" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5844,7 +5844,7 @@
       <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R31#001；位置：L026-F001；源位置：1号炉炉左至炉右第26屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L59" s="1" t="inlineStr">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="88" customHeight="1">
+    <row r="60" ht="32" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5936,7 +5936,7 @@
       <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R32#001；位置：L027-F001；源位置：1号炉炉左至炉右第24屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格；用户确认源表第32行“第24屏”实为第27屏（原表笔误），编码按L027修正</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L60" s="1" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="69" customHeight="1">
+    <row r="61" ht="32" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6028,7 +6028,7 @@
       <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R33#001；位置：L028-F001；源位置：1号炉炉左至炉右第28屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L61" s="1" t="inlineStr">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="69" customHeight="1">
+    <row r="62" ht="32" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6120,7 +6120,7 @@
       <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R34#001；位置：L029-F001；源位置：1号炉炉左至炉右第29屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="69" customHeight="1">
+    <row r="63" ht="32" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6212,7 +6212,7 @@
       <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R35#001；位置：L030-F001；源位置：1号炉炉左至炉右第30屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L63" s="1" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="69" customHeight="1">
+    <row r="64" ht="32" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6304,7 +6304,7 @@
       <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R36#001；位置：L031-F001；源位置：1号炉炉左至炉右第31屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L64" s="1" t="inlineStr">
@@ -6357,7 +6357,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="69" customHeight="1">
+    <row r="65" ht="32" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6396,7 +6396,7 @@
       <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R37#001；位置：L032-F001；源位置：1号炉炉左至炉右第32屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="107" customHeight="1">
+    <row r="66" ht="32" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6488,7 +6488,7 @@
       <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L66" s="1" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="V66" s="1" t="inlineStr"/>
     </row>
-    <row r="67" ht="107" customHeight="1">
+    <row r="67" ht="32" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6576,7 +6576,7 @@
       <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L67" s="1" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="V67" s="1" t="inlineStr"/>
     </row>
-    <row r="68" ht="107" customHeight="1">
+    <row r="68" ht="32" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6664,7 +6664,7 @@
       <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L68" s="1" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="V68" s="1" t="inlineStr"/>
     </row>
-    <row r="69" ht="107" customHeight="1">
+    <row r="69" ht="32" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6752,7 +6752,7 @@
       <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L69" s="1" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="V69" s="1" t="inlineStr"/>
     </row>
-    <row r="70" ht="107" customHeight="1">
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6840,7 +6840,7 @@
       <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L70" s="1" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V70" s="1" t="inlineStr"/>
     </row>
-    <row r="71" ht="107" customHeight="1">
+    <row r="71" ht="32" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6928,7 +6928,7 @@
       <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L71" s="1" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="V71" s="1" t="inlineStr"/>
     </row>
-    <row r="72" ht="107" customHeight="1">
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7016,7 +7016,7 @@
       <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L72" s="1" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="V72" s="1" t="inlineStr"/>
     </row>
-    <row r="73" ht="107" customHeight="1">
+    <row r="73" ht="50" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7104,7 +7104,7 @@
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L73" s="1" t="inlineStr">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="107" customHeight="1">
+    <row r="74" ht="50" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7196,7 +7196,7 @@
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L74" s="1" t="inlineStr">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="107" customHeight="1">
+    <row r="75" ht="32" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7288,7 +7288,7 @@
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L75" s="1" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="V75" s="1" t="inlineStr"/>
     </row>
-    <row r="76" ht="107" customHeight="1">
+    <row r="76" ht="32" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7376,7 +7376,7 @@
       <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L76" s="1" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="V76" s="1" t="inlineStr"/>
     </row>
-    <row r="77" ht="107" customHeight="1">
+    <row r="77" ht="32" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7464,7 +7464,7 @@
       <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L77" s="1" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="V77" s="1" t="inlineStr"/>
     </row>
-    <row r="78" ht="107" customHeight="1">
+    <row r="78" ht="32" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7552,7 +7552,7 @@
       <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L78" s="1" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="V78" s="1" t="inlineStr"/>
     </row>
-    <row r="79" ht="107" customHeight="1">
+    <row r="79" ht="32" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7640,7 +7640,7 @@
       <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L79" s="1" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="V79" s="1" t="inlineStr"/>
     </row>
-    <row r="80" ht="107" customHeight="1">
+    <row r="80" ht="32" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7728,7 +7728,7 @@
       <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L80" s="1" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="V80" s="1" t="inlineStr"/>
     </row>
-    <row r="81" ht="107" customHeight="1">
+    <row r="81" ht="32" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7816,7 +7816,7 @@
       <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L81" s="1" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="V81" s="1" t="inlineStr"/>
     </row>
-    <row r="82" ht="107" customHeight="1">
+    <row r="82" ht="32" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7904,7 +7904,7 @@
       <c r="J82" s="1" t="inlineStr"/>
       <c r="K82" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L82" s="1" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="V82" s="1" t="inlineStr"/>
     </row>
-    <row r="83" ht="107" customHeight="1">
+    <row r="83" ht="32" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7992,7 +7992,7 @@
       <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L83" s="1" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="V83" s="1" t="inlineStr"/>
     </row>
-    <row r="84" ht="107" customHeight="1">
+    <row r="84" ht="50" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8080,7 +8080,7 @@
       <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L84" s="1" t="inlineStr">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="107" customHeight="1">
+    <row r="85" ht="32" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8172,7 +8172,7 @@
       <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L85" s="1" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="V85" s="1" t="inlineStr"/>
     </row>
-    <row r="86" ht="107" customHeight="1">
+    <row r="86" ht="32" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8260,7 +8260,7 @@
       <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L86" s="1" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="V86" s="1" t="inlineStr"/>
     </row>
-    <row r="87" ht="107" customHeight="1">
+    <row r="87" ht="32" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8348,7 +8348,7 @@
       <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L87" s="1" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="V87" s="1" t="inlineStr"/>
     </row>
-    <row r="88" ht="107" customHeight="1">
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8436,7 +8436,7 @@
       <c r="J88" s="1" t="inlineStr"/>
       <c r="K88" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L88" s="1" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="V88" s="1" t="inlineStr"/>
     </row>
-    <row r="89" ht="107" customHeight="1">
+    <row r="89" ht="32" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8524,7 +8524,7 @@
       <c r="J89" s="1" t="inlineStr"/>
       <c r="K89" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L89" s="1" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="V89" s="1" t="inlineStr"/>
     </row>
-    <row r="90" ht="107" customHeight="1">
+    <row r="90" ht="50" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8612,7 +8612,7 @@
       <c r="J90" s="1" t="inlineStr"/>
       <c r="K90" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L90" s="1" t="inlineStr">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="107" customHeight="1">
+    <row r="91" ht="32" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8704,7 +8704,7 @@
       <c r="J91" s="1" t="inlineStr"/>
       <c r="K91" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L91" s="1" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="V91" s="1" t="inlineStr"/>
     </row>
-    <row r="92" ht="107" customHeight="1">
+    <row r="92" ht="32" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8792,7 +8792,7 @@
       <c r="J92" s="1" t="inlineStr"/>
       <c r="K92" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L92" s="1" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="V92" s="1" t="inlineStr"/>
     </row>
-    <row r="93" ht="107" customHeight="1">
+    <row r="93" ht="32" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8880,7 +8880,7 @@
       <c r="J93" s="1" t="inlineStr"/>
       <c r="K93" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L93" s="1" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="V93" s="1" t="inlineStr"/>
     </row>
-    <row r="94" ht="107" customHeight="1">
+    <row r="94" ht="32" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8968,7 +8968,7 @@
       <c r="J94" s="1" t="inlineStr"/>
       <c r="K94" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L94" s="1" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="V94" s="1" t="inlineStr"/>
     </row>
-    <row r="95" ht="107" customHeight="1">
+    <row r="95" ht="32" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9056,7 +9056,7 @@
       <c r="J95" s="1" t="inlineStr"/>
       <c r="K95" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L95" s="1" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="V95" s="1" t="inlineStr"/>
     </row>
-    <row r="96" ht="107" customHeight="1">
+    <row r="96" ht="32" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9144,7 +9144,7 @@
       <c r="J96" s="1" t="inlineStr"/>
       <c r="K96" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L96" s="1" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="V96" s="1" t="inlineStr"/>
     </row>
-    <row r="97" ht="107" customHeight="1">
+    <row r="97" ht="32" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9232,7 +9232,7 @@
       <c r="J97" s="1" t="inlineStr"/>
       <c r="K97" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L97" s="1" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="V97" s="1" t="inlineStr"/>
     </row>
-    <row r="98" ht="107" customHeight="1">
+    <row r="98" ht="32" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9320,7 +9320,7 @@
       <c r="J98" s="1" t="inlineStr"/>
       <c r="K98" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L98" s="1" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="V98" s="1" t="inlineStr"/>
     </row>
-    <row r="99" ht="107" customHeight="1">
+    <row r="99" ht="32" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9408,7 +9408,7 @@
       <c r="J99" s="1" t="inlineStr"/>
       <c r="K99" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L99" s="1" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="V99" s="1" t="inlineStr"/>
     </row>
-    <row r="100" ht="107" customHeight="1">
+    <row r="100" ht="32" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9496,7 +9496,7 @@
       <c r="J100" s="1" t="inlineStr"/>
       <c r="K100" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L100" s="1" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="V100" s="1" t="inlineStr"/>
     </row>
-    <row r="101" ht="107" customHeight="1">
+    <row r="101" ht="32" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9584,7 +9584,7 @@
       <c r="J101" s="1" t="inlineStr"/>
       <c r="K101" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L101" s="1" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="V101" s="1" t="inlineStr"/>
     </row>
-    <row r="102" ht="107" customHeight="1">
+    <row r="102" ht="32" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9672,7 +9672,7 @@
       <c r="J102" s="1" t="inlineStr"/>
       <c r="K102" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L102" s="1" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="V102" s="1" t="inlineStr"/>
     </row>
-    <row r="103" ht="107" customHeight="1">
+    <row r="103" ht="32" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9760,7 +9760,7 @@
       <c r="J103" s="1" t="inlineStr"/>
       <c r="K103" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L103" s="1" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V103" s="1" t="inlineStr"/>
     </row>
-    <row r="104" ht="107" customHeight="1">
+    <row r="104" ht="32" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9848,7 +9848,7 @@
       <c r="J104" s="1" t="inlineStr"/>
       <c r="K104" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L104" s="1" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="V104" s="1" t="inlineStr"/>
     </row>
-    <row r="105" ht="107" customHeight="1">
+    <row r="105" ht="32" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9936,7 +9936,7 @@
       <c r="J105" s="1" t="inlineStr"/>
       <c r="K105" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L105" s="1" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="V105" s="1" t="inlineStr"/>
     </row>
-    <row r="106" ht="107" customHeight="1">
+    <row r="106" ht="32" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10024,7 +10024,7 @@
       <c r="J106" s="1" t="inlineStr"/>
       <c r="K106" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L106" s="1" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="V106" s="1" t="inlineStr"/>
     </row>
-    <row r="107" ht="107" customHeight="1">
+    <row r="107" ht="32" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10112,7 +10112,7 @@
       <c r="J107" s="1" t="inlineStr"/>
       <c r="K107" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L107" s="1" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="V107" s="1" t="inlineStr"/>
     </row>
-    <row r="108" ht="107" customHeight="1">
+    <row r="108" ht="32" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10200,7 +10200,7 @@
       <c r="J108" s="1" t="inlineStr"/>
       <c r="K108" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L108" s="1" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="V108" s="1" t="inlineStr"/>
     </row>
-    <row r="109" ht="107" customHeight="1">
+    <row r="109" ht="32" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10288,7 +10288,7 @@
       <c r="J109" s="1" t="inlineStr"/>
       <c r="K109" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L109" s="1" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="V109" s="1" t="inlineStr"/>
     </row>
-    <row r="110" ht="107" customHeight="1">
+    <row r="110" ht="32" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10376,7 +10376,7 @@
       <c r="J110" s="1" t="inlineStr"/>
       <c r="K110" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L110" s="1" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="V110" s="1" t="inlineStr"/>
     </row>
-    <row r="111" ht="107" customHeight="1">
+    <row r="111" ht="32" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10464,7 +10464,7 @@
       <c r="J111" s="1" t="inlineStr"/>
       <c r="K111" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L111" s="1" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="V111" s="1" t="inlineStr"/>
     </row>
-    <row r="112" ht="107" customHeight="1">
+    <row r="112" ht="32" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10552,7 +10552,7 @@
       <c r="J112" s="1" t="inlineStr"/>
       <c r="K112" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L112" s="1" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="V112" s="1" t="inlineStr"/>
     </row>
-    <row r="113" ht="107" customHeight="1">
+    <row r="113" ht="32" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10640,7 +10640,7 @@
       <c r="J113" s="1" t="inlineStr"/>
       <c r="K113" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L113" s="1" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="V113" s="1" t="inlineStr"/>
     </row>
-    <row r="114" ht="107" customHeight="1">
+    <row r="114" ht="50" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10728,7 +10728,7 @@
       <c r="J114" s="1" t="inlineStr"/>
       <c r="K114" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L114" s="1" t="inlineStr">
@@ -10781,7 +10781,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="107" customHeight="1">
+    <row r="115" ht="32" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10820,7 +10820,7 @@
       <c r="J115" s="1" t="inlineStr"/>
       <c r="K115" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L115" s="1" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="V115" s="1" t="inlineStr"/>
     </row>
-    <row r="116" ht="107" customHeight="1">
+    <row r="116" ht="32" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10908,7 +10908,7 @@
       <c r="J116" s="1" t="inlineStr"/>
       <c r="K116" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L116" s="1" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="V116" s="1" t="inlineStr"/>
     </row>
-    <row r="117" ht="107" customHeight="1">
+    <row r="117" ht="32" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10996,7 +10996,7 @@
       <c r="J117" s="1" t="inlineStr"/>
       <c r="K117" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L117" s="1" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="V117" s="1" t="inlineStr"/>
     </row>
-    <row r="118" ht="107" customHeight="1">
+    <row r="118" ht="32" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11084,7 +11084,7 @@
       <c r="J118" s="1" t="inlineStr"/>
       <c r="K118" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L118" s="1" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="V118" s="1" t="inlineStr"/>
     </row>
-    <row r="119" ht="107" customHeight="1">
+    <row r="119" ht="32" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11172,7 +11172,7 @@
       <c r="J119" s="1" t="inlineStr"/>
       <c r="K119" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L119" s="1" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="V119" s="1" t="inlineStr"/>
     </row>
-    <row r="120" ht="107" customHeight="1">
+    <row r="120" ht="32" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11260,7 +11260,7 @@
       <c r="J120" s="1" t="inlineStr"/>
       <c r="K120" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L120" s="1" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="V120" s="1" t="inlineStr"/>
     </row>
-    <row r="121" ht="107" customHeight="1">
+    <row r="121" ht="32" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11348,7 +11348,7 @@
       <c r="J121" s="1" t="inlineStr"/>
       <c r="K121" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L121" s="1" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="V121" s="1" t="inlineStr"/>
     </row>
-    <row r="122" ht="107" customHeight="1">
+    <row r="122" ht="32" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11436,7 +11436,7 @@
       <c r="J122" s="1" t="inlineStr"/>
       <c r="K122" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L122" s="1" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="V122" s="1" t="inlineStr"/>
     </row>
-    <row r="123" ht="107" customHeight="1">
+    <row r="123" ht="32" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11524,7 +11524,7 @@
       <c r="J123" s="1" t="inlineStr"/>
       <c r="K123" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L123" s="1" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="V123" s="1" t="inlineStr"/>
     </row>
-    <row r="124" ht="107" customHeight="1">
+    <row r="124" ht="32" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11612,7 +11612,7 @@
       <c r="J124" s="1" t="inlineStr"/>
       <c r="K124" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L124" s="1" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="V124" s="1" t="inlineStr"/>
     </row>
-    <row r="125" ht="107" customHeight="1">
+    <row r="125" ht="32" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11700,7 +11700,7 @@
       <c r="J125" s="1" t="inlineStr"/>
       <c r="K125" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L125" s="1" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="V125" s="1" t="inlineStr"/>
     </row>
-    <row r="126" ht="107" customHeight="1">
+    <row r="126" ht="32" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11788,7 +11788,7 @@
       <c r="J126" s="1" t="inlineStr"/>
       <c r="K126" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L126" s="1" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="V126" s="1" t="inlineStr"/>
     </row>
-    <row r="127" ht="107" customHeight="1">
+    <row r="127" ht="32" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11876,7 +11876,7 @@
       <c r="J127" s="1" t="inlineStr"/>
       <c r="K127" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L127" s="1" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="V127" s="1" t="inlineStr"/>
     </row>
-    <row r="128" ht="107" customHeight="1">
+    <row r="128" ht="32" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11964,7 +11964,7 @@
       <c r="J128" s="1" t="inlineStr"/>
       <c r="K128" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L128" s="1" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="V128" s="1" t="inlineStr"/>
     </row>
-    <row r="129" ht="107" customHeight="1">
+    <row r="129" ht="32" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12052,7 +12052,7 @@
       <c r="J129" s="1" t="inlineStr"/>
       <c r="K129" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L129" s="1" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="V129" s="1" t="inlineStr"/>
     </row>
-    <row r="130" ht="107" customHeight="1">
+    <row r="130" ht="32" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12140,7 +12140,7 @@
       <c r="J130" s="1" t="inlineStr"/>
       <c r="K130" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L130" s="1" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="V130" s="1" t="inlineStr"/>
     </row>
-    <row r="131" ht="107" customHeight="1">
+    <row r="131" ht="32" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12228,7 +12228,7 @@
       <c r="J131" s="1" t="inlineStr"/>
       <c r="K131" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L131" s="1" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="V131" s="1" t="inlineStr"/>
     </row>
-    <row r="132" ht="107" customHeight="1">
+    <row r="132" ht="32" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12316,7 +12316,7 @@
       <c r="J132" s="1" t="inlineStr"/>
       <c r="K132" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L132" s="1" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="V132" s="1" t="inlineStr"/>
     </row>
-    <row r="133" ht="107" customHeight="1">
+    <row r="133" ht="32" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12404,7 +12404,7 @@
       <c r="J133" s="1" t="inlineStr"/>
       <c r="K133" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L133" s="1" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="V133" s="1" t="inlineStr"/>
     </row>
-    <row r="134" ht="107" customHeight="1">
+    <row r="134" ht="32" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12492,7 +12492,7 @@
       <c r="J134" s="1" t="inlineStr"/>
       <c r="K134" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L134" s="1" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="V134" s="1" t="inlineStr"/>
     </row>
-    <row r="135" ht="107" customHeight="1">
+    <row r="135" ht="32" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12580,7 +12580,7 @@
       <c r="J135" s="1" t="inlineStr"/>
       <c r="K135" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L135" s="1" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="V135" s="1" t="inlineStr"/>
     </row>
-    <row r="136" ht="107" customHeight="1">
+    <row r="136" ht="32" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12668,7 +12668,7 @@
       <c r="J136" s="1" t="inlineStr"/>
       <c r="K136" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L136" s="1" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="V136" s="1" t="inlineStr"/>
     </row>
-    <row r="137" ht="107" customHeight="1">
+    <row r="137" ht="32" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12756,7 +12756,7 @@
       <c r="J137" s="1" t="inlineStr"/>
       <c r="K137" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L137" s="1" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="V137" s="1" t="inlineStr"/>
     </row>
-    <row r="138" ht="107" customHeight="1">
+    <row r="138" ht="32" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12844,7 +12844,7 @@
       <c r="J138" s="1" t="inlineStr"/>
       <c r="K138" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L138" s="1" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="V138" s="1" t="inlineStr"/>
     </row>
-    <row r="139" ht="107" customHeight="1">
+    <row r="139" ht="32" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12932,7 +12932,7 @@
       <c r="J139" s="1" t="inlineStr"/>
       <c r="K139" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L139" s="1" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="V139" s="1" t="inlineStr"/>
     </row>
-    <row r="140" ht="107" customHeight="1">
+    <row r="140" ht="32" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13020,7 +13020,7 @@
       <c r="J140" s="1" t="inlineStr"/>
       <c r="K140" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L140" s="1" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="V140" s="1" t="inlineStr"/>
     </row>
-    <row r="141" ht="107" customHeight="1">
+    <row r="141" ht="32" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13108,7 +13108,7 @@
       <c r="J141" s="1" t="inlineStr"/>
       <c r="K141" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L141" s="1" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="V141" s="1" t="inlineStr"/>
     </row>
-    <row r="142" ht="107" customHeight="1">
+    <row r="142" ht="32" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13196,7 +13196,7 @@
       <c r="J142" s="1" t="inlineStr"/>
       <c r="K142" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L142" s="1" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="V142" s="1" t="inlineStr"/>
     </row>
-    <row r="143" ht="107" customHeight="1">
+    <row r="143" ht="32" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13284,7 +13284,7 @@
       <c r="J143" s="1" t="inlineStr"/>
       <c r="K143" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L143" s="1" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="V143" s="1" t="inlineStr"/>
     </row>
-    <row r="144" ht="107" customHeight="1">
+    <row r="144" ht="32" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13372,7 +13372,7 @@
       <c r="J144" s="1" t="inlineStr"/>
       <c r="K144" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L144" s="1" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="V144" s="1" t="inlineStr"/>
     </row>
-    <row r="145" ht="107" customHeight="1">
+    <row r="145" ht="32" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13460,7 +13460,7 @@
       <c r="J145" s="1" t="inlineStr"/>
       <c r="K145" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L145" s="1" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="V145" s="1" t="inlineStr"/>
     </row>
-    <row r="146" ht="107" customHeight="1">
+    <row r="146" ht="32" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13548,7 +13548,7 @@
       <c r="J146" s="1" t="inlineStr"/>
       <c r="K146" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L146" s="1" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="V146" s="1" t="inlineStr"/>
     </row>
-    <row r="147" ht="107" customHeight="1">
+    <row r="147" ht="32" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13636,7 +13636,7 @@
       <c r="J147" s="1" t="inlineStr"/>
       <c r="K147" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L147" s="1" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="V147" s="1" t="inlineStr"/>
     </row>
-    <row r="148" ht="107" customHeight="1">
+    <row r="148" ht="32" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13724,7 +13724,7 @@
       <c r="J148" s="1" t="inlineStr"/>
       <c r="K148" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L148" s="1" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="V148" s="1" t="inlineStr"/>
     </row>
-    <row r="149" ht="107" customHeight="1">
+    <row r="149" ht="32" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13812,7 +13812,7 @@
       <c r="J149" s="1" t="inlineStr"/>
       <c r="K149" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L149" s="1" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="V149" s="1" t="inlineStr"/>
     </row>
-    <row r="150" ht="107" customHeight="1">
+    <row r="150" ht="32" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13900,7 +13900,7 @@
       <c r="J150" s="1" t="inlineStr"/>
       <c r="K150" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L150" s="1" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="V150" s="1" t="inlineStr"/>
     </row>
-    <row r="151" ht="107" customHeight="1">
+    <row r="151" ht="32" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13988,7 +13988,7 @@
       <c r="J151" s="1" t="inlineStr"/>
       <c r="K151" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L151" s="1" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="V151" s="1" t="inlineStr"/>
     </row>
-    <row r="152" ht="107" customHeight="1">
+    <row r="152" ht="32" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14076,7 +14076,7 @@
       <c r="J152" s="1" t="inlineStr"/>
       <c r="K152" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L152" s="1" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="V152" s="1" t="inlineStr"/>
     </row>
-    <row r="153" ht="107" customHeight="1">
+    <row r="153" ht="32" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14164,7 +14164,7 @@
       <c r="J153" s="1" t="inlineStr"/>
       <c r="K153" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L153" s="1" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="V153" s="1" t="inlineStr"/>
     </row>
-    <row r="154" ht="107" customHeight="1">
+    <row r="154" ht="32" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14252,7 +14252,7 @@
       <c r="J154" s="1" t="inlineStr"/>
       <c r="K154" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L154" s="1" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="V154" s="1" t="inlineStr"/>
     </row>
-    <row r="155" ht="107" customHeight="1">
+    <row r="155" ht="32" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14340,7 +14340,7 @@
       <c r="J155" s="1" t="inlineStr"/>
       <c r="K155" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L155" s="1" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="V155" s="1" t="inlineStr"/>
     </row>
-    <row r="156" ht="107" customHeight="1">
+    <row r="156" ht="32" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14428,7 +14428,7 @@
       <c r="J156" s="1" t="inlineStr"/>
       <c r="K156" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L156" s="1" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="V156" s="1" t="inlineStr"/>
     </row>
-    <row r="157" ht="107" customHeight="1">
+    <row r="157" ht="32" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14516,7 +14516,7 @@
       <c r="J157" s="1" t="inlineStr"/>
       <c r="K157" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L157" s="1" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="V157" s="1" t="inlineStr"/>
     </row>
-    <row r="158" ht="107" customHeight="1">
+    <row r="158" ht="32" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14604,7 +14604,7 @@
       <c r="J158" s="1" t="inlineStr"/>
       <c r="K158" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L158" s="1" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="V158" s="1" t="inlineStr"/>
     </row>
-    <row r="159" ht="107" customHeight="1">
+    <row r="159" ht="32" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14692,7 +14692,7 @@
       <c r="J159" s="1" t="inlineStr"/>
       <c r="K159" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L159" s="1" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="V159" s="1" t="inlineStr"/>
     </row>
-    <row r="160" ht="107" customHeight="1">
+    <row r="160" ht="32" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14780,7 +14780,7 @@
       <c r="J160" s="1" t="inlineStr"/>
       <c r="K160" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L160" s="1" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="V160" s="1" t="inlineStr"/>
     </row>
-    <row r="161" ht="107" customHeight="1">
+    <row r="161" ht="32" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14868,7 +14868,7 @@
       <c r="J161" s="1" t="inlineStr"/>
       <c r="K161" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L161" s="1" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="V161" s="1" t="inlineStr"/>
     </row>
-    <row r="162" ht="126" customHeight="1">
+    <row r="162" ht="32" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14956,7 +14956,7 @@
       <c r="J162" s="1" t="inlineStr"/>
       <c r="K162" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L162" s="1" t="inlineStr">
@@ -15009,7 +15009,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="126" customHeight="1">
+    <row r="163" ht="32" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15048,7 +15048,7 @@
       <c r="J163" s="1" t="inlineStr"/>
       <c r="K163" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L163" s="1" t="inlineStr">
@@ -15101,7 +15101,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="126" customHeight="1">
+    <row r="164" ht="32" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15140,7 +15140,7 @@
       <c r="J164" s="1" t="inlineStr"/>
       <c r="K164" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L164" s="1" t="inlineStr">
@@ -15193,7 +15193,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="126" customHeight="1">
+    <row r="165" ht="32" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15232,7 +15232,7 @@
       <c r="J165" s="1" t="inlineStr"/>
       <c r="K165" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L165" s="1" t="inlineStr">
@@ -15285,7 +15285,7 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="126" customHeight="1">
+    <row r="166" ht="32" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15324,7 +15324,7 @@
       <c r="J166" s="1" t="inlineStr"/>
       <c r="K166" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L166" s="1" t="inlineStr">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="126" customHeight="1">
+    <row r="167" ht="32" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15416,7 +15416,7 @@
       <c r="J167" s="1" t="inlineStr"/>
       <c r="K167" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L167" s="1" t="inlineStr">
@@ -15469,7 +15469,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="126" customHeight="1">
+    <row r="168" ht="32" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15508,7 +15508,7 @@
       <c r="J168" s="1" t="inlineStr"/>
       <c r="K168" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L168" s="1" t="inlineStr">
@@ -15561,7 +15561,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="126" customHeight="1">
+    <row r="169" ht="32" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15600,7 +15600,7 @@
       <c r="J169" s="1" t="inlineStr"/>
       <c r="K169" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L169" s="1" t="inlineStr">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="126" customHeight="1">
+    <row r="170" ht="32" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15692,7 +15692,7 @@
       <c r="J170" s="1" t="inlineStr"/>
       <c r="K170" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L170" s="1" t="inlineStr">
@@ -15745,7 +15745,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="126" customHeight="1">
+    <row r="171" ht="32" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15784,7 +15784,7 @@
       <c r="J171" s="1" t="inlineStr"/>
       <c r="K171" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L171" s="1" t="inlineStr">
@@ -15837,7 +15837,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="126" customHeight="1">
+    <row r="172" ht="32" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15876,7 +15876,7 @@
       <c r="J172" s="1" t="inlineStr"/>
       <c r="K172" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L172" s="1" t="inlineStr">
@@ -15929,7 +15929,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="126" customHeight="1">
+    <row r="173" ht="32" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -15968,7 +15968,7 @@
       <c r="J173" s="1" t="inlineStr"/>
       <c r="K173" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L173" s="1" t="inlineStr">
@@ -16021,7 +16021,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="126" customHeight="1">
+    <row r="174" ht="32" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16060,7 +16060,7 @@
       <c r="J174" s="1" t="inlineStr"/>
       <c r="K174" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L174" s="1" t="inlineStr">
@@ -16113,7 +16113,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="126" customHeight="1">
+    <row r="175" ht="32" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16152,7 +16152,7 @@
       <c r="J175" s="1" t="inlineStr"/>
       <c r="K175" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L175" s="1" t="inlineStr">
@@ -16205,7 +16205,7 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="126" customHeight="1">
+    <row r="176" ht="32" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16244,7 +16244,7 @@
       <c r="J176" s="1" t="inlineStr"/>
       <c r="K176" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L176" s="1" t="inlineStr">
@@ -16297,7 +16297,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="126" customHeight="1">
+    <row r="177" ht="32" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16336,7 +16336,7 @@
       <c r="J177" s="1" t="inlineStr"/>
       <c r="K177" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L177" s="1" t="inlineStr">
@@ -16389,7 +16389,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="126" customHeight="1">
+    <row r="178" ht="32" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16428,7 +16428,7 @@
       <c r="J178" s="1" t="inlineStr"/>
       <c r="K178" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L178" s="1" t="inlineStr">
@@ -16481,7 +16481,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="126" customHeight="1">
+    <row r="179" ht="32" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16520,7 +16520,7 @@
       <c r="J179" s="1" t="inlineStr"/>
       <c r="K179" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L179" s="1" t="inlineStr">
@@ -16573,7 +16573,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="126" customHeight="1">
+    <row r="180" ht="32" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16612,7 +16612,7 @@
       <c r="J180" s="1" t="inlineStr"/>
       <c r="K180" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L180" s="1" t="inlineStr">
@@ -16665,7 +16665,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="126" customHeight="1">
+    <row r="181" ht="32" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16704,7 +16704,7 @@
       <c r="J181" s="1" t="inlineStr"/>
       <c r="K181" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L181" s="1" t="inlineStr">
@@ -16757,7 +16757,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="126" customHeight="1">
+    <row r="182" ht="32" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16796,7 +16796,7 @@
       <c r="J182" s="1" t="inlineStr"/>
       <c r="K182" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L182" s="1" t="inlineStr">
@@ -16849,7 +16849,7 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="126" customHeight="1">
+    <row r="183" ht="32" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16888,7 +16888,7 @@
       <c r="J183" s="1" t="inlineStr"/>
       <c r="K183" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L183" s="1" t="inlineStr">
@@ -16941,7 +16941,7 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="126" customHeight="1">
+    <row r="184" ht="32" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -16980,7 +16980,7 @@
       <c r="J184" s="1" t="inlineStr"/>
       <c r="K184" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L184" s="1" t="inlineStr">
@@ -17033,7 +17033,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="126" customHeight="1">
+    <row r="185" ht="32" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17072,7 +17072,7 @@
       <c r="J185" s="1" t="inlineStr"/>
       <c r="K185" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L185" s="1" t="inlineStr">
@@ -17125,7 +17125,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="126" customHeight="1">
+    <row r="186" ht="32" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17164,7 +17164,7 @@
       <c r="J186" s="1" t="inlineStr"/>
       <c r="K186" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L186" s="1" t="inlineStr">
@@ -17217,7 +17217,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="126" customHeight="1">
+    <row r="187" ht="32" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17256,7 +17256,7 @@
       <c r="J187" s="1" t="inlineStr"/>
       <c r="K187" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L187" s="1" t="inlineStr">
@@ -17309,7 +17309,7 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="126" customHeight="1">
+    <row r="188" ht="32" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17348,7 +17348,7 @@
       <c r="J188" s="1" t="inlineStr"/>
       <c r="K188" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L188" s="1" t="inlineStr">
@@ -17401,7 +17401,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="126" customHeight="1">
+    <row r="189" ht="32" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17440,7 +17440,7 @@
       <c r="J189" s="1" t="inlineStr"/>
       <c r="K189" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L189" s="1" t="inlineStr">
@@ -17493,7 +17493,7 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="126" customHeight="1">
+    <row r="190" ht="32" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17532,7 +17532,7 @@
       <c r="J190" s="1" t="inlineStr"/>
       <c r="K190" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L190" s="1" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="126" customHeight="1">
+    <row r="191" ht="32" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17624,7 +17624,7 @@
       <c r="J191" s="1" t="inlineStr"/>
       <c r="K191" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L191" s="1" t="inlineStr">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="126" customHeight="1">
+    <row r="192" ht="32" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17716,7 +17716,7 @@
       <c r="J192" s="1" t="inlineStr"/>
       <c r="K192" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L192" s="1" t="inlineStr">
@@ -17769,7 +17769,7 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="126" customHeight="1">
+    <row r="193" ht="32" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17808,7 +17808,7 @@
       <c r="J193" s="1" t="inlineStr"/>
       <c r="K193" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L193" s="1" t="inlineStr">
@@ -17861,7 +17861,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="126" customHeight="1">
+    <row r="194" ht="32" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17900,7 +17900,7 @@
       <c r="J194" s="1" t="inlineStr"/>
       <c r="K194" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L194" s="1" t="inlineStr">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="126" customHeight="1">
+    <row r="195" ht="32" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -17992,7 +17992,7 @@
       <c r="J195" s="1" t="inlineStr"/>
       <c r="K195" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L195" s="1" t="inlineStr">
@@ -18045,7 +18045,7 @@
         </is>
       </c>
     </row>
-    <row r="196" ht="126" customHeight="1">
+    <row r="196" ht="32" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18084,7 +18084,7 @@
       <c r="J196" s="1" t="inlineStr"/>
       <c r="K196" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L196" s="1" t="inlineStr">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="126" customHeight="1">
+    <row r="197" ht="32" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18176,7 +18176,7 @@
       <c r="J197" s="1" t="inlineStr"/>
       <c r="K197" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L197" s="1" t="inlineStr">
@@ -18229,7 +18229,7 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="126" customHeight="1">
+    <row r="198" ht="32" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18268,7 +18268,7 @@
       <c r="J198" s="1" t="inlineStr"/>
       <c r="K198" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L198" s="1" t="inlineStr">
@@ -18321,7 +18321,7 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="126" customHeight="1">
+    <row r="199" ht="32" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18360,7 +18360,7 @@
       <c r="J199" s="1" t="inlineStr"/>
       <c r="K199" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L199" s="1" t="inlineStr">
@@ -18413,7 +18413,7 @@
         </is>
       </c>
     </row>
-    <row r="200" ht="126" customHeight="1">
+    <row r="200" ht="32" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18452,7 +18452,7 @@
       <c r="J200" s="1" t="inlineStr"/>
       <c r="K200" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L200" s="1" t="inlineStr">
@@ -18505,7 +18505,7 @@
         </is>
       </c>
     </row>
-    <row r="201" ht="126" customHeight="1">
+    <row r="201" ht="32" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18544,7 +18544,7 @@
       <c r="J201" s="1" t="inlineStr"/>
       <c r="K201" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L201" s="1" t="inlineStr">
@@ -18597,7 +18597,7 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="126" customHeight="1">
+    <row r="202" ht="32" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18636,7 +18636,7 @@
       <c r="J202" s="1" t="inlineStr"/>
       <c r="K202" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L202" s="1" t="inlineStr">
@@ -18689,7 +18689,7 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="126" customHeight="1">
+    <row r="203" ht="32" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18728,7 +18728,7 @@
       <c r="J203" s="1" t="inlineStr"/>
       <c r="K203" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L203" s="1" t="inlineStr">
@@ -18781,7 +18781,7 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="126" customHeight="1">
+    <row r="204" ht="32" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18820,7 +18820,7 @@
       <c r="J204" s="1" t="inlineStr"/>
       <c r="K204" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L204" s="1" t="inlineStr">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="126" customHeight="1">
+    <row r="205" ht="32" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -18912,7 +18912,7 @@
       <c r="J205" s="1" t="inlineStr"/>
       <c r="K205" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L205" s="1" t="inlineStr">
@@ -18965,7 +18965,7 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="126" customHeight="1">
+    <row r="206" ht="32" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19004,7 +19004,7 @@
       <c r="J206" s="1" t="inlineStr"/>
       <c r="K206" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L206" s="1" t="inlineStr">
@@ -19057,7 +19057,7 @@
         </is>
       </c>
     </row>
-    <row r="207" ht="126" customHeight="1">
+    <row r="207" ht="32" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19096,7 +19096,7 @@
       <c r="J207" s="1" t="inlineStr"/>
       <c r="K207" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L207" s="1" t="inlineStr">
@@ -19149,7 +19149,7 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="126" customHeight="1">
+    <row r="208" ht="32" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19188,7 +19188,7 @@
       <c r="J208" s="1" t="inlineStr"/>
       <c r="K208" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L208" s="1" t="inlineStr">
@@ -19241,7 +19241,7 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="126" customHeight="1">
+    <row r="209" ht="32" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19280,7 +19280,7 @@
       <c r="J209" s="1" t="inlineStr"/>
       <c r="K209" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L209" s="1" t="inlineStr">
@@ -19333,7 +19333,7 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="126" customHeight="1">
+    <row r="210" ht="32" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19372,7 +19372,7 @@
       <c r="J210" s="1" t="inlineStr"/>
       <c r="K210" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L210" s="1" t="inlineStr">
@@ -19425,7 +19425,7 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="126" customHeight="1">
+    <row r="211" ht="32" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19464,7 +19464,7 @@
       <c r="J211" s="1" t="inlineStr"/>
       <c r="K211" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L211" s="1" t="inlineStr">
@@ -19517,7 +19517,7 @@
         </is>
       </c>
     </row>
-    <row r="212" ht="126" customHeight="1">
+    <row r="212" ht="32" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19556,7 +19556,7 @@
       <c r="J212" s="1" t="inlineStr"/>
       <c r="K212" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L212" s="1" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="126" customHeight="1">
+    <row r="213" ht="32" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19648,7 +19648,7 @@
       <c r="J213" s="1" t="inlineStr"/>
       <c r="K213" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L213" s="1" t="inlineStr">
@@ -19701,7 +19701,7 @@
         </is>
       </c>
     </row>
-    <row r="214" ht="126" customHeight="1">
+    <row r="214" ht="32" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19740,7 +19740,7 @@
       <c r="J214" s="1" t="inlineStr"/>
       <c r="K214" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L214" s="1" t="inlineStr">
@@ -19793,7 +19793,7 @@
         </is>
       </c>
     </row>
-    <row r="215" ht="126" customHeight="1">
+    <row r="215" ht="32" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19832,7 +19832,7 @@
       <c r="J215" s="1" t="inlineStr"/>
       <c r="K215" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L215" s="1" t="inlineStr">
@@ -19885,7 +19885,7 @@
         </is>
       </c>
     </row>
-    <row r="216" ht="126" customHeight="1">
+    <row r="216" ht="32" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -19924,7 +19924,7 @@
       <c r="J216" s="1" t="inlineStr"/>
       <c r="K216" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L216" s="1" t="inlineStr">
@@ -19977,7 +19977,7 @@
         </is>
       </c>
     </row>
-    <row r="217" ht="126" customHeight="1">
+    <row r="217" ht="32" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20016,7 +20016,7 @@
       <c r="J217" s="1" t="inlineStr"/>
       <c r="K217" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L217" s="1" t="inlineStr">
@@ -20069,7 +20069,7 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="126" customHeight="1">
+    <row r="218" ht="32" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20108,7 +20108,7 @@
       <c r="J218" s="1" t="inlineStr"/>
       <c r="K218" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L218" s="1" t="inlineStr">
@@ -20161,7 +20161,7 @@
         </is>
       </c>
     </row>
-    <row r="219" ht="126" customHeight="1">
+    <row r="219" ht="32" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20200,7 +20200,7 @@
       <c r="J219" s="1" t="inlineStr"/>
       <c r="K219" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L219" s="1" t="inlineStr">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
     </row>
-    <row r="220" ht="126" customHeight="1">
+    <row r="220" ht="32" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20292,7 +20292,7 @@
       <c r="J220" s="1" t="inlineStr"/>
       <c r="K220" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L220" s="1" t="inlineStr">
@@ -20345,7 +20345,7 @@
         </is>
       </c>
     </row>
-    <row r="221" ht="126" customHeight="1">
+    <row r="221" ht="32" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20384,7 +20384,7 @@
       <c r="J221" s="1" t="inlineStr"/>
       <c r="K221" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L221" s="1" t="inlineStr">
@@ -20437,7 +20437,7 @@
         </is>
       </c>
     </row>
-    <row r="222" ht="126" customHeight="1">
+    <row r="222" ht="32" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20476,7 +20476,7 @@
       <c r="J222" s="1" t="inlineStr"/>
       <c r="K222" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L222" s="1" t="inlineStr">
@@ -20529,7 +20529,7 @@
         </is>
       </c>
     </row>
-    <row r="223" ht="126" customHeight="1">
+    <row r="223" ht="32" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20568,7 +20568,7 @@
       <c r="J223" s="1" t="inlineStr"/>
       <c r="K223" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L223" s="1" t="inlineStr">
@@ -20621,7 +20621,7 @@
         </is>
       </c>
     </row>
-    <row r="224" ht="126" customHeight="1">
+    <row r="224" ht="32" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20660,7 +20660,7 @@
       <c r="J224" s="1" t="inlineStr"/>
       <c r="K224" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L224" s="1" t="inlineStr">
@@ -20713,7 +20713,7 @@
         </is>
       </c>
     </row>
-    <row r="225" ht="126" customHeight="1">
+    <row r="225" ht="32" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20752,7 +20752,7 @@
       <c r="J225" s="1" t="inlineStr"/>
       <c r="K225" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L225" s="1" t="inlineStr">
@@ -20805,7 +20805,7 @@
         </is>
       </c>
     </row>
-    <row r="226" ht="126" customHeight="1">
+    <row r="226" ht="32" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20844,7 +20844,7 @@
       <c r="J226" s="1" t="inlineStr"/>
       <c r="K226" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L226" s="1" t="inlineStr">
@@ -20897,7 +20897,7 @@
         </is>
       </c>
     </row>
-    <row r="227" ht="126" customHeight="1">
+    <row r="227" ht="32" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -20936,7 +20936,7 @@
       <c r="J227" s="1" t="inlineStr"/>
       <c r="K227" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L227" s="1" t="inlineStr">
@@ -20989,7 +20989,7 @@
         </is>
       </c>
     </row>
-    <row r="228" ht="126" customHeight="1">
+    <row r="228" ht="32" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21028,7 +21028,7 @@
       <c r="J228" s="1" t="inlineStr"/>
       <c r="K228" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L228" s="1" t="inlineStr">
@@ -21081,7 +21081,7 @@
         </is>
       </c>
     </row>
-    <row r="229" ht="126" customHeight="1">
+    <row r="229" ht="32" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21120,7 +21120,7 @@
       <c r="J229" s="1" t="inlineStr"/>
       <c r="K229" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L229" s="1" t="inlineStr">
@@ -21173,7 +21173,7 @@
         </is>
       </c>
     </row>
-    <row r="230" ht="126" customHeight="1">
+    <row r="230" ht="32" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21212,7 +21212,7 @@
       <c r="J230" s="1" t="inlineStr"/>
       <c r="K230" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L230" s="1" t="inlineStr">
@@ -21265,7 +21265,7 @@
         </is>
       </c>
     </row>
-    <row r="231" ht="126" customHeight="1">
+    <row r="231" ht="32" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21304,7 +21304,7 @@
       <c r="J231" s="1" t="inlineStr"/>
       <c r="K231" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L231" s="1" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
     </row>
-    <row r="232" ht="126" customHeight="1">
+    <row r="232" ht="32" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21396,7 +21396,7 @@
       <c r="J232" s="1" t="inlineStr"/>
       <c r="K232" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L232" s="1" t="inlineStr">
@@ -21449,7 +21449,7 @@
         </is>
       </c>
     </row>
-    <row r="233" ht="126" customHeight="1">
+    <row r="233" ht="32" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21488,7 +21488,7 @@
       <c r="J233" s="1" t="inlineStr"/>
       <c r="K233" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L233" s="1" t="inlineStr">
@@ -21541,7 +21541,7 @@
         </is>
       </c>
     </row>
-    <row r="234" ht="126" customHeight="1">
+    <row r="234" ht="32" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21580,7 +21580,7 @@
       <c r="J234" s="1" t="inlineStr"/>
       <c r="K234" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L234" s="1" t="inlineStr">
@@ -21633,7 +21633,7 @@
         </is>
       </c>
     </row>
-    <row r="235" ht="126" customHeight="1">
+    <row r="235" ht="32" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21672,7 +21672,7 @@
       <c r="J235" s="1" t="inlineStr"/>
       <c r="K235" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L235" s="1" t="inlineStr">
@@ -21725,7 +21725,7 @@
         </is>
       </c>
     </row>
-    <row r="236" ht="126" customHeight="1">
+    <row r="236" ht="32" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21764,7 +21764,7 @@
       <c r="J236" s="1" t="inlineStr"/>
       <c r="K236" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L236" s="1" t="inlineStr">
@@ -21817,7 +21817,7 @@
         </is>
       </c>
     </row>
-    <row r="237" ht="126" customHeight="1">
+    <row r="237" ht="32" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21856,7 +21856,7 @@
       <c r="J237" s="1" t="inlineStr"/>
       <c r="K237" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L237" s="1" t="inlineStr">
@@ -21909,7 +21909,7 @@
         </is>
       </c>
     </row>
-    <row r="238" ht="126" customHeight="1">
+    <row r="238" ht="32" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -21948,7 +21948,7 @@
       <c r="J238" s="1" t="inlineStr"/>
       <c r="K238" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L238" s="1" t="inlineStr">
@@ -22001,7 +22001,7 @@
         </is>
       </c>
     </row>
-    <row r="239" ht="126" customHeight="1">
+    <row r="239" ht="32" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22040,7 +22040,7 @@
       <c r="J239" s="1" t="inlineStr"/>
       <c r="K239" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L239" s="1" t="inlineStr">
@@ -22093,7 +22093,7 @@
         </is>
       </c>
     </row>
-    <row r="240" ht="126" customHeight="1">
+    <row r="240" ht="32" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22132,7 +22132,7 @@
       <c r="J240" s="1" t="inlineStr"/>
       <c r="K240" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L240" s="1" t="inlineStr">
@@ -22185,7 +22185,7 @@
         </is>
       </c>
     </row>
-    <row r="241" ht="126" customHeight="1">
+    <row r="241" ht="32" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22224,7 +22224,7 @@
       <c r="J241" s="1" t="inlineStr"/>
       <c r="K241" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L241" s="1" t="inlineStr">
@@ -22277,7 +22277,7 @@
         </is>
       </c>
     </row>
-    <row r="242" ht="126" customHeight="1">
+    <row r="242" ht="32" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22316,7 +22316,7 @@
       <c r="J242" s="1" t="inlineStr"/>
       <c r="K242" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L242" s="1" t="inlineStr">
@@ -22369,7 +22369,7 @@
         </is>
       </c>
     </row>
-    <row r="243" ht="126" customHeight="1">
+    <row r="243" ht="32" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22408,7 +22408,7 @@
       <c r="J243" s="1" t="inlineStr"/>
       <c r="K243" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L243" s="1" t="inlineStr">
@@ -22461,7 +22461,7 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="126" customHeight="1">
+    <row r="244" ht="32" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22500,7 +22500,7 @@
       <c r="J244" s="1" t="inlineStr"/>
       <c r="K244" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L244" s="1" t="inlineStr">
@@ -22553,7 +22553,7 @@
         </is>
       </c>
     </row>
-    <row r="245" ht="126" customHeight="1">
+    <row r="245" ht="32" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22592,7 +22592,7 @@
       <c r="J245" s="1" t="inlineStr"/>
       <c r="K245" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L245" s="1" t="inlineStr">
@@ -22645,7 +22645,7 @@
         </is>
       </c>
     </row>
-    <row r="246" ht="126" customHeight="1">
+    <row r="246" ht="32" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22684,7 +22684,7 @@
       <c r="J246" s="1" t="inlineStr"/>
       <c r="K246" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L246" s="1" t="inlineStr">
@@ -22737,7 +22737,7 @@
         </is>
       </c>
     </row>
-    <row r="247" ht="126" customHeight="1">
+    <row r="247" ht="32" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22776,7 +22776,7 @@
       <c r="J247" s="1" t="inlineStr"/>
       <c r="K247" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L247" s="1" t="inlineStr">
@@ -22829,7 +22829,7 @@
         </is>
       </c>
     </row>
-    <row r="248" ht="126" customHeight="1">
+    <row r="248" ht="32" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22868,7 +22868,7 @@
       <c r="J248" s="1" t="inlineStr"/>
       <c r="K248" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L248" s="1" t="inlineStr">
@@ -22921,7 +22921,7 @@
         </is>
       </c>
     </row>
-    <row r="249" ht="126" customHeight="1">
+    <row r="249" ht="32" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -22960,7 +22960,7 @@
       <c r="J249" s="1" t="inlineStr"/>
       <c r="K249" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L249" s="1" t="inlineStr">
@@ -23013,7 +23013,7 @@
         </is>
       </c>
     </row>
-    <row r="250" ht="126" customHeight="1">
+    <row r="250" ht="32" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23052,7 +23052,7 @@
       <c r="J250" s="1" t="inlineStr"/>
       <c r="K250" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L250" s="1" t="inlineStr">
@@ -23105,7 +23105,7 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="126" customHeight="1">
+    <row r="251" ht="32" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23144,7 +23144,7 @@
       <c r="J251" s="1" t="inlineStr"/>
       <c r="K251" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L251" s="1" t="inlineStr">
@@ -23197,7 +23197,7 @@
         </is>
       </c>
     </row>
-    <row r="252" ht="126" customHeight="1">
+    <row r="252" ht="32" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23236,7 +23236,7 @@
       <c r="J252" s="1" t="inlineStr"/>
       <c r="K252" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L252" s="1" t="inlineStr">
@@ -23289,7 +23289,7 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="126" customHeight="1">
+    <row r="253" ht="32" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23328,7 +23328,7 @@
       <c r="J253" s="1" t="inlineStr"/>
       <c r="K253" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L253" s="1" t="inlineStr">
@@ -23381,7 +23381,7 @@
         </is>
       </c>
     </row>
-    <row r="254" ht="126" customHeight="1">
+    <row r="254" ht="32" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23420,7 +23420,7 @@
       <c r="J254" s="1" t="inlineStr"/>
       <c r="K254" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L254" s="1" t="inlineStr">
@@ -23473,7 +23473,7 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="126" customHeight="1">
+    <row r="255" ht="32" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23512,7 +23512,7 @@
       <c r="J255" s="1" t="inlineStr"/>
       <c r="K255" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L255" s="1" t="inlineStr">
@@ -23565,7 +23565,7 @@
         </is>
       </c>
     </row>
-    <row r="256" ht="126" customHeight="1">
+    <row r="256" ht="32" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23604,7 +23604,7 @@
       <c r="J256" s="1" t="inlineStr"/>
       <c r="K256" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L256" s="1" t="inlineStr">
@@ -23657,7 +23657,7 @@
         </is>
       </c>
     </row>
-    <row r="257" ht="126" customHeight="1">
+    <row r="257" ht="32" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23696,7 +23696,7 @@
       <c r="J257" s="1" t="inlineStr"/>
       <c r="K257" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L257" s="1" t="inlineStr">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
     </row>
-    <row r="258" ht="107" customHeight="1">
+    <row r="258" ht="32" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23788,7 +23788,7 @@
       <c r="J258" s="1" t="inlineStr"/>
       <c r="K258" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L258" s="1" t="inlineStr">
@@ -23841,7 +23841,7 @@
         </is>
       </c>
     </row>
-    <row r="259" ht="107" customHeight="1">
+    <row r="259" ht="32" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23880,7 +23880,7 @@
       <c r="J259" s="1" t="inlineStr"/>
       <c r="K259" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L259" s="1" t="inlineStr">
@@ -23933,7 +23933,7 @@
         </is>
       </c>
     </row>
-    <row r="260" ht="107" customHeight="1">
+    <row r="260" ht="32" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -23972,7 +23972,7 @@
       <c r="J260" s="1" t="inlineStr"/>
       <c r="K260" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L260" s="1" t="inlineStr">
@@ -24025,7 +24025,7 @@
         </is>
       </c>
     </row>
-    <row r="261" ht="107" customHeight="1">
+    <row r="261" ht="32" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24064,7 +24064,7 @@
       <c r="J261" s="1" t="inlineStr"/>
       <c r="K261" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L261" s="1" t="inlineStr">
@@ -24117,7 +24117,7 @@
         </is>
       </c>
     </row>
-    <row r="262" ht="107" customHeight="1">
+    <row r="262" ht="32" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24156,7 +24156,7 @@
       <c r="J262" s="1" t="inlineStr"/>
       <c r="K262" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L262" s="1" t="inlineStr">
@@ -24209,7 +24209,7 @@
         </is>
       </c>
     </row>
-    <row r="263" ht="107" customHeight="1">
+    <row r="263" ht="32" customHeight="1">
       <c r="A263" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24248,7 +24248,7 @@
       <c r="J263" s="1" t="inlineStr"/>
       <c r="K263" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L263" s="1" t="inlineStr">
@@ -24301,7 +24301,7 @@
         </is>
       </c>
     </row>
-    <row r="264" ht="107" customHeight="1">
+    <row r="264" ht="32" customHeight="1">
       <c r="A264" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24340,7 +24340,7 @@
       <c r="J264" s="1" t="inlineStr"/>
       <c r="K264" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L264" s="1" t="inlineStr">
@@ -24393,7 +24393,7 @@
         </is>
       </c>
     </row>
-    <row r="265" ht="107" customHeight="1">
+    <row r="265" ht="32" customHeight="1">
       <c r="A265" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24432,7 +24432,7 @@
       <c r="J265" s="1" t="inlineStr"/>
       <c r="K265" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L265" s="1" t="inlineStr">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
     </row>
-    <row r="266" ht="107" customHeight="1">
+    <row r="266" ht="32" customHeight="1">
       <c r="A266" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24524,7 +24524,7 @@
       <c r="J266" s="1" t="inlineStr"/>
       <c r="K266" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L266" s="1" t="inlineStr">
@@ -24577,7 +24577,7 @@
         </is>
       </c>
     </row>
-    <row r="267" ht="107" customHeight="1">
+    <row r="267" ht="32" customHeight="1">
       <c r="A267" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24616,7 +24616,7 @@
       <c r="J267" s="1" t="inlineStr"/>
       <c r="K267" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L267" s="1" t="inlineStr">
@@ -24669,7 +24669,7 @@
         </is>
       </c>
     </row>
-    <row r="268" ht="107" customHeight="1">
+    <row r="268" ht="32" customHeight="1">
       <c r="A268" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24708,7 +24708,7 @@
       <c r="J268" s="1" t="inlineStr"/>
       <c r="K268" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L268" s="1" t="inlineStr">
@@ -24761,7 +24761,7 @@
         </is>
       </c>
     </row>
-    <row r="269" ht="107" customHeight="1">
+    <row r="269" ht="32" customHeight="1">
       <c r="A269" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24800,7 +24800,7 @@
       <c r="J269" s="1" t="inlineStr"/>
       <c r="K269" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L269" s="1" t="inlineStr">
@@ -24853,7 +24853,7 @@
         </is>
       </c>
     </row>
-    <row r="270" ht="107" customHeight="1">
+    <row r="270" ht="32" customHeight="1">
       <c r="A270" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24892,7 +24892,7 @@
       <c r="J270" s="1" t="inlineStr"/>
       <c r="K270" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L270" s="1" t="inlineStr">
@@ -24945,7 +24945,7 @@
         </is>
       </c>
     </row>
-    <row r="271" ht="107" customHeight="1">
+    <row r="271" ht="32" customHeight="1">
       <c r="A271" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -24984,7 +24984,7 @@
       <c r="J271" s="1" t="inlineStr"/>
       <c r="K271" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L271" s="1" t="inlineStr">
@@ -25037,7 +25037,7 @@
         </is>
       </c>
     </row>
-    <row r="272" ht="107" customHeight="1">
+    <row r="272" ht="32" customHeight="1">
       <c r="A272" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25076,7 +25076,7 @@
       <c r="J272" s="1" t="inlineStr"/>
       <c r="K272" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L272" s="1" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
     </row>
-    <row r="273" ht="107" customHeight="1">
+    <row r="273" ht="32" customHeight="1">
       <c r="A273" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25168,7 +25168,7 @@
       <c r="J273" s="1" t="inlineStr"/>
       <c r="K273" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L273" s="1" t="inlineStr">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
     </row>
-    <row r="274" ht="107" customHeight="1">
+    <row r="274" ht="32" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25260,7 +25260,7 @@
       <c r="J274" s="1" t="inlineStr"/>
       <c r="K274" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L274" s="1" t="inlineStr">
@@ -25313,7 +25313,7 @@
         </is>
       </c>
     </row>
-    <row r="275" ht="107" customHeight="1">
+    <row r="275" ht="32" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25352,7 +25352,7 @@
       <c r="J275" s="1" t="inlineStr"/>
       <c r="K275" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L275" s="1" t="inlineStr">
@@ -25405,7 +25405,7 @@
         </is>
       </c>
     </row>
-    <row r="276" ht="107" customHeight="1">
+    <row r="276" ht="32" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25444,7 +25444,7 @@
       <c r="J276" s="1" t="inlineStr"/>
       <c r="K276" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L276" s="1" t="inlineStr">
@@ -25497,7 +25497,7 @@
         </is>
       </c>
     </row>
-    <row r="277" ht="107" customHeight="1">
+    <row r="277" ht="32" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25536,7 +25536,7 @@
       <c r="J277" s="1" t="inlineStr"/>
       <c r="K277" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L277" s="1" t="inlineStr">
@@ -25589,7 +25589,7 @@
         </is>
       </c>
     </row>
-    <row r="278" ht="107" customHeight="1">
+    <row r="278" ht="32" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25628,7 +25628,7 @@
       <c r="J278" s="1" t="inlineStr"/>
       <c r="K278" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L278" s="1" t="inlineStr">
@@ -25681,7 +25681,7 @@
         </is>
       </c>
     </row>
-    <row r="279" ht="107" customHeight="1">
+    <row r="279" ht="32" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25720,7 +25720,7 @@
       <c r="J279" s="1" t="inlineStr"/>
       <c r="K279" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L279" s="1" t="inlineStr">
@@ -25773,7 +25773,7 @@
         </is>
       </c>
     </row>
-    <row r="280" ht="107" customHeight="1">
+    <row r="280" ht="32" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25812,7 +25812,7 @@
       <c r="J280" s="1" t="inlineStr"/>
       <c r="K280" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L280" s="1" t="inlineStr">
@@ -25865,7 +25865,7 @@
         </is>
       </c>
     </row>
-    <row r="281" ht="107" customHeight="1">
+    <row r="281" ht="32" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25904,7 +25904,7 @@
       <c r="J281" s="1" t="inlineStr"/>
       <c r="K281" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L281" s="1" t="inlineStr">
@@ -25957,7 +25957,7 @@
         </is>
       </c>
     </row>
-    <row r="282" ht="107" customHeight="1">
+    <row r="282" ht="32" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -25996,7 +25996,7 @@
       <c r="J282" s="1" t="inlineStr"/>
       <c r="K282" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L282" s="1" t="inlineStr">
@@ -26049,7 +26049,7 @@
         </is>
       </c>
     </row>
-    <row r="283" ht="107" customHeight="1">
+    <row r="283" ht="32" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26088,7 +26088,7 @@
       <c r="J283" s="1" t="inlineStr"/>
       <c r="K283" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L283" s="1" t="inlineStr">
@@ -26141,7 +26141,7 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="107" customHeight="1">
+    <row r="284" ht="32" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26180,7 +26180,7 @@
       <c r="J284" s="1" t="inlineStr"/>
       <c r="K284" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L284" s="1" t="inlineStr">
@@ -26233,7 +26233,7 @@
         </is>
       </c>
     </row>
-    <row r="285" ht="107" customHeight="1">
+    <row r="285" ht="32" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26272,7 +26272,7 @@
       <c r="J285" s="1" t="inlineStr"/>
       <c r="K285" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L285" s="1" t="inlineStr">
@@ -26325,7 +26325,7 @@
         </is>
       </c>
     </row>
-    <row r="286" ht="107" customHeight="1">
+    <row r="286" ht="32" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26364,7 +26364,7 @@
       <c r="J286" s="1" t="inlineStr"/>
       <c r="K286" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L286" s="1" t="inlineStr">
@@ -26417,7 +26417,7 @@
         </is>
       </c>
     </row>
-    <row r="287" ht="107" customHeight="1">
+    <row r="287" ht="32" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26456,7 +26456,7 @@
       <c r="J287" s="1" t="inlineStr"/>
       <c r="K287" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L287" s="1" t="inlineStr">
@@ -26509,7 +26509,7 @@
         </is>
       </c>
     </row>
-    <row r="288" ht="107" customHeight="1">
+    <row r="288" ht="32" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26548,7 +26548,7 @@
       <c r="J288" s="1" t="inlineStr"/>
       <c r="K288" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L288" s="1" t="inlineStr">
@@ -26601,7 +26601,7 @@
         </is>
       </c>
     </row>
-    <row r="289" ht="107" customHeight="1">
+    <row r="289" ht="32" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26640,7 +26640,7 @@
       <c r="J289" s="1" t="inlineStr"/>
       <c r="K289" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L289" s="1" t="inlineStr">
@@ -26693,7 +26693,7 @@
         </is>
       </c>
     </row>
-    <row r="290" ht="107" customHeight="1">
+    <row r="290" ht="32" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26732,7 +26732,7 @@
       <c r="J290" s="1" t="inlineStr"/>
       <c r="K290" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L290" s="1" t="inlineStr">
@@ -26785,7 +26785,7 @@
         </is>
       </c>
     </row>
-    <row r="291" ht="107" customHeight="1">
+    <row r="291" ht="32" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26824,7 +26824,7 @@
       <c r="J291" s="1" t="inlineStr"/>
       <c r="K291" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L291" s="1" t="inlineStr">
@@ -26877,7 +26877,7 @@
         </is>
       </c>
     </row>
-    <row r="292" ht="107" customHeight="1">
+    <row r="292" ht="32" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -26916,7 +26916,7 @@
       <c r="J292" s="1" t="inlineStr"/>
       <c r="K292" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L292" s="1" t="inlineStr">
@@ -26969,7 +26969,7 @@
         </is>
       </c>
     </row>
-    <row r="293" ht="107" customHeight="1">
+    <row r="293" ht="32" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27008,7 +27008,7 @@
       <c r="J293" s="1" t="inlineStr"/>
       <c r="K293" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L293" s="1" t="inlineStr">
@@ -27061,7 +27061,7 @@
         </is>
       </c>
     </row>
-    <row r="294" ht="107" customHeight="1">
+    <row r="294" ht="32" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27100,7 +27100,7 @@
       <c r="J294" s="1" t="inlineStr"/>
       <c r="K294" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L294" s="1" t="inlineStr">
@@ -27153,7 +27153,7 @@
         </is>
       </c>
     </row>
-    <row r="295" ht="107" customHeight="1">
+    <row r="295" ht="32" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27192,7 +27192,7 @@
       <c r="J295" s="1" t="inlineStr"/>
       <c r="K295" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L295" s="1" t="inlineStr">
@@ -27245,7 +27245,7 @@
         </is>
       </c>
     </row>
-    <row r="296" ht="107" customHeight="1">
+    <row r="296" ht="32" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27284,7 +27284,7 @@
       <c r="J296" s="1" t="inlineStr"/>
       <c r="K296" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L296" s="1" t="inlineStr">
@@ -27337,7 +27337,7 @@
         </is>
       </c>
     </row>
-    <row r="297" ht="107" customHeight="1">
+    <row r="297" ht="32" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27376,7 +27376,7 @@
       <c r="J297" s="1" t="inlineStr"/>
       <c r="K297" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L297" s="1" t="inlineStr">
@@ -27429,7 +27429,7 @@
         </is>
       </c>
     </row>
-    <row r="298" ht="107" customHeight="1">
+    <row r="298" ht="32" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27468,7 +27468,7 @@
       <c r="J298" s="1" t="inlineStr"/>
       <c r="K298" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L298" s="1" t="inlineStr">
@@ -27521,7 +27521,7 @@
         </is>
       </c>
     </row>
-    <row r="299" ht="107" customHeight="1">
+    <row r="299" ht="32" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27560,7 +27560,7 @@
       <c r="J299" s="1" t="inlineStr"/>
       <c r="K299" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L299" s="1" t="inlineStr">
@@ -27613,7 +27613,7 @@
         </is>
       </c>
     </row>
-    <row r="300" ht="107" customHeight="1">
+    <row r="300" ht="32" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27652,7 +27652,7 @@
       <c r="J300" s="1" t="inlineStr"/>
       <c r="K300" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L300" s="1" t="inlineStr">
@@ -27705,7 +27705,7 @@
         </is>
       </c>
     </row>
-    <row r="301" ht="107" customHeight="1">
+    <row r="301" ht="32" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27744,7 +27744,7 @@
       <c r="J301" s="1" t="inlineStr"/>
       <c r="K301" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L301" s="1" t="inlineStr">
@@ -27797,7 +27797,7 @@
         </is>
       </c>
     </row>
-    <row r="302" ht="107" customHeight="1">
+    <row r="302" ht="32" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27836,7 +27836,7 @@
       <c r="J302" s="1" t="inlineStr"/>
       <c r="K302" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L302" s="1" t="inlineStr">
@@ -27889,7 +27889,7 @@
         </is>
       </c>
     </row>
-    <row r="303" ht="107" customHeight="1">
+    <row r="303" ht="32" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -27928,7 +27928,7 @@
       <c r="J303" s="1" t="inlineStr"/>
       <c r="K303" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L303" s="1" t="inlineStr">
@@ -27981,7 +27981,7 @@
         </is>
       </c>
     </row>
-    <row r="304" ht="107" customHeight="1">
+    <row r="304" ht="32" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28020,7 +28020,7 @@
       <c r="J304" s="1" t="inlineStr"/>
       <c r="K304" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L304" s="1" t="inlineStr">
@@ -28073,7 +28073,7 @@
         </is>
       </c>
     </row>
-    <row r="305" ht="107" customHeight="1">
+    <row r="305" ht="32" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28112,7 +28112,7 @@
       <c r="J305" s="1" t="inlineStr"/>
       <c r="K305" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L305" s="1" t="inlineStr">
@@ -28165,7 +28165,7 @@
         </is>
       </c>
     </row>
-    <row r="306" ht="107" customHeight="1">
+    <row r="306" ht="32" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28204,7 +28204,7 @@
       <c r="J306" s="1" t="inlineStr"/>
       <c r="K306" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L306" s="1" t="inlineStr">
@@ -28257,7 +28257,7 @@
         </is>
       </c>
     </row>
-    <row r="307" ht="107" customHeight="1">
+    <row r="307" ht="32" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28296,7 +28296,7 @@
       <c r="J307" s="1" t="inlineStr"/>
       <c r="K307" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L307" s="1" t="inlineStr">
@@ -28349,7 +28349,7 @@
         </is>
       </c>
     </row>
-    <row r="308" ht="107" customHeight="1">
+    <row r="308" ht="32" customHeight="1">
       <c r="A308" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28388,7 +28388,7 @@
       <c r="J308" s="1" t="inlineStr"/>
       <c r="K308" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L308" s="1" t="inlineStr">
@@ -28441,7 +28441,7 @@
         </is>
       </c>
     </row>
-    <row r="309" ht="107" customHeight="1">
+    <row r="309" ht="32" customHeight="1">
       <c r="A309" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28480,7 +28480,7 @@
       <c r="J309" s="1" t="inlineStr"/>
       <c r="K309" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L309" s="1" t="inlineStr">
@@ -28533,7 +28533,7 @@
         </is>
       </c>
     </row>
-    <row r="310" ht="107" customHeight="1">
+    <row r="310" ht="32" customHeight="1">
       <c r="A310" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28572,7 +28572,7 @@
       <c r="J310" s="1" t="inlineStr"/>
       <c r="K310" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L310" s="1" t="inlineStr">
@@ -28625,7 +28625,7 @@
         </is>
       </c>
     </row>
-    <row r="311" ht="107" customHeight="1">
+    <row r="311" ht="32" customHeight="1">
       <c r="A311" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28664,7 +28664,7 @@
       <c r="J311" s="1" t="inlineStr"/>
       <c r="K311" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L311" s="1" t="inlineStr">
@@ -28717,7 +28717,7 @@
         </is>
       </c>
     </row>
-    <row r="312" ht="107" customHeight="1">
+    <row r="312" ht="32" customHeight="1">
       <c r="A312" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28756,7 +28756,7 @@
       <c r="J312" s="1" t="inlineStr"/>
       <c r="K312" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L312" s="1" t="inlineStr">
@@ -28809,7 +28809,7 @@
         </is>
       </c>
     </row>
-    <row r="313" ht="107" customHeight="1">
+    <row r="313" ht="32" customHeight="1">
       <c r="A313" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28848,7 +28848,7 @@
       <c r="J313" s="1" t="inlineStr"/>
       <c r="K313" s="1" t="inlineStr">
         <is>
-          <t>批次：2022年1号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2022年1号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：2G→1G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L313" s="1" t="inlineStr">
@@ -28901,7 +28901,7 @@
         </is>
       </c>
     </row>
-    <row r="314" ht="126" customHeight="1">
+    <row r="314" ht="32" customHeight="1">
       <c r="A314" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -28940,7 +28940,7 @@
       <c r="J314" s="1" t="inlineStr"/>
       <c r="K314" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L314" s="1" t="inlineStr">
@@ -28993,7 +28993,7 @@
         </is>
       </c>
     </row>
-    <row r="315" ht="126" customHeight="1">
+    <row r="315" ht="32" customHeight="1">
       <c r="A315" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29032,7 +29032,7 @@
       <c r="J315" s="1" t="inlineStr"/>
       <c r="K315" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L315" s="1" t="inlineStr">
@@ -29085,7 +29085,7 @@
         </is>
       </c>
     </row>
-    <row r="316" ht="126" customHeight="1">
+    <row r="316" ht="32" customHeight="1">
       <c r="A316" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29124,7 +29124,7 @@
       <c r="J316" s="1" t="inlineStr"/>
       <c r="K316" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L316" s="1" t="inlineStr">
@@ -29177,7 +29177,7 @@
         </is>
       </c>
     </row>
-    <row r="317" ht="126" customHeight="1">
+    <row r="317" ht="32" customHeight="1">
       <c r="A317" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29216,7 +29216,7 @@
       <c r="J317" s="1" t="inlineStr"/>
       <c r="K317" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L317" s="1" t="inlineStr">
@@ -29269,7 +29269,7 @@
         </is>
       </c>
     </row>
-    <row r="318" ht="126" customHeight="1">
+    <row r="318" ht="32" customHeight="1">
       <c r="A318" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29308,7 +29308,7 @@
       <c r="J318" s="1" t="inlineStr"/>
       <c r="K318" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L318" s="1" t="inlineStr">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
     </row>
-    <row r="319" ht="126" customHeight="1">
+    <row r="319" ht="32" customHeight="1">
       <c r="A319" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29400,7 +29400,7 @@
       <c r="J319" s="1" t="inlineStr"/>
       <c r="K319" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L319" s="1" t="inlineStr">
@@ -29453,7 +29453,7 @@
         </is>
       </c>
     </row>
-    <row r="320" ht="126" customHeight="1">
+    <row r="320" ht="32" customHeight="1">
       <c r="A320" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29492,7 +29492,7 @@
       <c r="J320" s="1" t="inlineStr"/>
       <c r="K320" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L320" s="1" t="inlineStr">
@@ -29545,7 +29545,7 @@
         </is>
       </c>
     </row>
-    <row r="321" ht="126" customHeight="1">
+    <row r="321" ht="32" customHeight="1">
       <c r="A321" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29584,7 +29584,7 @@
       <c r="J321" s="1" t="inlineStr"/>
       <c r="K321" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#008；位置：L001-F008；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L321" s="1" t="inlineStr">
@@ -29637,7 +29637,7 @@
         </is>
       </c>
     </row>
-    <row r="322" ht="126" customHeight="1">
+    <row r="322" ht="32" customHeight="1">
       <c r="A322" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29676,7 +29676,7 @@
       <c r="J322" s="1" t="inlineStr"/>
       <c r="K322" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#009；位置：L001-F009；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L322" s="1" t="inlineStr">
@@ -29729,7 +29729,7 @@
         </is>
       </c>
     </row>
-    <row r="323" ht="126" customHeight="1">
+    <row r="323" ht="32" customHeight="1">
       <c r="A323" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29768,7 +29768,7 @@
       <c r="J323" s="1" t="inlineStr"/>
       <c r="K323" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#010；位置：L001-F010；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L323" s="1" t="inlineStr">
@@ -29821,7 +29821,7 @@
         </is>
       </c>
     </row>
-    <row r="324" ht="126" customHeight="1">
+    <row r="324" ht="32" customHeight="1">
       <c r="A324" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29860,7 +29860,7 @@
       <c r="J324" s="1" t="inlineStr"/>
       <c r="K324" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#011；位置：L001-F011；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L324" s="1" t="inlineStr">
@@ -29913,7 +29913,7 @@
         </is>
       </c>
     </row>
-    <row r="325" ht="126" customHeight="1">
+    <row r="325" ht="32" customHeight="1">
       <c r="A325" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -29952,7 +29952,7 @@
       <c r="J325" s="1" t="inlineStr"/>
       <c r="K325" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R4#012；位置：L001-F012；源位置：B侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L325" s="1" t="inlineStr">
@@ -30005,7 +30005,7 @@
         </is>
       </c>
     </row>
-    <row r="326" ht="126" customHeight="1">
+    <row r="326" ht="32" customHeight="1">
       <c r="A326" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30044,7 +30044,7 @@
       <c r="J326" s="1" t="inlineStr"/>
       <c r="K326" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L326" s="1" t="inlineStr">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
     </row>
-    <row r="327" ht="126" customHeight="1">
+    <row r="327" ht="32" customHeight="1">
       <c r="A327" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30136,7 +30136,7 @@
       <c r="J327" s="1" t="inlineStr"/>
       <c r="K327" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L327" s="1" t="inlineStr">
@@ -30189,7 +30189,7 @@
         </is>
       </c>
     </row>
-    <row r="328" ht="126" customHeight="1">
+    <row r="328" ht="32" customHeight="1">
       <c r="A328" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30228,7 +30228,7 @@
       <c r="J328" s="1" t="inlineStr"/>
       <c r="K328" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L328" s="1" t="inlineStr">
@@ -30281,7 +30281,7 @@
         </is>
       </c>
     </row>
-    <row r="329" ht="126" customHeight="1">
+    <row r="329" ht="32" customHeight="1">
       <c r="A329" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30320,7 +30320,7 @@
       <c r="J329" s="1" t="inlineStr"/>
       <c r="K329" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L329" s="1" t="inlineStr">
@@ -30373,7 +30373,7 @@
         </is>
       </c>
     </row>
-    <row r="330" ht="126" customHeight="1">
+    <row r="330" ht="32" customHeight="1">
       <c r="A330" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30412,7 +30412,7 @@
       <c r="J330" s="1" t="inlineStr"/>
       <c r="K330" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L330" s="1" t="inlineStr">
@@ -30465,7 +30465,7 @@
         </is>
       </c>
     </row>
-    <row r="331" ht="126" customHeight="1">
+    <row r="331" ht="32" customHeight="1">
       <c r="A331" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30504,7 +30504,7 @@
       <c r="J331" s="1" t="inlineStr"/>
       <c r="K331" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L331" s="1" t="inlineStr">
@@ -30557,7 +30557,7 @@
         </is>
       </c>
     </row>
-    <row r="332" ht="126" customHeight="1">
+    <row r="332" ht="32" customHeight="1">
       <c r="A332" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30596,7 +30596,7 @@
       <c r="J332" s="1" t="inlineStr"/>
       <c r="K332" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L332" s="1" t="inlineStr">
@@ -30649,7 +30649,7 @@
         </is>
       </c>
     </row>
-    <row r="333" ht="126" customHeight="1">
+    <row r="333" ht="32" customHeight="1">
       <c r="A333" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30688,7 +30688,7 @@
       <c r="J333" s="1" t="inlineStr"/>
       <c r="K333" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#008；位置：L003-F008；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L333" s="1" t="inlineStr">
@@ -30741,7 +30741,7 @@
         </is>
       </c>
     </row>
-    <row r="334" ht="126" customHeight="1">
+    <row r="334" ht="32" customHeight="1">
       <c r="A334" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30780,7 +30780,7 @@
       <c r="J334" s="1" t="inlineStr"/>
       <c r="K334" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#009；位置：L003-F009；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L334" s="1" t="inlineStr">
@@ -30833,7 +30833,7 @@
         </is>
       </c>
     </row>
-    <row r="335" ht="126" customHeight="1">
+    <row r="335" ht="32" customHeight="1">
       <c r="A335" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30872,7 +30872,7 @@
       <c r="J335" s="1" t="inlineStr"/>
       <c r="K335" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#010；位置：L003-F010；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L335" s="1" t="inlineStr">
@@ -30925,7 +30925,7 @@
         </is>
       </c>
     </row>
-    <row r="336" ht="126" customHeight="1">
+    <row r="336" ht="32" customHeight="1">
       <c r="A336" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -30964,7 +30964,7 @@
       <c r="J336" s="1" t="inlineStr"/>
       <c r="K336" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#011；位置：L003-F011；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L336" s="1" t="inlineStr">
@@ -31017,7 +31017,7 @@
         </is>
       </c>
     </row>
-    <row r="337" ht="126" customHeight="1">
+    <row r="337" ht="32" customHeight="1">
       <c r="A337" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31056,7 +31056,7 @@
       <c r="J337" s="1" t="inlineStr"/>
       <c r="K337" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R5#012；位置：L003-F012；源位置：B侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L337" s="1" t="inlineStr">
@@ -31109,7 +31109,7 @@
         </is>
       </c>
     </row>
-    <row r="338" ht="126" customHeight="1">
+    <row r="338" ht="32" customHeight="1">
       <c r="A338" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31148,7 +31148,7 @@
       <c r="J338" s="1" t="inlineStr"/>
       <c r="K338" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L338" s="1" t="inlineStr">
@@ -31201,7 +31201,7 @@
         </is>
       </c>
     </row>
-    <row r="339" ht="126" customHeight="1">
+    <row r="339" ht="32" customHeight="1">
       <c r="A339" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31240,7 +31240,7 @@
       <c r="J339" s="1" t="inlineStr"/>
       <c r="K339" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L339" s="1" t="inlineStr">
@@ -31293,7 +31293,7 @@
         </is>
       </c>
     </row>
-    <row r="340" ht="126" customHeight="1">
+    <row r="340" ht="32" customHeight="1">
       <c r="A340" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31332,7 +31332,7 @@
       <c r="J340" s="1" t="inlineStr"/>
       <c r="K340" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L340" s="1" t="inlineStr">
@@ -31385,7 +31385,7 @@
         </is>
       </c>
     </row>
-    <row r="341" ht="126" customHeight="1">
+    <row r="341" ht="32" customHeight="1">
       <c r="A341" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31424,7 +31424,7 @@
       <c r="J341" s="1" t="inlineStr"/>
       <c r="K341" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L341" s="1" t="inlineStr">
@@ -31477,7 +31477,7 @@
         </is>
       </c>
     </row>
-    <row r="342" ht="126" customHeight="1">
+    <row r="342" ht="32" customHeight="1">
       <c r="A342" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31516,7 +31516,7 @@
       <c r="J342" s="1" t="inlineStr"/>
       <c r="K342" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L342" s="1" t="inlineStr">
@@ -31569,7 +31569,7 @@
         </is>
       </c>
     </row>
-    <row r="343" ht="126" customHeight="1">
+    <row r="343" ht="32" customHeight="1">
       <c r="A343" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31608,7 +31608,7 @@
       <c r="J343" s="1" t="inlineStr"/>
       <c r="K343" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L343" s="1" t="inlineStr">
@@ -31661,7 +31661,7 @@
         </is>
       </c>
     </row>
-    <row r="344" ht="126" customHeight="1">
+    <row r="344" ht="32" customHeight="1">
       <c r="A344" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31700,7 +31700,7 @@
       <c r="J344" s="1" t="inlineStr"/>
       <c r="K344" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L344" s="1" t="inlineStr">
@@ -31753,7 +31753,7 @@
         </is>
       </c>
     </row>
-    <row r="345" ht="126" customHeight="1">
+    <row r="345" ht="32" customHeight="1">
       <c r="A345" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31792,7 +31792,7 @@
       <c r="J345" s="1" t="inlineStr"/>
       <c r="K345" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#008；位置：L005-F008；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L345" s="1" t="inlineStr">
@@ -31845,7 +31845,7 @@
         </is>
       </c>
     </row>
-    <row r="346" ht="126" customHeight="1">
+    <row r="346" ht="32" customHeight="1">
       <c r="A346" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31884,7 +31884,7 @@
       <c r="J346" s="1" t="inlineStr"/>
       <c r="K346" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#009；位置：L005-F009；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L346" s="1" t="inlineStr">
@@ -31937,7 +31937,7 @@
         </is>
       </c>
     </row>
-    <row r="347" ht="126" customHeight="1">
+    <row r="347" ht="32" customHeight="1">
       <c r="A347" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -31976,7 +31976,7 @@
       <c r="J347" s="1" t="inlineStr"/>
       <c r="K347" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#010；位置：L005-F010；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L347" s="1" t="inlineStr">
@@ -32029,7 +32029,7 @@
         </is>
       </c>
     </row>
-    <row r="348" ht="126" customHeight="1">
+    <row r="348" ht="32" customHeight="1">
       <c r="A348" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32068,7 +32068,7 @@
       <c r="J348" s="1" t="inlineStr"/>
       <c r="K348" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#011；位置：L005-F011；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L348" s="1" t="inlineStr">
@@ -32121,7 +32121,7 @@
         </is>
       </c>
     </row>
-    <row r="349" ht="126" customHeight="1">
+    <row r="349" ht="32" customHeight="1">
       <c r="A349" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32160,7 +32160,7 @@
       <c r="J349" s="1" t="inlineStr"/>
       <c r="K349" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R6#012；位置：L005-F012；源位置：B侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L349" s="1" t="inlineStr">
@@ -32213,7 +32213,7 @@
         </is>
       </c>
     </row>
-    <row r="350" ht="126" customHeight="1">
+    <row r="350" ht="32" customHeight="1">
       <c r="A350" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32252,7 +32252,7 @@
       <c r="J350" s="1" t="inlineStr"/>
       <c r="K350" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L350" s="1" t="inlineStr">
@@ -32305,7 +32305,7 @@
         </is>
       </c>
     </row>
-    <row r="351" ht="126" customHeight="1">
+    <row r="351" ht="32" customHeight="1">
       <c r="A351" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32344,7 +32344,7 @@
       <c r="J351" s="1" t="inlineStr"/>
       <c r="K351" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L351" s="1" t="inlineStr">
@@ -32397,7 +32397,7 @@
         </is>
       </c>
     </row>
-    <row r="352" ht="126" customHeight="1">
+    <row r="352" ht="32" customHeight="1">
       <c r="A352" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32436,7 +32436,7 @@
       <c r="J352" s="1" t="inlineStr"/>
       <c r="K352" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L352" s="1" t="inlineStr">
@@ -32489,7 +32489,7 @@
         </is>
       </c>
     </row>
-    <row r="353" ht="126" customHeight="1">
+    <row r="353" ht="32" customHeight="1">
       <c r="A353" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32528,7 +32528,7 @@
       <c r="J353" s="1" t="inlineStr"/>
       <c r="K353" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L353" s="1" t="inlineStr">
@@ -32581,7 +32581,7 @@
         </is>
       </c>
     </row>
-    <row r="354" ht="126" customHeight="1">
+    <row r="354" ht="32" customHeight="1">
       <c r="A354" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32620,7 +32620,7 @@
       <c r="J354" s="1" t="inlineStr"/>
       <c r="K354" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L354" s="1" t="inlineStr">
@@ -32673,7 +32673,7 @@
         </is>
       </c>
     </row>
-    <row r="355" ht="126" customHeight="1">
+    <row r="355" ht="32" customHeight="1">
       <c r="A355" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32712,7 +32712,7 @@
       <c r="J355" s="1" t="inlineStr"/>
       <c r="K355" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L355" s="1" t="inlineStr">
@@ -32765,7 +32765,7 @@
         </is>
       </c>
     </row>
-    <row r="356" ht="126" customHeight="1">
+    <row r="356" ht="32" customHeight="1">
       <c r="A356" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32804,7 +32804,7 @@
       <c r="J356" s="1" t="inlineStr"/>
       <c r="K356" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L356" s="1" t="inlineStr">
@@ -32857,7 +32857,7 @@
         </is>
       </c>
     </row>
-    <row r="357" ht="126" customHeight="1">
+    <row r="357" ht="32" customHeight="1">
       <c r="A357" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32896,7 +32896,7 @@
       <c r="J357" s="1" t="inlineStr"/>
       <c r="K357" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#008；位置：L007-F008；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L357" s="1" t="inlineStr">
@@ -32949,7 +32949,7 @@
         </is>
       </c>
     </row>
-    <row r="358" ht="126" customHeight="1">
+    <row r="358" ht="32" customHeight="1">
       <c r="A358" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -32988,7 +32988,7 @@
       <c r="J358" s="1" t="inlineStr"/>
       <c r="K358" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#009；位置：L007-F009；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L358" s="1" t="inlineStr">
@@ -33041,7 +33041,7 @@
         </is>
       </c>
     </row>
-    <row r="359" ht="126" customHeight="1">
+    <row r="359" ht="32" customHeight="1">
       <c r="A359" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33080,7 +33080,7 @@
       <c r="J359" s="1" t="inlineStr"/>
       <c r="K359" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#010；位置：L007-F010；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L359" s="1" t="inlineStr">
@@ -33133,7 +33133,7 @@
         </is>
       </c>
     </row>
-    <row r="360" ht="126" customHeight="1">
+    <row r="360" ht="32" customHeight="1">
       <c r="A360" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33172,7 +33172,7 @@
       <c r="J360" s="1" t="inlineStr"/>
       <c r="K360" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#011；位置：L007-F011；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L360" s="1" t="inlineStr">
@@ -33225,7 +33225,7 @@
         </is>
       </c>
     </row>
-    <row r="361" ht="126" customHeight="1">
+    <row r="361" ht="32" customHeight="1">
       <c r="A361" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33264,7 +33264,7 @@
       <c r="J361" s="1" t="inlineStr"/>
       <c r="K361" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R7#012；位置：L007-F012；源位置：B侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L361" s="1" t="inlineStr">
@@ -33317,7 +33317,7 @@
         </is>
       </c>
     </row>
-    <row r="362" ht="126" customHeight="1">
+    <row r="362" ht="32" customHeight="1">
       <c r="A362" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33356,7 +33356,7 @@
       <c r="J362" s="1" t="inlineStr"/>
       <c r="K362" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L362" s="1" t="inlineStr">
@@ -33409,7 +33409,7 @@
         </is>
       </c>
     </row>
-    <row r="363" ht="126" customHeight="1">
+    <row r="363" ht="32" customHeight="1">
       <c r="A363" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33448,7 +33448,7 @@
       <c r="J363" s="1" t="inlineStr"/>
       <c r="K363" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L363" s="1" t="inlineStr">
@@ -33501,7 +33501,7 @@
         </is>
       </c>
     </row>
-    <row r="364" ht="126" customHeight="1">
+    <row r="364" ht="32" customHeight="1">
       <c r="A364" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33540,7 +33540,7 @@
       <c r="J364" s="1" t="inlineStr"/>
       <c r="K364" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L364" s="1" t="inlineStr">
@@ -33593,7 +33593,7 @@
         </is>
       </c>
     </row>
-    <row r="365" ht="126" customHeight="1">
+    <row r="365" ht="32" customHeight="1">
       <c r="A365" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33632,7 +33632,7 @@
       <c r="J365" s="1" t="inlineStr"/>
       <c r="K365" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L365" s="1" t="inlineStr">
@@ -33685,7 +33685,7 @@
         </is>
       </c>
     </row>
-    <row r="366" ht="126" customHeight="1">
+    <row r="366" ht="32" customHeight="1">
       <c r="A366" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33724,7 +33724,7 @@
       <c r="J366" s="1" t="inlineStr"/>
       <c r="K366" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L366" s="1" t="inlineStr">
@@ -33777,7 +33777,7 @@
         </is>
       </c>
     </row>
-    <row r="367" ht="126" customHeight="1">
+    <row r="367" ht="32" customHeight="1">
       <c r="A367" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33816,7 +33816,7 @@
       <c r="J367" s="1" t="inlineStr"/>
       <c r="K367" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L367" s="1" t="inlineStr">
@@ -33869,7 +33869,7 @@
         </is>
       </c>
     </row>
-    <row r="368" ht="126" customHeight="1">
+    <row r="368" ht="32" customHeight="1">
       <c r="A368" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -33908,7 +33908,7 @@
       <c r="J368" s="1" t="inlineStr"/>
       <c r="K368" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L368" s="1" t="inlineStr">
@@ -33961,7 +33961,7 @@
         </is>
       </c>
     </row>
-    <row r="369" ht="126" customHeight="1">
+    <row r="369" ht="32" customHeight="1">
       <c r="A369" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34000,7 +34000,7 @@
       <c r="J369" s="1" t="inlineStr"/>
       <c r="K369" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#008；位置：R001-F008；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L369" s="1" t="inlineStr">
@@ -34053,7 +34053,7 @@
         </is>
       </c>
     </row>
-    <row r="370" ht="126" customHeight="1">
+    <row r="370" ht="32" customHeight="1">
       <c r="A370" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34092,7 +34092,7 @@
       <c r="J370" s="1" t="inlineStr"/>
       <c r="K370" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#009；位置：R001-F009；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L370" s="1" t="inlineStr">
@@ -34145,7 +34145,7 @@
         </is>
       </c>
     </row>
-    <row r="371" ht="126" customHeight="1">
+    <row r="371" ht="32" customHeight="1">
       <c r="A371" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34184,7 +34184,7 @@
       <c r="J371" s="1" t="inlineStr"/>
       <c r="K371" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#010；位置：R001-F010；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L371" s="1" t="inlineStr">
@@ -34237,7 +34237,7 @@
         </is>
       </c>
     </row>
-    <row r="372" ht="126" customHeight="1">
+    <row r="372" ht="32" customHeight="1">
       <c r="A372" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34276,7 +34276,7 @@
       <c r="J372" s="1" t="inlineStr"/>
       <c r="K372" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#011；位置：R001-F011；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L372" s="1" t="inlineStr">
@@ -34329,7 +34329,7 @@
         </is>
       </c>
     </row>
-    <row r="373" ht="126" customHeight="1">
+    <row r="373" ht="32" customHeight="1">
       <c r="A373" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34368,7 +34368,7 @@
       <c r="J373" s="1" t="inlineStr"/>
       <c r="K373" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R8#012；位置：R001-F012；源位置：A侧第1排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L373" s="1" t="inlineStr">
@@ -34421,7 +34421,7 @@
         </is>
       </c>
     </row>
-    <row r="374" ht="126" customHeight="1">
+    <row r="374" ht="32" customHeight="1">
       <c r="A374" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34460,7 +34460,7 @@
       <c r="J374" s="1" t="inlineStr"/>
       <c r="K374" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L374" s="1" t="inlineStr">
@@ -34513,7 +34513,7 @@
         </is>
       </c>
     </row>
-    <row r="375" ht="126" customHeight="1">
+    <row r="375" ht="32" customHeight="1">
       <c r="A375" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34552,7 +34552,7 @@
       <c r="J375" s="1" t="inlineStr"/>
       <c r="K375" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L375" s="1" t="inlineStr">
@@ -34605,7 +34605,7 @@
         </is>
       </c>
     </row>
-    <row r="376" ht="126" customHeight="1">
+    <row r="376" ht="32" customHeight="1">
       <c r="A376" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34644,7 +34644,7 @@
       <c r="J376" s="1" t="inlineStr"/>
       <c r="K376" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L376" s="1" t="inlineStr">
@@ -34697,7 +34697,7 @@
         </is>
       </c>
     </row>
-    <row r="377" ht="126" customHeight="1">
+    <row r="377" ht="32" customHeight="1">
       <c r="A377" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34736,7 +34736,7 @@
       <c r="J377" s="1" t="inlineStr"/>
       <c r="K377" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L377" s="1" t="inlineStr">
@@ -34789,7 +34789,7 @@
         </is>
       </c>
     </row>
-    <row r="378" ht="126" customHeight="1">
+    <row r="378" ht="32" customHeight="1">
       <c r="A378" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34828,7 +34828,7 @@
       <c r="J378" s="1" t="inlineStr"/>
       <c r="K378" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L378" s="1" t="inlineStr">
@@ -34881,7 +34881,7 @@
         </is>
       </c>
     </row>
-    <row r="379" ht="126" customHeight="1">
+    <row r="379" ht="32" customHeight="1">
       <c r="A379" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -34920,7 +34920,7 @@
       <c r="J379" s="1" t="inlineStr"/>
       <c r="K379" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L379" s="1" t="inlineStr">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
     </row>
-    <row r="380" ht="126" customHeight="1">
+    <row r="380" ht="32" customHeight="1">
       <c r="A380" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35012,7 +35012,7 @@
       <c r="J380" s="1" t="inlineStr"/>
       <c r="K380" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L380" s="1" t="inlineStr">
@@ -35065,7 +35065,7 @@
         </is>
       </c>
     </row>
-    <row r="381" ht="126" customHeight="1">
+    <row r="381" ht="32" customHeight="1">
       <c r="A381" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35104,7 +35104,7 @@
       <c r="J381" s="1" t="inlineStr"/>
       <c r="K381" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#008；位置：R003-F008；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L381" s="1" t="inlineStr">
@@ -35157,7 +35157,7 @@
         </is>
       </c>
     </row>
-    <row r="382" ht="126" customHeight="1">
+    <row r="382" ht="32" customHeight="1">
       <c r="A382" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35196,7 +35196,7 @@
       <c r="J382" s="1" t="inlineStr"/>
       <c r="K382" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#009；位置：R003-F009；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L382" s="1" t="inlineStr">
@@ -35249,7 +35249,7 @@
         </is>
       </c>
     </row>
-    <row r="383" ht="126" customHeight="1">
+    <row r="383" ht="32" customHeight="1">
       <c r="A383" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35288,7 +35288,7 @@
       <c r="J383" s="1" t="inlineStr"/>
       <c r="K383" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#010；位置：R003-F010；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L383" s="1" t="inlineStr">
@@ -35341,7 +35341,7 @@
         </is>
       </c>
     </row>
-    <row r="384" ht="126" customHeight="1">
+    <row r="384" ht="32" customHeight="1">
       <c r="A384" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35380,7 +35380,7 @@
       <c r="J384" s="1" t="inlineStr"/>
       <c r="K384" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#011；位置：R003-F011；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L384" s="1" t="inlineStr">
@@ -35433,7 +35433,7 @@
         </is>
       </c>
     </row>
-    <row r="385" ht="126" customHeight="1">
+    <row r="385" ht="32" customHeight="1">
       <c r="A385" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35472,7 +35472,7 @@
       <c r="J385" s="1" t="inlineStr"/>
       <c r="K385" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R9#012；位置：R003-F012；源位置：A侧第3排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L385" s="1" t="inlineStr">
@@ -35525,7 +35525,7 @@
         </is>
       </c>
     </row>
-    <row r="386" ht="126" customHeight="1">
+    <row r="386" ht="32" customHeight="1">
       <c r="A386" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35564,7 +35564,7 @@
       <c r="J386" s="1" t="inlineStr"/>
       <c r="K386" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L386" s="1" t="inlineStr">
@@ -35617,7 +35617,7 @@
         </is>
       </c>
     </row>
-    <row r="387" ht="126" customHeight="1">
+    <row r="387" ht="32" customHeight="1">
       <c r="A387" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35656,7 +35656,7 @@
       <c r="J387" s="1" t="inlineStr"/>
       <c r="K387" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L387" s="1" t="inlineStr">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
     </row>
-    <row r="388" ht="126" customHeight="1">
+    <row r="388" ht="32" customHeight="1">
       <c r="A388" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35748,7 +35748,7 @@
       <c r="J388" s="1" t="inlineStr"/>
       <c r="K388" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L388" s="1" t="inlineStr">
@@ -35801,7 +35801,7 @@
         </is>
       </c>
     </row>
-    <row r="389" ht="126" customHeight="1">
+    <row r="389" ht="32" customHeight="1">
       <c r="A389" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35840,7 +35840,7 @@
       <c r="J389" s="1" t="inlineStr"/>
       <c r="K389" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L389" s="1" t="inlineStr">
@@ -35893,7 +35893,7 @@
         </is>
       </c>
     </row>
-    <row r="390" ht="126" customHeight="1">
+    <row r="390" ht="32" customHeight="1">
       <c r="A390" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -35932,7 +35932,7 @@
       <c r="J390" s="1" t="inlineStr"/>
       <c r="K390" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L390" s="1" t="inlineStr">
@@ -35985,7 +35985,7 @@
         </is>
       </c>
     </row>
-    <row r="391" ht="126" customHeight="1">
+    <row r="391" ht="32" customHeight="1">
       <c r="A391" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36024,7 +36024,7 @@
       <c r="J391" s="1" t="inlineStr"/>
       <c r="K391" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L391" s="1" t="inlineStr">
@@ -36077,7 +36077,7 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="126" customHeight="1">
+    <row r="392" ht="32" customHeight="1">
       <c r="A392" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36116,7 +36116,7 @@
       <c r="J392" s="1" t="inlineStr"/>
       <c r="K392" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L392" s="1" t="inlineStr">
@@ -36169,7 +36169,7 @@
         </is>
       </c>
     </row>
-    <row r="393" ht="126" customHeight="1">
+    <row r="393" ht="32" customHeight="1">
       <c r="A393" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36208,7 +36208,7 @@
       <c r="J393" s="1" t="inlineStr"/>
       <c r="K393" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#008；位置：R005-F008；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L393" s="1" t="inlineStr">
@@ -36261,7 +36261,7 @@
         </is>
       </c>
     </row>
-    <row r="394" ht="126" customHeight="1">
+    <row r="394" ht="32" customHeight="1">
       <c r="A394" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36300,7 +36300,7 @@
       <c r="J394" s="1" t="inlineStr"/>
       <c r="K394" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#009；位置：R005-F009；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L394" s="1" t="inlineStr">
@@ -36353,7 +36353,7 @@
         </is>
       </c>
     </row>
-    <row r="395" ht="126" customHeight="1">
+    <row r="395" ht="32" customHeight="1">
       <c r="A395" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36392,7 +36392,7 @@
       <c r="J395" s="1" t="inlineStr"/>
       <c r="K395" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#010；位置：R005-F010；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L395" s="1" t="inlineStr">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
     </row>
-    <row r="396" ht="126" customHeight="1">
+    <row r="396" ht="32" customHeight="1">
       <c r="A396" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36484,7 +36484,7 @@
       <c r="J396" s="1" t="inlineStr"/>
       <c r="K396" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#011；位置：R005-F011；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L396" s="1" t="inlineStr">
@@ -36537,7 +36537,7 @@
         </is>
       </c>
     </row>
-    <row r="397" ht="126" customHeight="1">
+    <row r="397" ht="32" customHeight="1">
       <c r="A397" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36576,7 +36576,7 @@
       <c r="J397" s="1" t="inlineStr"/>
       <c r="K397" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R10#012；位置：R005-F012；源位置：A侧第5排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L397" s="1" t="inlineStr">
@@ -36629,7 +36629,7 @@
         </is>
       </c>
     </row>
-    <row r="398" ht="126" customHeight="1">
+    <row r="398" ht="32" customHeight="1">
       <c r="A398" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36668,7 +36668,7 @@
       <c r="J398" s="1" t="inlineStr"/>
       <c r="K398" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F001=回路1底弯段→Φ54×7.5 SA-213TP347H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L398" s="1" t="inlineStr">
@@ -36721,7 +36721,7 @@
         </is>
       </c>
     </row>
-    <row r="399" ht="126" customHeight="1">
+    <row r="399" ht="32" customHeight="1">
       <c r="A399" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36760,7 +36760,7 @@
       <c r="J399" s="1" t="inlineStr"/>
       <c r="K399" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F002=回路2底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L399" s="1" t="inlineStr">
@@ -36813,7 +36813,7 @@
         </is>
       </c>
     </row>
-    <row r="400" ht="126" customHeight="1">
+    <row r="400" ht="32" customHeight="1">
       <c r="A400" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36852,7 +36852,7 @@
       <c r="J400" s="1" t="inlineStr"/>
       <c r="K400" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F003=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L400" s="1" t="inlineStr">
@@ -36905,7 +36905,7 @@
         </is>
       </c>
     </row>
-    <row r="401" ht="126" customHeight="1">
+    <row r="401" ht="32" customHeight="1">
       <c r="A401" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -36944,7 +36944,7 @@
       <c r="J401" s="1" t="inlineStr"/>
       <c r="K401" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L401" s="1" t="inlineStr">
@@ -36997,7 +36997,7 @@
         </is>
       </c>
     </row>
-    <row r="402" ht="126" customHeight="1">
+    <row r="402" ht="32" customHeight="1">
       <c r="A402" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37036,7 +37036,7 @@
       <c r="J402" s="1" t="inlineStr"/>
       <c r="K402" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L402" s="1" t="inlineStr">
@@ -37089,7 +37089,7 @@
         </is>
       </c>
     </row>
-    <row r="403" ht="126" customHeight="1">
+    <row r="403" ht="32" customHeight="1">
       <c r="A403" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37128,7 +37128,7 @@
       <c r="J403" s="1" t="inlineStr"/>
       <c r="K403" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L403" s="1" t="inlineStr">
@@ -37181,7 +37181,7 @@
         </is>
       </c>
     </row>
-    <row r="404" ht="126" customHeight="1">
+    <row r="404" ht="32" customHeight="1">
       <c r="A404" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37220,7 +37220,7 @@
       <c r="J404" s="1" t="inlineStr"/>
       <c r="K404" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L404" s="1" t="inlineStr">
@@ -37273,7 +37273,7 @@
         </is>
       </c>
     </row>
-    <row r="405" ht="126" customHeight="1">
+    <row r="405" ht="32" customHeight="1">
       <c r="A405" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37312,7 +37312,7 @@
       <c r="J405" s="1" t="inlineStr"/>
       <c r="K405" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#008；位置：R007-F008；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L405" s="1" t="inlineStr">
@@ -37365,7 +37365,7 @@
         </is>
       </c>
     </row>
-    <row r="406" ht="126" customHeight="1">
+    <row r="406" ht="32" customHeight="1">
       <c r="A406" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37404,7 +37404,7 @@
       <c r="J406" s="1" t="inlineStr"/>
       <c r="K406" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#009；位置：R007-F009；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L406" s="1" t="inlineStr">
@@ -37457,7 +37457,7 @@
         </is>
       </c>
     </row>
-    <row r="407" ht="126" customHeight="1">
+    <row r="407" ht="32" customHeight="1">
       <c r="A407" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37496,7 +37496,7 @@
       <c r="J407" s="1" t="inlineStr"/>
       <c r="K407" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#010；位置：R007-F010；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L407" s="1" t="inlineStr">
@@ -37549,7 +37549,7 @@
         </is>
       </c>
     </row>
-    <row r="408" ht="126" customHeight="1">
+    <row r="408" ht="32" customHeight="1">
       <c r="A408" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37588,7 +37588,7 @@
       <c r="J408" s="1" t="inlineStr"/>
       <c r="K408" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#011；位置：R007-F011；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F011=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L408" s="1" t="inlineStr">
@@ -37641,7 +37641,7 @@
         </is>
       </c>
     </row>
-    <row r="409" ht="126" customHeight="1">
+    <row r="409" ht="32" customHeight="1">
       <c r="A409" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37680,7 +37680,7 @@
       <c r="J409" s="1" t="inlineStr"/>
       <c r="K409" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R11#012；位置：R007-F012；源位置：A侧第7排炉前至炉后数1-12个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP347H，2、3、4为304H，5、6、7为T91，8、9、10、11为12CrMoVG，12为T91。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按回路分段基准映射：F012=回路12底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L409" s="1" t="inlineStr">
@@ -37733,7 +37733,7 @@
         </is>
       </c>
     </row>
-    <row r="410" ht="107" customHeight="1">
+    <row r="410" ht="32" customHeight="1">
       <c r="A410" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37772,7 +37772,7 @@
       <c r="J410" s="1" t="inlineStr"/>
       <c r="K410" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#001；位置：L001-F001；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L410" s="1" t="inlineStr">
@@ -37825,7 +37825,7 @@
         </is>
       </c>
     </row>
-    <row r="411" ht="107" customHeight="1">
+    <row r="411" ht="32" customHeight="1">
       <c r="A411" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37864,7 +37864,7 @@
       <c r="J411" s="1" t="inlineStr"/>
       <c r="K411" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#002；位置：L001-F002；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L411" s="1" t="inlineStr">
@@ -37917,7 +37917,7 @@
         </is>
       </c>
     </row>
-    <row r="412" ht="107" customHeight="1">
+    <row r="412" ht="32" customHeight="1">
       <c r="A412" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -37956,7 +37956,7 @@
       <c r="J412" s="1" t="inlineStr"/>
       <c r="K412" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#003；位置：L001-F003；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L412" s="1" t="inlineStr">
@@ -38009,7 +38009,7 @@
         </is>
       </c>
     </row>
-    <row r="413" ht="107" customHeight="1">
+    <row r="413" ht="32" customHeight="1">
       <c r="A413" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38048,7 +38048,7 @@
       <c r="J413" s="1" t="inlineStr"/>
       <c r="K413" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#004；位置：L001-F004；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L413" s="1" t="inlineStr">
@@ -38101,7 +38101,7 @@
         </is>
       </c>
     </row>
-    <row r="414" ht="107" customHeight="1">
+    <row r="414" ht="32" customHeight="1">
       <c r="A414" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38140,7 +38140,7 @@
       <c r="J414" s="1" t="inlineStr"/>
       <c r="K414" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#005；位置：L001-F005；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L414" s="1" t="inlineStr">
@@ -38193,7 +38193,7 @@
         </is>
       </c>
     </row>
-    <row r="415" ht="107" customHeight="1">
+    <row r="415" ht="32" customHeight="1">
       <c r="A415" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38232,7 +38232,7 @@
       <c r="J415" s="1" t="inlineStr"/>
       <c r="K415" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#006；位置：L001-F006；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L415" s="1" t="inlineStr">
@@ -38285,7 +38285,7 @@
         </is>
       </c>
     </row>
-    <row r="416" ht="107" customHeight="1">
+    <row r="416" ht="32" customHeight="1">
       <c r="A416" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38324,7 +38324,7 @@
       <c r="J416" s="1" t="inlineStr"/>
       <c r="K416" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R12#007；位置：L001-F007；源位置：B侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L416" s="1" t="inlineStr">
@@ -38377,7 +38377,7 @@
         </is>
       </c>
     </row>
-    <row r="417" ht="107" customHeight="1">
+    <row r="417" ht="32" customHeight="1">
       <c r="A417" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38416,7 +38416,7 @@
       <c r="J417" s="1" t="inlineStr"/>
       <c r="K417" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#001；位置：L003-F001；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L417" s="1" t="inlineStr">
@@ -38469,7 +38469,7 @@
         </is>
       </c>
     </row>
-    <row r="418" ht="107" customHeight="1">
+    <row r="418" ht="32" customHeight="1">
       <c r="A418" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38508,7 +38508,7 @@
       <c r="J418" s="1" t="inlineStr"/>
       <c r="K418" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#002；位置：L003-F002；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L418" s="1" t="inlineStr">
@@ -38561,7 +38561,7 @@
         </is>
       </c>
     </row>
-    <row r="419" ht="107" customHeight="1">
+    <row r="419" ht="32" customHeight="1">
       <c r="A419" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38600,7 +38600,7 @@
       <c r="J419" s="1" t="inlineStr"/>
       <c r="K419" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#003；位置：L003-F003；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L419" s="1" t="inlineStr">
@@ -38653,7 +38653,7 @@
         </is>
       </c>
     </row>
-    <row r="420" ht="107" customHeight="1">
+    <row r="420" ht="32" customHeight="1">
       <c r="A420" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38692,7 +38692,7 @@
       <c r="J420" s="1" t="inlineStr"/>
       <c r="K420" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#004；位置：L003-F004；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L420" s="1" t="inlineStr">
@@ -38745,7 +38745,7 @@
         </is>
       </c>
     </row>
-    <row r="421" ht="107" customHeight="1">
+    <row r="421" ht="32" customHeight="1">
       <c r="A421" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38784,7 +38784,7 @@
       <c r="J421" s="1" t="inlineStr"/>
       <c r="K421" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#005；位置：L003-F005；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L421" s="1" t="inlineStr">
@@ -38837,7 +38837,7 @@
         </is>
       </c>
     </row>
-    <row r="422" ht="107" customHeight="1">
+    <row r="422" ht="32" customHeight="1">
       <c r="A422" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38876,7 +38876,7 @@
       <c r="J422" s="1" t="inlineStr"/>
       <c r="K422" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#006；位置：L003-F006；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L422" s="1" t="inlineStr">
@@ -38929,7 +38929,7 @@
         </is>
       </c>
     </row>
-    <row r="423" ht="107" customHeight="1">
+    <row r="423" ht="32" customHeight="1">
       <c r="A423" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -38968,7 +38968,7 @@
       <c r="J423" s="1" t="inlineStr"/>
       <c r="K423" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R13#007；位置：L003-F007；源位置：B侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L423" s="1" t="inlineStr">
@@ -39021,7 +39021,7 @@
         </is>
       </c>
     </row>
-    <row r="424" ht="107" customHeight="1">
+    <row r="424" ht="32" customHeight="1">
       <c r="A424" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39060,7 +39060,7 @@
       <c r="J424" s="1" t="inlineStr"/>
       <c r="K424" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#001；位置：L005-F001；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L424" s="1" t="inlineStr">
@@ -39113,7 +39113,7 @@
         </is>
       </c>
     </row>
-    <row r="425" ht="107" customHeight="1">
+    <row r="425" ht="32" customHeight="1">
       <c r="A425" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39152,7 +39152,7 @@
       <c r="J425" s="1" t="inlineStr"/>
       <c r="K425" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#002；位置：L005-F002；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L425" s="1" t="inlineStr">
@@ -39205,7 +39205,7 @@
         </is>
       </c>
     </row>
-    <row r="426" ht="107" customHeight="1">
+    <row r="426" ht="32" customHeight="1">
       <c r="A426" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39244,7 +39244,7 @@
       <c r="J426" s="1" t="inlineStr"/>
       <c r="K426" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#003；位置：L005-F003；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L426" s="1" t="inlineStr">
@@ -39297,7 +39297,7 @@
         </is>
       </c>
     </row>
-    <row r="427" ht="107" customHeight="1">
+    <row r="427" ht="32" customHeight="1">
       <c r="A427" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39336,7 +39336,7 @@
       <c r="J427" s="1" t="inlineStr"/>
       <c r="K427" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#004；位置：L005-F004；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L427" s="1" t="inlineStr">
@@ -39389,7 +39389,7 @@
         </is>
       </c>
     </row>
-    <row r="428" ht="107" customHeight="1">
+    <row r="428" ht="32" customHeight="1">
       <c r="A428" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39428,7 +39428,7 @@
       <c r="J428" s="1" t="inlineStr"/>
       <c r="K428" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#005；位置：L005-F005；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L428" s="1" t="inlineStr">
@@ -39481,7 +39481,7 @@
         </is>
       </c>
     </row>
-    <row r="429" ht="107" customHeight="1">
+    <row r="429" ht="32" customHeight="1">
       <c r="A429" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39520,7 +39520,7 @@
       <c r="J429" s="1" t="inlineStr"/>
       <c r="K429" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#006；位置：L005-F006；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L429" s="1" t="inlineStr">
@@ -39573,7 +39573,7 @@
         </is>
       </c>
     </row>
-    <row r="430" ht="107" customHeight="1">
+    <row r="430" ht="32" customHeight="1">
       <c r="A430" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39612,7 +39612,7 @@
       <c r="J430" s="1" t="inlineStr"/>
       <c r="K430" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R14#007；位置：L005-F007；源位置：B侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L430" s="1" t="inlineStr">
@@ -39665,7 +39665,7 @@
         </is>
       </c>
     </row>
-    <row r="431" ht="107" customHeight="1">
+    <row r="431" ht="32" customHeight="1">
       <c r="A431" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39704,7 +39704,7 @@
       <c r="J431" s="1" t="inlineStr"/>
       <c r="K431" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#001；位置：L007-F001；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L431" s="1" t="inlineStr">
@@ -39757,7 +39757,7 @@
         </is>
       </c>
     </row>
-    <row r="432" ht="107" customHeight="1">
+    <row r="432" ht="32" customHeight="1">
       <c r="A432" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39796,7 +39796,7 @@
       <c r="J432" s="1" t="inlineStr"/>
       <c r="K432" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#002；位置：L007-F002；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L432" s="1" t="inlineStr">
@@ -39849,7 +39849,7 @@
         </is>
       </c>
     </row>
-    <row r="433" ht="107" customHeight="1">
+    <row r="433" ht="32" customHeight="1">
       <c r="A433" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39888,7 +39888,7 @@
       <c r="J433" s="1" t="inlineStr"/>
       <c r="K433" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#003；位置：L007-F003；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L433" s="1" t="inlineStr">
@@ -39941,7 +39941,7 @@
         </is>
       </c>
     </row>
-    <row r="434" ht="107" customHeight="1">
+    <row r="434" ht="32" customHeight="1">
       <c r="A434" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -39980,7 +39980,7 @@
       <c r="J434" s="1" t="inlineStr"/>
       <c r="K434" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#004；位置：L007-F004；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L434" s="1" t="inlineStr">
@@ -40033,7 +40033,7 @@
         </is>
       </c>
     </row>
-    <row r="435" ht="107" customHeight="1">
+    <row r="435" ht="32" customHeight="1">
       <c r="A435" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40072,7 +40072,7 @@
       <c r="J435" s="1" t="inlineStr"/>
       <c r="K435" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#005；位置：L007-F005；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L435" s="1" t="inlineStr">
@@ -40125,7 +40125,7 @@
         </is>
       </c>
     </row>
-    <row r="436" ht="107" customHeight="1">
+    <row r="436" ht="32" customHeight="1">
       <c r="A436" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40164,7 +40164,7 @@
       <c r="J436" s="1" t="inlineStr"/>
       <c r="K436" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#006；位置：L007-F006；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L436" s="1" t="inlineStr">
@@ -40217,7 +40217,7 @@
         </is>
       </c>
     </row>
-    <row r="437" ht="107" customHeight="1">
+    <row r="437" ht="32" customHeight="1">
       <c r="A437" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40256,7 +40256,7 @@
       <c r="J437" s="1" t="inlineStr"/>
       <c r="K437" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R15#007；位置：L007-F007；源位置：B侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：B侧→L；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L437" s="1" t="inlineStr">
@@ -40309,7 +40309,7 @@
         </is>
       </c>
     </row>
-    <row r="438" ht="107" customHeight="1">
+    <row r="438" ht="32" customHeight="1">
       <c r="A438" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40348,7 +40348,7 @@
       <c r="J438" s="1" t="inlineStr"/>
       <c r="K438" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#001；位置：R001-F001；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L438" s="1" t="inlineStr">
@@ -40401,7 +40401,7 @@
         </is>
       </c>
     </row>
-    <row r="439" ht="107" customHeight="1">
+    <row r="439" ht="32" customHeight="1">
       <c r="A439" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40440,7 +40440,7 @@
       <c r="J439" s="1" t="inlineStr"/>
       <c r="K439" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#002；位置：R001-F002；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L439" s="1" t="inlineStr">
@@ -40493,7 +40493,7 @@
         </is>
       </c>
     </row>
-    <row r="440" ht="107" customHeight="1">
+    <row r="440" ht="32" customHeight="1">
       <c r="A440" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40532,7 +40532,7 @@
       <c r="J440" s="1" t="inlineStr"/>
       <c r="K440" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#003；位置：R001-F003；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L440" s="1" t="inlineStr">
@@ -40585,7 +40585,7 @@
         </is>
       </c>
     </row>
-    <row r="441" ht="107" customHeight="1">
+    <row r="441" ht="32" customHeight="1">
       <c r="A441" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40624,7 +40624,7 @@
       <c r="J441" s="1" t="inlineStr"/>
       <c r="K441" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#004；位置：R001-F004；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L441" s="1" t="inlineStr">
@@ -40677,7 +40677,7 @@
         </is>
       </c>
     </row>
-    <row r="442" ht="107" customHeight="1">
+    <row r="442" ht="32" customHeight="1">
       <c r="A442" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40716,7 +40716,7 @@
       <c r="J442" s="1" t="inlineStr"/>
       <c r="K442" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#005；位置：R001-F005；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L442" s="1" t="inlineStr">
@@ -40769,7 +40769,7 @@
         </is>
       </c>
     </row>
-    <row r="443" ht="107" customHeight="1">
+    <row r="443" ht="32" customHeight="1">
       <c r="A443" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40808,7 +40808,7 @@
       <c r="J443" s="1" t="inlineStr"/>
       <c r="K443" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#006；位置：R001-F006；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L443" s="1" t="inlineStr">
@@ -40861,7 +40861,7 @@
         </is>
       </c>
     </row>
-    <row r="444" ht="107" customHeight="1">
+    <row r="444" ht="32" customHeight="1">
       <c r="A444" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40900,7 +40900,7 @@
       <c r="J444" s="1" t="inlineStr"/>
       <c r="K444" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R16#007；位置：R001-F007；源位置：A侧第1排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L444" s="1" t="inlineStr">
@@ -40953,7 +40953,7 @@
         </is>
       </c>
     </row>
-    <row r="445" ht="107" customHeight="1">
+    <row r="445" ht="32" customHeight="1">
       <c r="A445" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -40992,7 +40992,7 @@
       <c r="J445" s="1" t="inlineStr"/>
       <c r="K445" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#001；位置：R003-F001；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L445" s="1" t="inlineStr">
@@ -41045,7 +41045,7 @@
         </is>
       </c>
     </row>
-    <row r="446" ht="107" customHeight="1">
+    <row r="446" ht="32" customHeight="1">
       <c r="A446" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41084,7 +41084,7 @@
       <c r="J446" s="1" t="inlineStr"/>
       <c r="K446" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#002；位置：R003-F002；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L446" s="1" t="inlineStr">
@@ -41137,7 +41137,7 @@
         </is>
       </c>
     </row>
-    <row r="447" ht="107" customHeight="1">
+    <row r="447" ht="32" customHeight="1">
       <c r="A447" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41176,7 +41176,7 @@
       <c r="J447" s="1" t="inlineStr"/>
       <c r="K447" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#003；位置：R003-F003；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L447" s="1" t="inlineStr">
@@ -41229,7 +41229,7 @@
         </is>
       </c>
     </row>
-    <row r="448" ht="107" customHeight="1">
+    <row r="448" ht="32" customHeight="1">
       <c r="A448" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41268,7 +41268,7 @@
       <c r="J448" s="1" t="inlineStr"/>
       <c r="K448" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#004；位置：R003-F004；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L448" s="1" t="inlineStr">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
     </row>
-    <row r="449" ht="107" customHeight="1">
+    <row r="449" ht="32" customHeight="1">
       <c r="A449" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41360,7 +41360,7 @@
       <c r="J449" s="1" t="inlineStr"/>
       <c r="K449" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#005；位置：R003-F005；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L449" s="1" t="inlineStr">
@@ -41413,7 +41413,7 @@
         </is>
       </c>
     </row>
-    <row r="450" ht="107" customHeight="1">
+    <row r="450" ht="32" customHeight="1">
       <c r="A450" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41452,7 +41452,7 @@
       <c r="J450" s="1" t="inlineStr"/>
       <c r="K450" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#006；位置：R003-F006；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L450" s="1" t="inlineStr">
@@ -41505,7 +41505,7 @@
         </is>
       </c>
     </row>
-    <row r="451" ht="107" customHeight="1">
+    <row r="451" ht="32" customHeight="1">
       <c r="A451" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41544,7 +41544,7 @@
       <c r="J451" s="1" t="inlineStr"/>
       <c r="K451" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R17#007；位置：R003-F007；源位置：A侧第3排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L451" s="1" t="inlineStr">
@@ -41597,7 +41597,7 @@
         </is>
       </c>
     </row>
-    <row r="452" ht="107" customHeight="1">
+    <row r="452" ht="32" customHeight="1">
       <c r="A452" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41636,7 +41636,7 @@
       <c r="J452" s="1" t="inlineStr"/>
       <c r="K452" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#001；位置：R005-F001；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L452" s="1" t="inlineStr">
@@ -41689,7 +41689,7 @@
         </is>
       </c>
     </row>
-    <row r="453" ht="107" customHeight="1">
+    <row r="453" ht="32" customHeight="1">
       <c r="A453" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41728,7 +41728,7 @@
       <c r="J453" s="1" t="inlineStr"/>
       <c r="K453" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#002；位置：R005-F002；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L453" s="1" t="inlineStr">
@@ -41781,7 +41781,7 @@
         </is>
       </c>
     </row>
-    <row r="454" ht="107" customHeight="1">
+    <row r="454" ht="32" customHeight="1">
       <c r="A454" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41820,7 +41820,7 @@
       <c r="J454" s="1" t="inlineStr"/>
       <c r="K454" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#003；位置：R005-F003；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L454" s="1" t="inlineStr">
@@ -41873,7 +41873,7 @@
         </is>
       </c>
     </row>
-    <row r="455" ht="107" customHeight="1">
+    <row r="455" ht="32" customHeight="1">
       <c r="A455" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -41912,7 +41912,7 @@
       <c r="J455" s="1" t="inlineStr"/>
       <c r="K455" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#004；位置：R005-F004；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L455" s="1" t="inlineStr">
@@ -41965,7 +41965,7 @@
         </is>
       </c>
     </row>
-    <row r="456" ht="107" customHeight="1">
+    <row r="456" ht="32" customHeight="1">
       <c r="A456" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42004,7 +42004,7 @@
       <c r="J456" s="1" t="inlineStr"/>
       <c r="K456" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#005；位置：R005-F005；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L456" s="1" t="inlineStr">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
     </row>
-    <row r="457" ht="107" customHeight="1">
+    <row r="457" ht="32" customHeight="1">
       <c r="A457" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42096,7 +42096,7 @@
       <c r="J457" s="1" t="inlineStr"/>
       <c r="K457" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#006；位置：R005-F006；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L457" s="1" t="inlineStr">
@@ -42149,7 +42149,7 @@
         </is>
       </c>
     </row>
-    <row r="458" ht="107" customHeight="1">
+    <row r="458" ht="32" customHeight="1">
       <c r="A458" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42188,7 +42188,7 @@
       <c r="J458" s="1" t="inlineStr"/>
       <c r="K458" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R18#007；位置：R005-F007；源位置：A侧第5排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L458" s="1" t="inlineStr">
@@ -42241,7 +42241,7 @@
         </is>
       </c>
     </row>
-    <row r="459" ht="107" customHeight="1">
+    <row r="459" ht="32" customHeight="1">
       <c r="A459" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42280,7 +42280,7 @@
       <c r="J459" s="1" t="inlineStr"/>
       <c r="K459" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#001；位置：R007-F001；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F001=第1弯头→TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L459" s="1" t="inlineStr">
@@ -42333,7 +42333,7 @@
         </is>
       </c>
     </row>
-    <row r="460" ht="107" customHeight="1">
+    <row r="460" ht="32" customHeight="1">
       <c r="A460" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42372,7 +42372,7 @@
       <c r="J460" s="1" t="inlineStr"/>
       <c r="K460" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#002；位置：R007-F002；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F002=第2弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L460" s="1" t="inlineStr">
@@ -42425,7 +42425,7 @@
         </is>
       </c>
     </row>
-    <row r="461" ht="107" customHeight="1">
+    <row r="461" ht="32" customHeight="1">
       <c r="A461" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42464,7 +42464,7 @@
       <c r="J461" s="1" t="inlineStr"/>
       <c r="K461" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#003；位置：R007-F003；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F003=第3弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L461" s="1" t="inlineStr">
@@ -42517,7 +42517,7 @@
         </is>
       </c>
     </row>
-    <row r="462" ht="107" customHeight="1">
+    <row r="462" ht="32" customHeight="1">
       <c r="A462" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42556,7 +42556,7 @@
       <c r="J462" s="1" t="inlineStr"/>
       <c r="K462" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#004；位置：R007-F004；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F004=第4弯头→SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L462" s="1" t="inlineStr">
@@ -42609,7 +42609,7 @@
         </is>
       </c>
     </row>
-    <row r="463" ht="107" customHeight="1">
+    <row r="463" ht="32" customHeight="1">
       <c r="A463" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42648,7 +42648,7 @@
       <c r="J463" s="1" t="inlineStr"/>
       <c r="K463" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#005；位置：R007-F005；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F005=第5弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L463" s="1" t="inlineStr">
@@ -42701,7 +42701,7 @@
         </is>
       </c>
     </row>
-    <row r="464" ht="107" customHeight="1">
+    <row r="464" ht="32" customHeight="1">
       <c r="A464" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42740,7 +42740,7 @@
       <c r="J464" s="1" t="inlineStr"/>
       <c r="K464" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#006；位置：R007-F006；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F006=第6弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L464" s="1" t="inlineStr">
@@ -42793,7 +42793,7 @@
         </is>
       </c>
     </row>
-    <row r="465" ht="107" customHeight="1">
+    <row r="465" ht="32" customHeight="1">
       <c r="A465" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -42832,7 +42832,7 @@
       <c r="J465" s="1" t="inlineStr"/>
       <c r="K465" s="1" t="inlineStr">
         <is>
-          <t>批次：2021年2号机A修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2021年2号机A修!R19#007；位置：R007-F007；源位置：A侧第7排炉前至炉后数1-7个下部弯头；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第一个弯头为TP304H，2、3、4为T91，5、6、7为12CrMoVG。；机组按已确认批次修正：1G→2G；侧别按用户规则修正：A侧→R；材质按管位区带映射：F007=第7弯头→12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L465" s="1" t="inlineStr">
